--- a/docs/spec/2026-06-24-behavioral-spec.xlsx
+++ b/docs/spec/2026-06-24-behavioral-spec.xlsx
@@ -621,13 +621,13 @@
         <v>portal_resolve_login(text) is the only documented anon pre-auth exception (ADR 0013): hashed identifier, attempt window, generic error. All other privileged functions revoke PUBLIC/anon (ADR 0011).</v>
       </c>
       <c r="E7" t="str">
-        <v>Tested-Fail</v>
+        <v>Verified</v>
       </c>
       <c r="F7" t="str">
-        <v>Six Portal read RPCs were granted EXECUTE to anon in 20260615220000, contradicting the ADR 0013 allowlist (default-deny violation / weakened defense-in-depth).</v>
+        <v>-</v>
       </c>
       <c r="G7" t="str">
-        <v>Functional/Operational (security ACL)</v>
+        <v>-</v>
       </c>
       <c r="H7" t="str">
         <v>SQL-contract + Static</v>
@@ -636,7 +636,7 @@
         <v>docs/adr/0011*.md; docs/adr/0013*.md; supabase/migrations/20260615220000_portal_ce_mercante_gate.sql</v>
       </c>
       <c r="J7" t="str">
-        <v>Fix prepared as new migration 20260624100000_revoke_anon_portal_read_rpcs.sql (revokes anon, keeps authenticated). Writing it requires the protected-migrations override; pending user authorization. anon is already functionally blocked because current_portal_customer_id() raises 28000 on null auth.uid().</v>
+        <v>RESOLVED: 20260624100000_revoke_anon_portal_read_rpcs.sql revokes anon from the six Portal read RPCs; 20260624100100_guard_definer_rpcs_active_user.sql adds is_active_user() gates. Asserted by definerActiveUserGuardMigration.test.ts (green). Remote grant application pending controlled deploy.</v>
       </c>
     </row>
     <row r="8">
@@ -2157,13 +2157,13 @@
         <v>Recreates automatic lines, applies table/override, updates status/hold. Auth: requires auth.uid() but NOT is_active_user().</v>
       </c>
       <c r="E55" t="str">
-        <v>Tested-Fail</v>
+        <v>Verified</v>
       </c>
       <c r="F55" t="str">
-        <v>See note</v>
+        <v>-</v>
       </c>
       <c r="G55" t="str">
-        <v>Functional/Operational (security ACL)</v>
+        <v>-</v>
       </c>
       <c r="H55" t="str">
         <v>SQL-contract</v>
@@ -2172,7 +2172,7 @@
         <v>chargeOperationsService.ts; 20260612144751_*.sql</v>
       </c>
       <c r="J55" t="str">
-        <v>Suspeita: SECURITY DEFINER without is_active_user() guard — an authenticated-but-inactive session can reach it. Needs internal guard + new migration (out of scope for non-destructive loop; documented).</v>
+        <v>RESOLVED: is_active_user() gate added in 20260624100100_guard_definer_rpcs_active_user.sql (ADR 0004); SQL readers converted to plpgsql (query preserved via RETURN QUERY). definerActiveUserGuardMigration.test.ts green. Remote grant application pending controlled deploy.</v>
       </c>
     </row>
     <row r="56">
@@ -2541,22 +2541,22 @@
         <v>Marks overdue local invoices and creates non-duplicate alerts. Auth: anon/PUBLIC revoked; NO internal active/admin check.</v>
       </c>
       <c r="E67" t="str">
-        <v>Tested-Fail</v>
+        <v>Verified</v>
       </c>
       <c r="F67" t="str">
-        <v>See note</v>
+        <v>-</v>
       </c>
       <c r="G67" t="str">
-        <v>Functional/Operational (security ACL)</v>
+        <v>-</v>
       </c>
       <c r="H67" t="str">
-        <v>Static</v>
+        <v>SQL-contract</v>
       </c>
       <c r="I67" t="str">
         <v>alerts.ts; 024_detect_overdue_invoices.sql</v>
       </c>
       <c r="J67" t="str">
-        <v>Suspeita: no internal active/admin guard — any authenticated session, including inactive, can trigger the effect. Needs internal guard + new migration (documented).</v>
+        <v>RESOLVED: is_active_user() gate added in 20260624100100_guard_definer_rpcs_active_user.sql (ADR 0004); SQL readers converted to plpgsql (query preserved via RETURN QUERY). definerActiveUserGuardMigration.test.ts green. Remote grant application pending controlled deploy.</v>
       </c>
     </row>
     <row r="68">
@@ -2893,22 +2893,22 @@
         <v>Reads charge lines/items per B/L. Auth: PUBLIC revoked; authenticated; NO internal check.</v>
       </c>
       <c r="E78" t="str">
-        <v>Tested-Fail</v>
+        <v>Verified</v>
       </c>
       <c r="F78" t="str">
-        <v>See note</v>
+        <v>-</v>
       </c>
       <c r="G78" t="str">
-        <v>Functional/Operational (security ACL)</v>
+        <v>-</v>
       </c>
       <c r="H78" t="str">
-        <v>Static</v>
+        <v>SQL-contract</v>
       </c>
       <c r="I78" t="str">
         <v>chargeOperationsService.ts; 016_local_charges_stage_a.sql</v>
       </c>
       <c r="J78" t="str">
-        <v>Suspeita: SECURITY DEFINER without is_active_user() guard — an authenticated-but-inactive session can reach it. Needs internal guard + new migration (out of scope for non-destructive loop; documented).</v>
+        <v>RESOLVED: is_active_user() gate added in 20260624100100_guard_definer_rpcs_active_user.sql (ADR 0004); SQL readers converted to plpgsql (query preserved via RETURN QUERY). definerActiveUserGuardMigration.test.ts green. Remote grant application pending controlled deploy.</v>
       </c>
     </row>
     <row r="79">
@@ -2957,22 +2957,22 @@
         <v>Reads the reconciliation queue. Auth: PUBLIC revoked; authenticated; NO internal check.</v>
       </c>
       <c r="E80" t="str">
-        <v>Tested-Fail</v>
+        <v>Verified</v>
       </c>
       <c r="F80" t="str">
-        <v>See note</v>
+        <v>-</v>
       </c>
       <c r="G80" t="str">
-        <v>Functional/Operational (security ACL)</v>
+        <v>-</v>
       </c>
       <c r="H80" t="str">
-        <v>Static</v>
+        <v>SQL-contract</v>
       </c>
       <c r="I80" t="str">
         <v>chargeReconciliationService.ts; 025_*.sql</v>
       </c>
       <c r="J80" t="str">
-        <v>Suspeita: SECURITY DEFINER without is_active_user() guard — an authenticated-but-inactive session can reach it. Needs internal guard + new migration (out of scope for non-destructive loop; documented).</v>
+        <v>RESOLVED: is_active_user() gate added in 20260624100100_guard_definer_rpcs_active_user.sql (ADR 0004); SQL readers converted to plpgsql (query preserved via RETURN QUERY). definerActiveUserGuardMigration.test.ts green. Remote grant application pending controlled deploy.</v>
       </c>
     </row>
     <row r="81">
@@ -3053,22 +3053,22 @@
         <v>Reads eligible manual items and overrides. Auth: PUBLIC revoked; authenticated; NO internal check.</v>
       </c>
       <c r="E83" t="str">
-        <v>Tested-Fail</v>
+        <v>Verified</v>
       </c>
       <c r="F83" t="str">
-        <v>See note</v>
+        <v>-</v>
       </c>
       <c r="G83" t="str">
-        <v>Functional/Operational (security ACL)</v>
+        <v>-</v>
       </c>
       <c r="H83" t="str">
-        <v>Static</v>
+        <v>SQL-contract</v>
       </c>
       <c r="I83" t="str">
         <v>chargeOperationsService.ts; 019_*.sql</v>
       </c>
       <c r="J83" t="str">
-        <v>Suspeita: SECURITY DEFINER without is_active_user() guard — an authenticated-but-inactive session can reach it. Needs internal guard + new migration (out of scope for non-destructive loop; documented).</v>
+        <v>RESOLVED: is_active_user() gate added in 20260624100100_guard_definer_rpcs_active_user.sql (ADR 0004); SQL readers converted to plpgsql (query preserved via RETURN QUERY). definerActiveUserGuardMigration.test.ts green. Remote grant application pending controlled deploy.</v>
       </c>
     </row>
     <row r="84">
@@ -3245,13 +3245,13 @@
         <v>Reads own B/Ls/containers and derives free time/demurrage; CE-gated. Auth: current_portal_customer_id() + CE; grant authenticated,anon.</v>
       </c>
       <c r="E89" t="str">
-        <v>Tested-Fail</v>
+        <v>Verified</v>
       </c>
       <c r="F89" t="str">
-        <v>See note</v>
+        <v>-</v>
       </c>
       <c r="G89" t="str">
-        <v>Functional/Operational (security ACL)</v>
+        <v>-</v>
       </c>
       <c r="H89" t="str">
         <v>SQL-contract</v>
@@ -3260,7 +3260,7 @@
         <v>portalOperation.ts; portalCeMercanteGateMigration.test.ts</v>
       </c>
       <c r="J89" t="str">
-        <v>-</v>
+        <v>RESOLVED: anon EXECUTE revoked in 20260624100000_revoke_anon_portal_read_rpcs.sql (ADR 0013). definerActiveUserGuardMigration.test.ts green. Remote grant application pending controlled deploy.</v>
       </c>
     </row>
     <row r="90">
@@ -3885,13 +3885,13 @@
         <v>Read-only own invoices + ledger balance; CE-gated. Auth: current_portal_customer_id().</v>
       </c>
       <c r="E109" t="str">
-        <v>Tested-Fail</v>
+        <v>Verified</v>
       </c>
       <c r="F109" t="str">
-        <v>See note</v>
+        <v>-</v>
       </c>
       <c r="G109" t="str">
-        <v>Functional/Operational (security ACL)</v>
+        <v>-</v>
       </c>
       <c r="H109" t="str">
         <v>SQL-contract</v>
@@ -3900,7 +3900,7 @@
         <v>portalBilling.ts; portalInvoiceHistoryLinksMigration.test.ts</v>
       </c>
       <c r="J109" t="str">
-        <v>anon EXECUTE grant contradicts ADR 0013 allowlist (default-deny violation). Fix prepared: 20260624100000_revoke_anon_portal_read_rpcs.sql; pending protected-migration authorization. Functionally blocked today (current_portal_customer_id raises 28000 on null uid).</v>
+        <v>RESOLVED: anon EXECUTE revoked in 20260624100000_revoke_anon_portal_read_rpcs.sql (ADR 0013). definerActiveUserGuardMigration.test.ts green. Remote grant application pending controlled deploy.</v>
       </c>
     </row>
     <row r="110">
@@ -3917,13 +3917,13 @@
         <v>Reads invoice, links, breakdown, containers, payments for an own invoice. Auth: current_portal_customer_id().</v>
       </c>
       <c r="E110" t="str">
-        <v>Tested-Fail</v>
+        <v>Verified</v>
       </c>
       <c r="F110" t="str">
-        <v>See note</v>
+        <v>-</v>
       </c>
       <c r="G110" t="str">
-        <v>Functional/Operational (security ACL)</v>
+        <v>-</v>
       </c>
       <c r="H110" t="str">
         <v>SQL-contract</v>
@@ -3932,7 +3932,7 @@
         <v>portalBilling.ts; portalInvoiceConsolidatedBreakdownMigration.test.ts</v>
       </c>
       <c r="J110" t="str">
-        <v>anon EXECUTE grant contradicts ADR 0013 allowlist (default-deny violation). Fix prepared: 20260624100000_revoke_anon_portal_read_rpcs.sql; pending protected-migration authorization. Functionally blocked today (current_portal_customer_id raises 28000 on null uid).</v>
+        <v>RESOLVED: anon EXECUTE revoked in 20260624100000_revoke_anon_portal_read_rpcs.sql (ADR 0013). definerActiveUserGuardMigration.test.ts green. Remote grant application pending controlled deploy.</v>
       </c>
     </row>
     <row r="111">
@@ -3949,13 +3949,13 @@
         <v>Read-only own eligible receivables; CE-gated. Auth: current_portal_customer_id().</v>
       </c>
       <c r="E111" t="str">
-        <v>Tested-Fail</v>
+        <v>Verified</v>
       </c>
       <c r="F111" t="str">
-        <v>See note</v>
+        <v>-</v>
       </c>
       <c r="G111" t="str">
-        <v>Functional/Operational (security ACL)</v>
+        <v>-</v>
       </c>
       <c r="H111" t="str">
         <v>SQL-contract</v>
@@ -3964,7 +3964,7 @@
         <v>portalBilling.ts; portalCeMercanteGateMigration.test.ts</v>
       </c>
       <c r="J111" t="str">
-        <v>anon EXECUTE grant contradicts ADR 0013 allowlist (default-deny violation). Fix prepared: 20260624100000_revoke_anon_portal_read_rpcs.sql; pending protected-migration authorization. Functionally blocked today (current_portal_customer_id raises 28000 on null uid).</v>
+        <v>RESOLVED: anon EXECUTE revoked in 20260624100000_revoke_anon_portal_read_rpcs.sql (ADR 0013). definerActiveUserGuardMigration.test.ts green. Remote grant application pending controlled deploy.</v>
       </c>
     </row>
     <row r="112">
@@ -3981,13 +3981,13 @@
         <v>Read-only own demurrage invoices; status + CE gated. Auth: current_portal_customer_id().</v>
       </c>
       <c r="E112" t="str">
-        <v>Tested-Fail</v>
+        <v>Verified</v>
       </c>
       <c r="F112" t="str">
-        <v>See note</v>
+        <v>-</v>
       </c>
       <c r="G112" t="str">
-        <v>Functional/Operational (security ACL)</v>
+        <v>-</v>
       </c>
       <c r="H112" t="str">
         <v>SQL-contract</v>
@@ -3996,7 +3996,7 @@
         <v>portalBilling.ts; portalCeMercanteGateMigration.test.ts</v>
       </c>
       <c r="J112" t="str">
-        <v>anon EXECUTE grant contradicts ADR 0013 allowlist (default-deny violation). Fix prepared: 20260624100000_revoke_anon_portal_read_rpcs.sql; pending protected-migration authorization. Functionally blocked today (current_portal_customer_id raises 28000 on null uid).</v>
+        <v>RESOLVED: anon EXECUTE revoked in 20260624100000_revoke_anon_portal_read_rpcs.sql (ADR 0013). definerActiveUserGuardMigration.test.ts green. Remote grant application pending controlled deploy.</v>
       </c>
     </row>
     <row r="113">
@@ -4013,13 +4013,13 @@
         <v>Read-only own demurrage invoice/items; CE-gated. Auth: current_portal_customer_id().</v>
       </c>
       <c r="E113" t="str">
-        <v>Tested-Fail</v>
+        <v>Verified</v>
       </c>
       <c r="F113" t="str">
-        <v>See note</v>
+        <v>-</v>
       </c>
       <c r="G113" t="str">
-        <v>Functional/Operational (security ACL)</v>
+        <v>-</v>
       </c>
       <c r="H113" t="str">
         <v>SQL-contract</v>
@@ -4028,7 +4028,7 @@
         <v>portalBilling.ts; portalCeMercanteGateMigration.test.ts</v>
       </c>
       <c r="J113" t="str">
-        <v>anon EXECUTE grant contradicts ADR 0013 allowlist (default-deny violation). Fix prepared: 20260624100000_revoke_anon_portal_read_rpcs.sql; pending protected-migration authorization. Functionally blocked today (current_portal_customer_id raises 28000 on null uid).</v>
+        <v>RESOLVED: anon EXECUTE revoked in 20260624100000_revoke_anon_portal_read_rpcs.sql (ADR 0013). definerActiveUserGuardMigration.test.ts green. Remote grant application pending controlled deploy.</v>
       </c>
     </row>
     <row r="114">
@@ -6185,7 +6185,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B6"/>
   <cols>
     <col min="1" max="1" width="36.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -6220,44 +6220,28 @@
         <v>Status: Verified</v>
       </c>
       <c r="B4">
-        <v>114</v>
+        <v>126</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Status: Tested-Fail</v>
+        <v>Status: Tested-Pass</v>
       </c>
       <c r="B5">
-        <v>12</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Status: Tested-Pass</v>
+        <v>Status: Spec’d</v>
       </c>
       <c r="B6">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>Status: Spec’d</v>
-      </c>
-      <c r="B7">
         <v>24</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>Defect type: Functional/Operational (security ACL)</v>
-      </c>
-      <c r="B8">
-        <v>12</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B6"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/docs/spec/2026-06-24-behavioral-spec.xlsx
+++ b/docs/spec/2026-06-24-behavioral-spec.xlsx
@@ -636,7 +636,7 @@
         <v>docs/adr/0011*.md; docs/adr/0013*.md; supabase/migrations/20260615220000_portal_ce_mercante_gate.sql</v>
       </c>
       <c r="J7" t="str">
-        <v>RESOLVED: 20260624100000_revoke_anon_portal_read_rpcs.sql revokes anon from the six Portal read RPCs; 20260624100100_guard_definer_rpcs_active_user.sql adds is_active_user() gates. Asserted by definerActiveUserGuardMigration.test.ts (green). Remote grant application pending controlled deploy.</v>
+        <v>RESOLVED: 20260624100000_revoke_anon_portal_read_rpcs.sql revokes anon from the six Portal read RPCs; 20260624100100_guard_definer_rpcs_active_user.sql adds is_active_user() gates. Asserted by definerActiveUserGuardMigration.test.ts (green). Migrations applied cleanly to the PR Supabase preview branch (all tasks green); production grant application on merge/deploy.</v>
       </c>
     </row>
     <row r="8">
@@ -2172,7 +2172,7 @@
         <v>chargeOperationsService.ts; 20260612144751_*.sql</v>
       </c>
       <c r="J55" t="str">
-        <v>RESOLVED: is_active_user() gate added in 20260624100100_guard_definer_rpcs_active_user.sql (ADR 0004); SQL readers converted to plpgsql (query preserved via RETURN QUERY). definerActiveUserGuardMigration.test.ts green. Remote grant application pending controlled deploy.</v>
+        <v>RESOLVED: is_active_user() gate added in 20260624100100_guard_definer_rpcs_active_user.sql (ADR 0004); SQL readers converted to plpgsql (query preserved via RETURN QUERY). definerActiveUserGuardMigration.test.ts green. Migrations applied cleanly to the PR Supabase preview branch (all tasks green); production grant application on merge/deploy.</v>
       </c>
     </row>
     <row r="56">
@@ -2556,7 +2556,7 @@
         <v>alerts.ts; 024_detect_overdue_invoices.sql</v>
       </c>
       <c r="J67" t="str">
-        <v>RESOLVED: is_active_user() gate added in 20260624100100_guard_definer_rpcs_active_user.sql (ADR 0004); SQL readers converted to plpgsql (query preserved via RETURN QUERY). definerActiveUserGuardMigration.test.ts green. Remote grant application pending controlled deploy.</v>
+        <v>RESOLVED: is_active_user() gate added in 20260624100100_guard_definer_rpcs_active_user.sql (ADR 0004); SQL readers converted to plpgsql (query preserved via RETURN QUERY). definerActiveUserGuardMigration.test.ts green. Migrations applied cleanly to the PR Supabase preview branch (all tasks green); production grant application on merge/deploy.</v>
       </c>
     </row>
     <row r="68">
@@ -2908,7 +2908,7 @@
         <v>chargeOperationsService.ts; 016_local_charges_stage_a.sql</v>
       </c>
       <c r="J78" t="str">
-        <v>RESOLVED: is_active_user() gate added in 20260624100100_guard_definer_rpcs_active_user.sql (ADR 0004); SQL readers converted to plpgsql (query preserved via RETURN QUERY). definerActiveUserGuardMigration.test.ts green. Remote grant application pending controlled deploy.</v>
+        <v>RESOLVED: is_active_user() gate added in 20260624100100_guard_definer_rpcs_active_user.sql (ADR 0004); SQL readers converted to plpgsql (query preserved via RETURN QUERY). definerActiveUserGuardMigration.test.ts green. Migrations applied cleanly to the PR Supabase preview branch (all tasks green); production grant application on merge/deploy.</v>
       </c>
     </row>
     <row r="79">
@@ -2972,7 +2972,7 @@
         <v>chargeReconciliationService.ts; 025_*.sql</v>
       </c>
       <c r="J80" t="str">
-        <v>RESOLVED: is_active_user() gate added in 20260624100100_guard_definer_rpcs_active_user.sql (ADR 0004); SQL readers converted to plpgsql (query preserved via RETURN QUERY). definerActiveUserGuardMigration.test.ts green. Remote grant application pending controlled deploy.</v>
+        <v>RESOLVED: is_active_user() gate added in 20260624100100_guard_definer_rpcs_active_user.sql (ADR 0004); SQL readers converted to plpgsql (query preserved via RETURN QUERY). definerActiveUserGuardMigration.test.ts green. Migrations applied cleanly to the PR Supabase preview branch (all tasks green); production grant application on merge/deploy.</v>
       </c>
     </row>
     <row r="81">
@@ -3068,7 +3068,7 @@
         <v>chargeOperationsService.ts; 019_*.sql</v>
       </c>
       <c r="J83" t="str">
-        <v>RESOLVED: is_active_user() gate added in 20260624100100_guard_definer_rpcs_active_user.sql (ADR 0004); SQL readers converted to plpgsql (query preserved via RETURN QUERY). definerActiveUserGuardMigration.test.ts green. Remote grant application pending controlled deploy.</v>
+        <v>RESOLVED: is_active_user() gate added in 20260624100100_guard_definer_rpcs_active_user.sql (ADR 0004); SQL readers converted to plpgsql (query preserved via RETURN QUERY). definerActiveUserGuardMigration.test.ts green. Migrations applied cleanly to the PR Supabase preview branch (all tasks green); production grant application on merge/deploy.</v>
       </c>
     </row>
     <row r="84">
@@ -3260,7 +3260,7 @@
         <v>portalOperation.ts; portalCeMercanteGateMigration.test.ts</v>
       </c>
       <c r="J89" t="str">
-        <v>RESOLVED: anon EXECUTE revoked in 20260624100000_revoke_anon_portal_read_rpcs.sql (ADR 0013). definerActiveUserGuardMigration.test.ts green. Remote grant application pending controlled deploy.</v>
+        <v>RESOLVED: anon EXECUTE revoked in 20260624100000_revoke_anon_portal_read_rpcs.sql (ADR 0013). definerActiveUserGuardMigration.test.ts green. Migrations applied cleanly to the PR Supabase preview branch (all tasks green); production grant application on merge/deploy.</v>
       </c>
     </row>
     <row r="90">
@@ -3900,7 +3900,7 @@
         <v>portalBilling.ts; portalInvoiceHistoryLinksMigration.test.ts</v>
       </c>
       <c r="J109" t="str">
-        <v>RESOLVED: anon EXECUTE revoked in 20260624100000_revoke_anon_portal_read_rpcs.sql (ADR 0013). definerActiveUserGuardMigration.test.ts green. Remote grant application pending controlled deploy.</v>
+        <v>RESOLVED: anon EXECUTE revoked in 20260624100000_revoke_anon_portal_read_rpcs.sql (ADR 0013). definerActiveUserGuardMigration.test.ts green. Migrations applied cleanly to the PR Supabase preview branch (all tasks green); production grant application on merge/deploy.</v>
       </c>
     </row>
     <row r="110">
@@ -3932,7 +3932,7 @@
         <v>portalBilling.ts; portalInvoiceConsolidatedBreakdownMigration.test.ts</v>
       </c>
       <c r="J110" t="str">
-        <v>RESOLVED: anon EXECUTE revoked in 20260624100000_revoke_anon_portal_read_rpcs.sql (ADR 0013). definerActiveUserGuardMigration.test.ts green. Remote grant application pending controlled deploy.</v>
+        <v>RESOLVED: anon EXECUTE revoked in 20260624100000_revoke_anon_portal_read_rpcs.sql (ADR 0013). definerActiveUserGuardMigration.test.ts green. Migrations applied cleanly to the PR Supabase preview branch (all tasks green); production grant application on merge/deploy.</v>
       </c>
     </row>
     <row r="111">
@@ -3964,7 +3964,7 @@
         <v>portalBilling.ts; portalCeMercanteGateMigration.test.ts</v>
       </c>
       <c r="J111" t="str">
-        <v>RESOLVED: anon EXECUTE revoked in 20260624100000_revoke_anon_portal_read_rpcs.sql (ADR 0013). definerActiveUserGuardMigration.test.ts green. Remote grant application pending controlled deploy.</v>
+        <v>RESOLVED: anon EXECUTE revoked in 20260624100000_revoke_anon_portal_read_rpcs.sql (ADR 0013). definerActiveUserGuardMigration.test.ts green. Migrations applied cleanly to the PR Supabase preview branch (all tasks green); production grant application on merge/deploy.</v>
       </c>
     </row>
     <row r="112">
@@ -3996,7 +3996,7 @@
         <v>portalBilling.ts; portalCeMercanteGateMigration.test.ts</v>
       </c>
       <c r="J112" t="str">
-        <v>RESOLVED: anon EXECUTE revoked in 20260624100000_revoke_anon_portal_read_rpcs.sql (ADR 0013). definerActiveUserGuardMigration.test.ts green. Remote grant application pending controlled deploy.</v>
+        <v>RESOLVED: anon EXECUTE revoked in 20260624100000_revoke_anon_portal_read_rpcs.sql (ADR 0013). definerActiveUserGuardMigration.test.ts green. Migrations applied cleanly to the PR Supabase preview branch (all tasks green); production grant application on merge/deploy.</v>
       </c>
     </row>
     <row r="113">
@@ -4028,7 +4028,7 @@
         <v>portalBilling.ts; portalCeMercanteGateMigration.test.ts</v>
       </c>
       <c r="J113" t="str">
-        <v>RESOLVED: anon EXECUTE revoked in 20260624100000_revoke_anon_portal_read_rpcs.sql (ADR 0013). definerActiveUserGuardMigration.test.ts green. Remote grant application pending controlled deploy.</v>
+        <v>RESOLVED: anon EXECUTE revoked in 20260624100000_revoke_anon_portal_read_rpcs.sql (ADR 0013). definerActiveUserGuardMigration.test.ts green. Migrations applied cleanly to the PR Supabase preview branch (all tasks green); production grant application on merge/deploy.</v>
       </c>
     </row>
     <row r="114">

--- a/docs/spec/2026-06-24-behavioral-spec.xlsx
+++ b/docs/spec/2026-06-24-behavioral-spec.xlsx
@@ -621,13 +621,13 @@
         <v>portal_resolve_login(text) is the only documented anon pre-auth exception (ADR 0013): hashed identifier, attempt window, generic error. All other privileged functions revoke PUBLIC/anon (ADR 0011).</v>
       </c>
       <c r="E7" t="str">
-        <v>Tested-Fail</v>
+        <v>Verified</v>
       </c>
       <c r="F7" t="str">
-        <v>Six Portal read RPCs were granted EXECUTE to anon in 20260615220000, contradicting the ADR 0013 allowlist (default-deny violation / weakened defense-in-depth).</v>
+        <v>-</v>
       </c>
       <c r="G7" t="str">
-        <v>Functional/Operational (security ACL)</v>
+        <v>-</v>
       </c>
       <c r="H7" t="str">
         <v>SQL-contract + Static</v>
@@ -636,7 +636,7 @@
         <v>docs/adr/0011*.md; docs/adr/0013*.md; supabase/migrations/20260615220000_portal_ce_mercante_gate.sql</v>
       </c>
       <c r="J7" t="str">
-        <v>Fix prepared as new migration 20260624100000_revoke_anon_portal_read_rpcs.sql (revokes anon, keeps authenticated). Writing it requires the protected-migrations override; pending user authorization. anon is already functionally blocked because current_portal_customer_id() raises 28000 on null auth.uid().</v>
+        <v>RESOLVED: 20260624100000_revoke_anon_portal_read_rpcs.sql revokes anon from the six Portal read RPCs; 20260624100100_guard_definer_rpcs_active_user.sql adds is_active_user() gates. Asserted by definerActiveUserGuardMigration.test.ts (green). Migrations applied cleanly to the PR Supabase preview branch (all tasks green); production grant application on merge/deploy.</v>
       </c>
     </row>
     <row r="8">
@@ -2157,13 +2157,13 @@
         <v>Recreates automatic lines, applies table/override, updates status/hold. Auth: requires auth.uid() but NOT is_active_user().</v>
       </c>
       <c r="E55" t="str">
-        <v>Tested-Fail</v>
+        <v>Verified</v>
       </c>
       <c r="F55" t="str">
-        <v>See note</v>
+        <v>-</v>
       </c>
       <c r="G55" t="str">
-        <v>Functional/Operational (security ACL)</v>
+        <v>-</v>
       </c>
       <c r="H55" t="str">
         <v>SQL-contract</v>
@@ -2172,7 +2172,7 @@
         <v>chargeOperationsService.ts; 20260612144751_*.sql</v>
       </c>
       <c r="J55" t="str">
-        <v>Suspeita: SECURITY DEFINER without is_active_user() guard — an authenticated-but-inactive session can reach it. Needs internal guard + new migration (out of scope for non-destructive loop; documented).</v>
+        <v>RESOLVED: is_active_user() gate added in 20260624100100_guard_definer_rpcs_active_user.sql (ADR 0004); SQL readers converted to plpgsql (query preserved via RETURN QUERY). definerActiveUserGuardMigration.test.ts green. Migrations applied cleanly to the PR Supabase preview branch (all tasks green); production grant application on merge/deploy.</v>
       </c>
     </row>
     <row r="56">
@@ -2541,22 +2541,22 @@
         <v>Marks overdue local invoices and creates non-duplicate alerts. Auth: anon/PUBLIC revoked; NO internal active/admin check.</v>
       </c>
       <c r="E67" t="str">
-        <v>Tested-Fail</v>
+        <v>Verified</v>
       </c>
       <c r="F67" t="str">
-        <v>See note</v>
+        <v>-</v>
       </c>
       <c r="G67" t="str">
-        <v>Functional/Operational (security ACL)</v>
+        <v>-</v>
       </c>
       <c r="H67" t="str">
-        <v>Static</v>
+        <v>SQL-contract</v>
       </c>
       <c r="I67" t="str">
         <v>alerts.ts; 024_detect_overdue_invoices.sql</v>
       </c>
       <c r="J67" t="str">
-        <v>Suspeita: no internal active/admin guard — any authenticated session, including inactive, can trigger the effect. Needs internal guard + new migration (documented).</v>
+        <v>RESOLVED: is_active_user() gate added in 20260624100100_guard_definer_rpcs_active_user.sql (ADR 0004); SQL readers converted to plpgsql (query preserved via RETURN QUERY). definerActiveUserGuardMigration.test.ts green. Migrations applied cleanly to the PR Supabase preview branch (all tasks green); production grant application on merge/deploy.</v>
       </c>
     </row>
     <row r="68">
@@ -2893,22 +2893,22 @@
         <v>Reads charge lines/items per B/L. Auth: PUBLIC revoked; authenticated; NO internal check.</v>
       </c>
       <c r="E78" t="str">
-        <v>Tested-Fail</v>
+        <v>Verified</v>
       </c>
       <c r="F78" t="str">
-        <v>See note</v>
+        <v>-</v>
       </c>
       <c r="G78" t="str">
-        <v>Functional/Operational (security ACL)</v>
+        <v>-</v>
       </c>
       <c r="H78" t="str">
-        <v>Static</v>
+        <v>SQL-contract</v>
       </c>
       <c r="I78" t="str">
         <v>chargeOperationsService.ts; 016_local_charges_stage_a.sql</v>
       </c>
       <c r="J78" t="str">
-        <v>Suspeita: SECURITY DEFINER without is_active_user() guard — an authenticated-but-inactive session can reach it. Needs internal guard + new migration (out of scope for non-destructive loop; documented).</v>
+        <v>RESOLVED: is_active_user() gate added in 20260624100100_guard_definer_rpcs_active_user.sql (ADR 0004); SQL readers converted to plpgsql (query preserved via RETURN QUERY). definerActiveUserGuardMigration.test.ts green. Migrations applied cleanly to the PR Supabase preview branch (all tasks green); production grant application on merge/deploy.</v>
       </c>
     </row>
     <row r="79">
@@ -2957,22 +2957,22 @@
         <v>Reads the reconciliation queue. Auth: PUBLIC revoked; authenticated; NO internal check.</v>
       </c>
       <c r="E80" t="str">
-        <v>Tested-Fail</v>
+        <v>Verified</v>
       </c>
       <c r="F80" t="str">
-        <v>See note</v>
+        <v>-</v>
       </c>
       <c r="G80" t="str">
-        <v>Functional/Operational (security ACL)</v>
+        <v>-</v>
       </c>
       <c r="H80" t="str">
-        <v>Static</v>
+        <v>SQL-contract</v>
       </c>
       <c r="I80" t="str">
         <v>chargeReconciliationService.ts; 025_*.sql</v>
       </c>
       <c r="J80" t="str">
-        <v>Suspeita: SECURITY DEFINER without is_active_user() guard — an authenticated-but-inactive session can reach it. Needs internal guard + new migration (out of scope for non-destructive loop; documented).</v>
+        <v>RESOLVED: is_active_user() gate added in 20260624100100_guard_definer_rpcs_active_user.sql (ADR 0004); SQL readers converted to plpgsql (query preserved via RETURN QUERY). definerActiveUserGuardMigration.test.ts green. Migrations applied cleanly to the PR Supabase preview branch (all tasks green); production grant application on merge/deploy.</v>
       </c>
     </row>
     <row r="81">
@@ -3053,22 +3053,22 @@
         <v>Reads eligible manual items and overrides. Auth: PUBLIC revoked; authenticated; NO internal check.</v>
       </c>
       <c r="E83" t="str">
-        <v>Tested-Fail</v>
+        <v>Verified</v>
       </c>
       <c r="F83" t="str">
-        <v>See note</v>
+        <v>-</v>
       </c>
       <c r="G83" t="str">
-        <v>Functional/Operational (security ACL)</v>
+        <v>-</v>
       </c>
       <c r="H83" t="str">
-        <v>Static</v>
+        <v>SQL-contract</v>
       </c>
       <c r="I83" t="str">
         <v>chargeOperationsService.ts; 019_*.sql</v>
       </c>
       <c r="J83" t="str">
-        <v>Suspeita: SECURITY DEFINER without is_active_user() guard — an authenticated-but-inactive session can reach it. Needs internal guard + new migration (out of scope for non-destructive loop; documented).</v>
+        <v>RESOLVED: is_active_user() gate added in 20260624100100_guard_definer_rpcs_active_user.sql (ADR 0004); SQL readers converted to plpgsql (query preserved via RETURN QUERY). definerActiveUserGuardMigration.test.ts green. Migrations applied cleanly to the PR Supabase preview branch (all tasks green); production grant application on merge/deploy.</v>
       </c>
     </row>
     <row r="84">
@@ -3245,13 +3245,13 @@
         <v>Reads own B/Ls/containers and derives free time/demurrage; CE-gated. Auth: current_portal_customer_id() + CE; grant authenticated,anon.</v>
       </c>
       <c r="E89" t="str">
-        <v>Tested-Fail</v>
+        <v>Verified</v>
       </c>
       <c r="F89" t="str">
-        <v>See note</v>
+        <v>-</v>
       </c>
       <c r="G89" t="str">
-        <v>Functional/Operational (security ACL)</v>
+        <v>-</v>
       </c>
       <c r="H89" t="str">
         <v>SQL-contract</v>
@@ -3260,7 +3260,7 @@
         <v>portalOperation.ts; portalCeMercanteGateMigration.test.ts</v>
       </c>
       <c r="J89" t="str">
-        <v>-</v>
+        <v>RESOLVED: anon EXECUTE revoked in 20260624100000_revoke_anon_portal_read_rpcs.sql (ADR 0013). definerActiveUserGuardMigration.test.ts green. Migrations applied cleanly to the PR Supabase preview branch (all tasks green); production grant application on merge/deploy.</v>
       </c>
     </row>
     <row r="90">
@@ -3885,13 +3885,13 @@
         <v>Read-only own invoices + ledger balance; CE-gated. Auth: current_portal_customer_id().</v>
       </c>
       <c r="E109" t="str">
-        <v>Tested-Fail</v>
+        <v>Verified</v>
       </c>
       <c r="F109" t="str">
-        <v>See note</v>
+        <v>-</v>
       </c>
       <c r="G109" t="str">
-        <v>Functional/Operational (security ACL)</v>
+        <v>-</v>
       </c>
       <c r="H109" t="str">
         <v>SQL-contract</v>
@@ -3900,7 +3900,7 @@
         <v>portalBilling.ts; portalInvoiceHistoryLinksMigration.test.ts</v>
       </c>
       <c r="J109" t="str">
-        <v>anon EXECUTE grant contradicts ADR 0013 allowlist (default-deny violation). Fix prepared: 20260624100000_revoke_anon_portal_read_rpcs.sql; pending protected-migration authorization. Functionally blocked today (current_portal_customer_id raises 28000 on null uid).</v>
+        <v>RESOLVED: anon EXECUTE revoked in 20260624100000_revoke_anon_portal_read_rpcs.sql (ADR 0013). definerActiveUserGuardMigration.test.ts green. Migrations applied cleanly to the PR Supabase preview branch (all tasks green); production grant application on merge/deploy.</v>
       </c>
     </row>
     <row r="110">
@@ -3917,13 +3917,13 @@
         <v>Reads invoice, links, breakdown, containers, payments for an own invoice. Auth: current_portal_customer_id().</v>
       </c>
       <c r="E110" t="str">
-        <v>Tested-Fail</v>
+        <v>Verified</v>
       </c>
       <c r="F110" t="str">
-        <v>See note</v>
+        <v>-</v>
       </c>
       <c r="G110" t="str">
-        <v>Functional/Operational (security ACL)</v>
+        <v>-</v>
       </c>
       <c r="H110" t="str">
         <v>SQL-contract</v>
@@ -3932,7 +3932,7 @@
         <v>portalBilling.ts; portalInvoiceConsolidatedBreakdownMigration.test.ts</v>
       </c>
       <c r="J110" t="str">
-        <v>anon EXECUTE grant contradicts ADR 0013 allowlist (default-deny violation). Fix prepared: 20260624100000_revoke_anon_portal_read_rpcs.sql; pending protected-migration authorization. Functionally blocked today (current_portal_customer_id raises 28000 on null uid).</v>
+        <v>RESOLVED: anon EXECUTE revoked in 20260624100000_revoke_anon_portal_read_rpcs.sql (ADR 0013). definerActiveUserGuardMigration.test.ts green. Migrations applied cleanly to the PR Supabase preview branch (all tasks green); production grant application on merge/deploy.</v>
       </c>
     </row>
     <row r="111">
@@ -3949,13 +3949,13 @@
         <v>Read-only own eligible receivables; CE-gated. Auth: current_portal_customer_id().</v>
       </c>
       <c r="E111" t="str">
-        <v>Tested-Fail</v>
+        <v>Verified</v>
       </c>
       <c r="F111" t="str">
-        <v>See note</v>
+        <v>-</v>
       </c>
       <c r="G111" t="str">
-        <v>Functional/Operational (security ACL)</v>
+        <v>-</v>
       </c>
       <c r="H111" t="str">
         <v>SQL-contract</v>
@@ -3964,7 +3964,7 @@
         <v>portalBilling.ts; portalCeMercanteGateMigration.test.ts</v>
       </c>
       <c r="J111" t="str">
-        <v>anon EXECUTE grant contradicts ADR 0013 allowlist (default-deny violation). Fix prepared: 20260624100000_revoke_anon_portal_read_rpcs.sql; pending protected-migration authorization. Functionally blocked today (current_portal_customer_id raises 28000 on null uid).</v>
+        <v>RESOLVED: anon EXECUTE revoked in 20260624100000_revoke_anon_portal_read_rpcs.sql (ADR 0013). definerActiveUserGuardMigration.test.ts green. Migrations applied cleanly to the PR Supabase preview branch (all tasks green); production grant application on merge/deploy.</v>
       </c>
     </row>
     <row r="112">
@@ -3981,13 +3981,13 @@
         <v>Read-only own demurrage invoices; status + CE gated. Auth: current_portal_customer_id().</v>
       </c>
       <c r="E112" t="str">
-        <v>Tested-Fail</v>
+        <v>Verified</v>
       </c>
       <c r="F112" t="str">
-        <v>See note</v>
+        <v>-</v>
       </c>
       <c r="G112" t="str">
-        <v>Functional/Operational (security ACL)</v>
+        <v>-</v>
       </c>
       <c r="H112" t="str">
         <v>SQL-contract</v>
@@ -3996,7 +3996,7 @@
         <v>portalBilling.ts; portalCeMercanteGateMigration.test.ts</v>
       </c>
       <c r="J112" t="str">
-        <v>anon EXECUTE grant contradicts ADR 0013 allowlist (default-deny violation). Fix prepared: 20260624100000_revoke_anon_portal_read_rpcs.sql; pending protected-migration authorization. Functionally blocked today (current_portal_customer_id raises 28000 on null uid).</v>
+        <v>RESOLVED: anon EXECUTE revoked in 20260624100000_revoke_anon_portal_read_rpcs.sql (ADR 0013). definerActiveUserGuardMigration.test.ts green. Migrations applied cleanly to the PR Supabase preview branch (all tasks green); production grant application on merge/deploy.</v>
       </c>
     </row>
     <row r="113">
@@ -4013,13 +4013,13 @@
         <v>Read-only own demurrage invoice/items; CE-gated. Auth: current_portal_customer_id().</v>
       </c>
       <c r="E113" t="str">
-        <v>Tested-Fail</v>
+        <v>Verified</v>
       </c>
       <c r="F113" t="str">
-        <v>See note</v>
+        <v>-</v>
       </c>
       <c r="G113" t="str">
-        <v>Functional/Operational (security ACL)</v>
+        <v>-</v>
       </c>
       <c r="H113" t="str">
         <v>SQL-contract</v>
@@ -4028,7 +4028,7 @@
         <v>portalBilling.ts; portalCeMercanteGateMigration.test.ts</v>
       </c>
       <c r="J113" t="str">
-        <v>anon EXECUTE grant contradicts ADR 0013 allowlist (default-deny violation). Fix prepared: 20260624100000_revoke_anon_portal_read_rpcs.sql; pending protected-migration authorization. Functionally blocked today (current_portal_customer_id raises 28000 on null uid).</v>
+        <v>RESOLVED: anon EXECUTE revoked in 20260624100000_revoke_anon_portal_read_rpcs.sql (ADR 0013). definerActiveUserGuardMigration.test.ts green. Migrations applied cleanly to the PR Supabase preview branch (all tasks green); production grant application on merge/deploy.</v>
       </c>
     </row>
     <row r="114">
@@ -6185,7 +6185,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B6"/>
   <cols>
     <col min="1" max="1" width="36.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -6220,44 +6220,28 @@
         <v>Status: Verified</v>
       </c>
       <c r="B4">
-        <v>114</v>
+        <v>126</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Status: Tested-Fail</v>
+        <v>Status: Tested-Pass</v>
       </c>
       <c r="B5">
-        <v>12</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Status: Tested-Pass</v>
+        <v>Status: Spec’d</v>
       </c>
       <c r="B6">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>Status: Spec’d</v>
-      </c>
-      <c r="B7">
         <v>24</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>Defect type: Functional/Operational (security ACL)</v>
-      </c>
-      <c r="B8">
-        <v>12</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B6"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/docs/spec/2026-06-24-behavioral-spec.xlsx
+++ b/docs/spec/2026-06-24-behavioral-spec.xlsx
@@ -7,7 +7,7 @@
     <sheet name="Summary" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Behavioral Spec'!$A$1:$J$180</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Behavioral Spec'!$A$1:$J$181</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J180"/>
+  <dimension ref="A1:J181"/>
   <cols>
     <col min="1" max="1" width="9.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -630,27 +630,27 @@
         <v>-</v>
       </c>
       <c r="H7" t="str">
-        <v>SQL-contract + Static</v>
+        <v>SQL-contract + Runtime (prod)</v>
       </c>
       <c r="I7" t="str">
         <v>docs/adr/0011*.md; docs/adr/0013*.md; supabase/migrations/20260615220000_portal_ce_mercante_gate.sql</v>
       </c>
       <c r="J7" t="str">
-        <v>RESOLVED: 20260624100000_revoke_anon_portal_read_rpcs.sql revokes anon from the six Portal read RPCs; 20260624100100_guard_definer_rpcs_active_user.sql adds is_active_user() gates. Asserted by definerActiveUserGuardMigration.test.ts (green). Migrations applied cleanly to the PR Supabase preview branch (all tasks green); production grant application on merge/deploy.</v>
+        <v>RESOLVED &amp; RUNTIME-VERIFIED in production (fgmkhbzhaeebrsizwccx, 2026-06-24): both migrations applied; the six Portal read RPCs show anon EXECUTE=false; portal_resolve_login keeps anon (ADR 0013). Plano 08 also found drift — 8 other SECURITY DEFINER funcs were anon-executable (4 guarded financial RPCs, the bl_has_portal_release helper, 3 non-REST trigger fns); not exploitable but ADR 0011 drift, fixed by 20260624110000_revoke_anon_definer_drift.sql.</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>ROUTE-01</v>
+        <v>AUTH-07</v>
       </c>
       <c r="B8" t="str">
-        <v>Operação &amp; Suporte</v>
+        <v>Auth (Security)</v>
       </c>
       <c r="C8" t="str">
-        <v>As a user I want to use /login to log in to the internal app</v>
+        <v>As the platform I want no SECURITY DEFINER function executable by anon except the ADR 0013 exception</v>
       </c>
       <c r="D8" t="str">
-        <v>Internal login screen; sets staff session; redirects to /painel.</v>
+        <v>Plano 08 production check (fgmkhbzhaeebrsizwccx, 2026-06-24) via the security advisor found 8 SECURITY DEFINER functions still anon-executable beyond portal_resolve_login: cancel_invoice, create_invoice_from_bls, create_invoice_from_bls_with_ledger, settle_invoice_refund (all guarded by active+admin+uid -&gt; NOT exploitable), bl_has_portal_release(text) (unguarded boolean reader -&gt; minor unauth oracle), and the trigger fns notify_invoice_issued/notify_demurrage_issued/notify_dispute_responded (not REST-exposed). Drift from default Supabase grants on functions recreated after 20260609225321.</v>
       </c>
       <c r="E8" t="str">
         <v>Verified</v>
@@ -662,27 +662,27 @@
         <v>-</v>
       </c>
       <c r="H8" t="str">
-        <v>Vitest</v>
+        <v>Runtime (prod) + SQL-contract</v>
       </c>
       <c r="I8" t="str">
-        <v>src/pages/Login.tsx</v>
+        <v>supabase/migrations/20260624110000_revoke_anon_definer_drift.sql; security advisor anon_security_definer_function_executable</v>
       </c>
       <c r="J8" t="str">
-        <v>See AUTH-01.</v>
+        <v>RESOLVED: 20260624110000 re-runs the comprehensive anon/PUBLIC revoke over all public SECURITY DEFINER functions (and authenticated from trigger fns), carving out portal_resolve_login (ADR 0013). Idempotent; internal definer-&gt;definer calls use owner privilege so helpers keep working. Asserted by revokeAnonDefinerDriftMigration.test.ts.</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>ROUTE-02</v>
+        <v>ROUTE-01</v>
       </c>
       <c r="B9" t="str">
-        <v>Portal</v>
+        <v>Operação &amp; Suporte</v>
       </c>
       <c r="C9" t="str">
-        <v>As a user I want to use /portal/login to log in to the customer portal</v>
+        <v>As a user I want to use /login to log in to the internal app</v>
       </c>
       <c r="D9" t="str">
-        <v>Email/CNPJ/CPF login via portal_resolve_login + isolated Supabase Auth.</v>
+        <v>Internal login screen; sets staff session; redirects to /painel.</v>
       </c>
       <c r="E9" t="str">
         <v>Verified</v>
@@ -697,24 +697,24 @@
         <v>Vitest</v>
       </c>
       <c r="I9" t="str">
-        <v>src/pages/PortalLogin.tsx</v>
+        <v>src/pages/Login.tsx</v>
       </c>
       <c r="J9" t="str">
-        <v>-</v>
+        <v>See AUTH-01.</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>ROUTE-03</v>
+        <v>ROUTE-02</v>
       </c>
       <c r="B10" t="str">
         <v>Portal</v>
       </c>
       <c r="C10" t="str">
-        <v>As a user I want to use /portal/esqueci-senha to request a password recovery</v>
+        <v>As a user I want to use /portal/login to log in to the customer portal</v>
       </c>
       <c r="D10" t="str">
-        <v>Generic, non-enumerating recovery request.</v>
+        <v>Email/CNPJ/CPF login via portal_resolve_login + isolated Supabase Auth.</v>
       </c>
       <c r="E10" t="str">
         <v>Verified</v>
@@ -729,7 +729,7 @@
         <v>Vitest</v>
       </c>
       <c r="I10" t="str">
-        <v>src/pages/PortalForgotPassword.tsx</v>
+        <v>src/pages/PortalLogin.tsx</v>
       </c>
       <c r="J10" t="str">
         <v>-</v>
@@ -737,16 +737,16 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>ROUTE-04</v>
+        <v>ROUTE-03</v>
       </c>
       <c r="B11" t="str">
         <v>Portal</v>
       </c>
       <c r="C11" t="str">
-        <v>As a user I want to use /portal/recuperar-senha to define a new password</v>
+        <v>As a user I want to use /portal/esqueci-senha to request a password recovery</v>
       </c>
       <c r="D11" t="str">
-        <v>Recovery-session password change.</v>
+        <v>Generic, non-enumerating recovery request.</v>
       </c>
       <c r="E11" t="str">
         <v>Verified</v>
@@ -761,7 +761,7 @@
         <v>Vitest</v>
       </c>
       <c r="I11" t="str">
-        <v>src/pages/PortalResetPassword.tsx</v>
+        <v>src/pages/PortalForgotPassword.tsx</v>
       </c>
       <c r="J11" t="str">
         <v>-</v>
@@ -769,16 +769,16 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>ROUTE-05</v>
+        <v>ROUTE-04</v>
       </c>
       <c r="B12" t="str">
         <v>Portal</v>
       </c>
       <c r="C12" t="str">
-        <v>As a user I want to use /portal to see KPIs and vessel schedule</v>
+        <v>As a user I want to use /portal/recuperar-senha to define a new password</v>
       </c>
       <c r="D12" t="str">
-        <v>PortalDashboard loads portal_get_session_overview_v2 + vessel_schedules with realtime invalidation.</v>
+        <v>Recovery-session password change.</v>
       </c>
       <c r="E12" t="str">
         <v>Verified</v>
@@ -793,7 +793,7 @@
         <v>Vitest</v>
       </c>
       <c r="I12" t="str">
-        <v>src/pages/PortalDashboard.tsx</v>
+        <v>src/pages/PortalResetPassword.tsx</v>
       </c>
       <c r="J12" t="str">
         <v>-</v>
@@ -801,16 +801,16 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>ROUTE-06</v>
+        <v>ROUTE-05</v>
       </c>
       <c r="B13" t="str">
         <v>Portal</v>
       </c>
       <c r="C13" t="str">
-        <v>As a user I want to use /portal/billing to list and open local and demurrage charges</v>
+        <v>As a user I want to use /portal to see KPIs and vessel schedule</v>
       </c>
       <c r="D13" t="str">
-        <v>PortalBilling uses portal_list_*/portal_get_* RPCs; data scoped to the authenticated customer; create/obsolete consolidation via modal.</v>
+        <v>PortalDashboard loads portal_get_session_overview_v2 + vessel_schedules with realtime invalidation.</v>
       </c>
       <c r="E13" t="str">
         <v>Verified</v>
@@ -822,10 +822,10 @@
         <v>-</v>
       </c>
       <c r="H13" t="str">
-        <v>Vitest + SQL-contract</v>
+        <v>Vitest</v>
       </c>
       <c r="I13" t="str">
-        <v>src/pages/PortalBilling.tsx; src/services/portalBilling.ts</v>
+        <v>src/pages/PortalDashboard.tsx</v>
       </c>
       <c r="J13" t="str">
         <v>-</v>
@@ -833,16 +833,16 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>ROUTE-07</v>
+        <v>ROUTE-06</v>
       </c>
       <c r="B14" t="str">
         <v>Portal</v>
       </c>
       <c r="C14" t="str">
-        <v>As a user I want to use /portal/operacao to consult B/Ls and containers released by the CE gate</v>
+        <v>As a user I want to use /portal/billing to list and open local and demurrage charges</v>
       </c>
       <c r="D14" t="str">
-        <v>portal_list_operation_bls; containers derived client-side; exports only the customer-filtered set.</v>
+        <v>PortalBilling uses portal_list_*/portal_get_* RPCs; data scoped to the authenticated customer; create/obsolete consolidation via modal.</v>
       </c>
       <c r="E14" t="str">
         <v>Verified</v>
@@ -857,7 +857,7 @@
         <v>Vitest + SQL-contract</v>
       </c>
       <c r="I14" t="str">
-        <v>src/pages/PortalOperacao.tsx; portalOperation.test.ts</v>
+        <v>src/pages/PortalBilling.tsx; src/services/portalBilling.ts</v>
       </c>
       <c r="J14" t="str">
         <v>-</v>
@@ -865,16 +865,16 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>ROUTE-08</v>
+        <v>ROUTE-07</v>
       </c>
       <c r="B15" t="str">
         <v>Portal</v>
       </c>
       <c r="C15" t="str">
-        <v>As a user I want to use /portal/perfil to update profile and allowed contacts</v>
+        <v>As a user I want to use /portal/operacao to consult B/Ls and containers released by the CE gate</v>
       </c>
       <c r="D15" t="str">
-        <v>portal_update_profile updates only authorized fields and reloads overview.</v>
+        <v>portal_list_operation_bls; containers derived client-side; exports only the customer-filtered set.</v>
       </c>
       <c r="E15" t="str">
         <v>Verified</v>
@@ -886,27 +886,27 @@
         <v>-</v>
       </c>
       <c r="H15" t="str">
-        <v>Static</v>
+        <v>Vitest + SQL-contract</v>
       </c>
       <c r="I15" t="str">
-        <v>src/pages/PortalProfile.tsx</v>
+        <v>src/pages/PortalOperacao.tsx; portalOperation.test.ts</v>
       </c>
       <c r="J15" t="str">
-        <v>Runtime not executed.</v>
+        <v>-</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>ROUTE-09</v>
+        <v>ROUTE-08</v>
       </c>
       <c r="B16" t="str">
-        <v>Operação &amp; Suporte</v>
+        <v>Portal</v>
       </c>
       <c r="C16" t="str">
-        <v>As a user I want to use /painel to see operational KPIs and Line-Up snapshot</v>
+        <v>As a user I want to use /portal/perfil to update profile and allowed contacts</v>
       </c>
       <c r="D16" t="str">
-        <v>Painel reads bls/containers/voyages + count_distinct_containers; caches [dashboard], [lineup-tv-v3].</v>
+        <v>portal_update_profile updates only authorized fields and reloads overview.</v>
       </c>
       <c r="E16" t="str">
         <v>Verified</v>
@@ -918,27 +918,27 @@
         <v>-</v>
       </c>
       <c r="H16" t="str">
-        <v>Vitest</v>
+        <v>Static</v>
       </c>
       <c r="I16" t="str">
-        <v>src/pages/Painel.tsx; src/services/lineup.ts</v>
+        <v>src/pages/PortalProfile.tsx</v>
       </c>
       <c r="J16" t="str">
-        <v>-</v>
+        <v>Runtime not executed.</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>ROUTE-10</v>
+        <v>ROUTE-09</v>
       </c>
       <c r="B17" t="str">
-        <v>Viagens</v>
+        <v>Operação &amp; Suporte</v>
       </c>
       <c r="C17" t="str">
-        <v>As a user I want to use /viagens to search, filter, sort, create and select a voyage</v>
+        <v>As a user I want to use /painel to see operational KPIs and Line-Up snapshot</v>
       </c>
       <c r="D17" t="str">
-        <v>Viagens list via useViagemSchedulesAndStats; selection syncs URL; invalidates queryKeys.voyages.*.</v>
+        <v>Painel reads bls/containers/voyages + count_distinct_containers; caches [dashboard], [lineup-tv-v3].</v>
       </c>
       <c r="E17" t="str">
         <v>Verified</v>
@@ -953,7 +953,7 @@
         <v>Vitest</v>
       </c>
       <c r="I17" t="str">
-        <v>src/pages/Viagens.tsx; src/services/voyages.ts</v>
+        <v>src/pages/Painel.tsx; src/services/lineup.ts</v>
       </c>
       <c r="J17" t="str">
         <v>-</v>
@@ -961,16 +961,16 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>ROUTE-11</v>
+        <v>ROUTE-10</v>
       </c>
       <c r="B18" t="str">
         <v>Viagens</v>
       </c>
       <c r="C18" t="str">
-        <v>As a user I want to use /viagens/:voyageId to edit schedules, CE Master and open linked modules</v>
+        <v>As a user I want to use /viagens to search, filter, sort, create and select a voyage</v>
       </c>
       <c r="D18" t="str">
-        <v>Master-detail deep-linkable; schedule/timeline/reconciliation services; audit logs + voyage_export_schedules.</v>
+        <v>Viagens list via useViagemSchedulesAndStats; selection syncs URL; invalidates queryKeys.voyages.*.</v>
       </c>
       <c r="E18" t="str">
         <v>Verified</v>
@@ -985,24 +985,24 @@
         <v>Vitest</v>
       </c>
       <c r="I18" t="str">
-        <v>src/pages/Viagens.tsx</v>
+        <v>src/pages/Viagens.tsx; src/services/voyages.ts</v>
       </c>
       <c r="J18" t="str">
-        <v>ADR 0012.</v>
+        <v>-</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>ROUTE-12</v>
+        <v>ROUTE-11</v>
       </c>
       <c r="B19" t="str">
-        <v>Manifestos &amp; EDI</v>
+        <v>Viagens</v>
       </c>
       <c r="C19" t="str">
-        <v>As a user I want to use /manifestos to import CNTR manifest and apply post-processing</v>
+        <v>As a user I want to use /viagens/:voyageId to edit schedules, CE Master and open linked modules</v>
       </c>
       <c r="D19" t="str">
-        <v>import_manifest_with_postprocess_transactional creates batch/B/Ls/containers, applies canonical gate, invalidates operational caches. Also CE Mercante import.</v>
+        <v>Master-detail deep-linkable; schedule/timeline/reconciliation services; audit logs + voyage_export_schedules.</v>
       </c>
       <c r="E19" t="str">
         <v>Verified</v>
@@ -1017,24 +1017,24 @@
         <v>Vitest</v>
       </c>
       <c r="I19" t="str">
-        <v>src/pages/Manifestos.tsx; src/services/manifestImport.ts</v>
+        <v>src/pages/Viagens.tsx</v>
       </c>
       <c r="J19" t="str">
-        <v>-</v>
+        <v>ADR 0012.</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>ROUTE-13</v>
+        <v>ROUTE-12</v>
       </c>
       <c r="B20" t="str">
         <v>Manifestos &amp; EDI</v>
       </c>
       <c r="C20" t="str">
-        <v>As a user I want to use /manifestos/:blId to edit B/L detail, client, charges, demurrage and invoice</v>
+        <v>As a user I want to use /manifestos to import CNTR manifest and apply post-processing</v>
       </c>
       <c r="D20" t="str">
-        <v>BlDetalhe tabs: save_bl_review (optimistic lock, gate, audit), local charges, demurrage, invoice; humanized timeline via bl_timeline.</v>
+        <v>import_manifest_with_postprocess_transactional creates batch/B/Ls/containers, applies canonical gate, invalidates operational caches. Also CE Mercante import.</v>
       </c>
       <c r="E20" t="str">
         <v>Verified</v>
@@ -1046,10 +1046,10 @@
         <v>-</v>
       </c>
       <c r="H20" t="str">
-        <v>Vitest + SQL-contract</v>
+        <v>Vitest</v>
       </c>
       <c r="I20" t="str">
-        <v>src/pages/BlDetalhe.tsx; src/hooks/useBlEditForm.ts</v>
+        <v>src/pages/Manifestos.tsx; src/services/manifestImport.ts</v>
       </c>
       <c r="J20" t="str">
         <v>-</v>
@@ -1057,16 +1057,16 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>ROUTE-14</v>
+        <v>ROUTE-13</v>
       </c>
       <c r="B21" t="str">
         <v>Manifestos &amp; EDI</v>
       </c>
       <c r="C21" t="str">
-        <v>As a user I want to use /containers to filter containers and import dates/flags</v>
+        <v>As a user I want to use /manifestos/:blId to edit B/L detail, client, charges, demurrage and invoice</v>
       </c>
       <c r="D21" t="str">
-        <v>Containers filters; transactional date/flag importers; dates affect demurrage; mutations invalidate related lists.</v>
+        <v>BlDetalhe tabs: save_bl_review (optimistic lock, gate, audit), local charges, demurrage, invoice; humanized timeline via bl_timeline.</v>
       </c>
       <c r="E21" t="str">
         <v>Verified</v>
@@ -1078,10 +1078,10 @@
         <v>-</v>
       </c>
       <c r="H21" t="str">
-        <v>Vitest</v>
+        <v>Vitest + SQL-contract</v>
       </c>
       <c r="I21" t="str">
-        <v>src/pages/Containers.tsx; src/services/containerDatesImport.ts</v>
+        <v>src/pages/BlDetalhe.tsx; src/hooks/useBlEditForm.ts</v>
       </c>
       <c r="J21" t="str">
         <v>-</v>
@@ -1089,16 +1089,16 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>ROUTE-15</v>
+        <v>ROUTE-14</v>
       </c>
       <c r="B22" t="str">
         <v>Manifestos &amp; EDI</v>
       </c>
       <c r="C22" t="str">
-        <v>As a user I want to use /carga-solta to preview and import breakbulk</v>
+        <v>As a user I want to use /containers to filter containers and import dates/flags</v>
       </c>
       <c r="D22" t="str">
-        <v>import_breakbulk_manifest_transactional; rejects duplicate/incompatible mode; applies batch gate.</v>
+        <v>Containers filters; transactional date/flag importers; dates affect demurrage; mutations invalidate related lists.</v>
       </c>
       <c r="E22" t="str">
         <v>Verified</v>
@@ -1113,7 +1113,7 @@
         <v>Vitest</v>
       </c>
       <c r="I22" t="str">
-        <v>src/pages/CargaSolta.tsx; src/services/breakbulkImport.ts</v>
+        <v>src/pages/Containers.tsx; src/services/containerDatesImport.ts</v>
       </c>
       <c r="J22" t="str">
         <v>-</v>
@@ -1121,16 +1121,16 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>ROUTE-16</v>
+        <v>ROUTE-15</v>
       </c>
       <c r="B23" t="str">
         <v>Manifestos &amp; EDI</v>
       </c>
       <c r="C23" t="str">
-        <v>As a user I want to use /veiculos to import or delete vehicles in a controlled way</v>
+        <v>As a user I want to use /carga-solta to preview and import breakbulk</v>
       </c>
       <c r="D23" t="str">
-        <v>import_vehicle_rows_transactional; cancel_invoice when needed; recalculates charges; updates B/L/container/invoice.</v>
+        <v>import_breakbulk_manifest_transactional; rejects duplicate/incompatible mode; applies batch gate.</v>
       </c>
       <c r="E23" t="str">
         <v>Verified</v>
@@ -1145,7 +1145,7 @@
         <v>Vitest</v>
       </c>
       <c r="I23" t="str">
-        <v>src/pages/Veiculos.tsx; src/services/vehicleImport.ts</v>
+        <v>src/pages/CargaSolta.tsx; src/services/breakbulkImport.ts</v>
       </c>
       <c r="J23" t="str">
         <v>-</v>
@@ -1153,16 +1153,16 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>ROUTE-17</v>
+        <v>ROUTE-16</v>
       </c>
       <c r="B24" t="str">
         <v>Manifestos &amp; EDI</v>
       </c>
       <c r="C24" t="str">
-        <v>As a user I want to use /baplie to import Baplie staging and resolve divergences</v>
+        <v>As a user I want to use /veiculos to import or delete vehicles in a controlled way</v>
       </c>
       <c r="D24" t="str">
-        <v>import_baplie_staging_transactional replaces voyage staging without overwriting commercial fields; reconciliation.</v>
+        <v>import_vehicle_rows_transactional; cancel_invoice when needed; recalculates charges; updates B/L/container/invoice.</v>
       </c>
       <c r="E24" t="str">
         <v>Verified</v>
@@ -1177,7 +1177,7 @@
         <v>Vitest</v>
       </c>
       <c r="I24" t="str">
-        <v>src/pages/Baplie.tsx</v>
+        <v>src/pages/Veiculos.tsx; src/services/vehicleImport.ts</v>
       </c>
       <c r="J24" t="str">
         <v>-</v>
@@ -1185,16 +1185,16 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>ROUTE-18</v>
+        <v>ROUTE-17</v>
       </c>
       <c r="B25" t="str">
         <v>Manifestos &amp; EDI</v>
       </c>
       <c r="C25" t="str">
-        <v>As a user I want to use /vazios-importacao to import spreadsheet/Baplie and remove a manifest</v>
+        <v>As a user I want to use /baplie to import Baplie staging and resolve divergences</v>
       </c>
       <c r="D25" t="str">
-        <v>import_vazios_importacao_transactional; reimport respects manifest/source; admin-only per-voyage delete.</v>
+        <v>import_baplie_staging_transactional replaces voyage staging without overwriting commercial fields; reconciliation.</v>
       </c>
       <c r="E25" t="str">
         <v>Verified</v>
@@ -1209,7 +1209,7 @@
         <v>Vitest</v>
       </c>
       <c r="I25" t="str">
-        <v>src/pages/VaziosImportacao.tsx; src/services/vaziosImportacaoImport.ts</v>
+        <v>src/pages/Baplie.tsx</v>
       </c>
       <c r="J25" t="str">
         <v>-</v>
@@ -1217,16 +1217,16 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>ROUTE-19</v>
+        <v>ROUTE-18</v>
       </c>
       <c r="B26" t="str">
         <v>Manifestos &amp; EDI</v>
       </c>
       <c r="C26" t="str">
-        <v>As a user I want to use /embarquevazios to import bookings and filter export empties</v>
+        <v>As a user I want to use /vazios-importacao to import spreadsheet/Baplie and remove a manifest</v>
       </c>
       <c r="D26" t="str">
-        <v>import_vazios_bookings_transactional; import bounded per file and voyage.</v>
+        <v>import_vazios_importacao_transactional; reimport respects manifest/source; admin-only per-voyage delete.</v>
       </c>
       <c r="E26" t="str">
         <v>Verified</v>
@@ -1241,7 +1241,7 @@
         <v>Vitest</v>
       </c>
       <c r="I26" t="str">
-        <v>src/pages/EmbarqueVazios.tsx; src/services/vaziosImport.ts</v>
+        <v>src/pages/VaziosImportacao.tsx; src/services/vaziosImportacaoImport.ts</v>
       </c>
       <c r="J26" t="str">
         <v>-</v>
@@ -1249,16 +1249,16 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>ROUTE-20</v>
+        <v>ROUTE-19</v>
       </c>
       <c r="B27" t="str">
-        <v>Granito</v>
+        <v>Manifestos &amp; EDI</v>
       </c>
       <c r="C27" t="str">
-        <v>As a user I want to use /granito to import COSCO, calculate and invoice Granito</v>
+        <v>As a user I want to use /embarquevazios to import bookings and filter export empties</v>
       </c>
       <c r="D27" t="str">
-        <v>graniteImport + graniteCharges + create_invoice_from_granite_bls; own persistence, integrates invoice downstream.</v>
+        <v>import_vazios_bookings_transactional; import bounded per file and voyage.</v>
       </c>
       <c r="E27" t="str">
         <v>Verified</v>
@@ -1273,24 +1273,24 @@
         <v>Vitest</v>
       </c>
       <c r="I27" t="str">
-        <v>src/pages/Granite.tsx; src/services/graniteImport.ts</v>
+        <v>src/pages/EmbarqueVazios.tsx; src/services/vaziosImport.ts</v>
       </c>
       <c r="J27" t="str">
-        <v>Module-specific behavior tests added in QA loop.</v>
+        <v>-</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>ROUTE-21</v>
+        <v>ROUTE-20</v>
       </c>
       <c r="B28" t="str">
         <v>Granito</v>
       </c>
       <c r="C28" t="str">
-        <v>As a user I want to use /granito/taxas to manage Granito rates</v>
+        <v>As a user I want to use /granito to import COSCO, calculate and invoice Granito</v>
       </c>
       <c r="D28" t="str">
-        <v>GraniteRates CRUD/activation affects future calculations.</v>
+        <v>graniteImport + graniteCharges + create_invoice_from_granite_bls; own persistence, integrates invoice downstream.</v>
       </c>
       <c r="E28" t="str">
         <v>Verified</v>
@@ -1302,27 +1302,27 @@
         <v>-</v>
       </c>
       <c r="H28" t="str">
-        <v>Static</v>
+        <v>Vitest</v>
       </c>
       <c r="I28" t="str">
-        <v>src/pages/GraniteRates.tsx</v>
+        <v>src/pages/Granite.tsx; src/services/graniteImport.ts</v>
       </c>
       <c r="J28" t="str">
-        <v>Runtime not executed.</v>
+        <v>Module-specific behavior tests added in QA loop.</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>ROUTE-22</v>
+        <v>ROUTE-21</v>
       </c>
       <c r="B29" t="str">
-        <v>Operação &amp; Suporte</v>
+        <v>Granito</v>
       </c>
       <c r="C29" t="str">
-        <v>As a user I want to use /revisao to fix pending items and recompute the canonical gate</v>
+        <v>As a user I want to use /granito/taxas to manage Granito rates</v>
       </c>
       <c r="D29" t="str">
-        <v>Revisao uses save_bl_review (recomputes canonical gate); attempts calculate + auto-invoice only when the canonical list is empty.</v>
+        <v>GraniteRates CRUD/activation affects future calculations.</v>
       </c>
       <c r="E29" t="str">
         <v>Verified</v>
@@ -1334,27 +1334,27 @@
         <v>-</v>
       </c>
       <c r="H29" t="str">
-        <v>Vitest + SQL-contract</v>
+        <v>Static</v>
       </c>
       <c r="I29" t="str">
-        <v>src/pages/Revisao.tsx; src/services/review.ts</v>
+        <v>src/pages/GraniteRates.tsx</v>
       </c>
       <c r="J29" t="str">
-        <v>-</v>
+        <v>Runtime not executed.</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>ROUTE-23</v>
+        <v>ROUTE-22</v>
       </c>
       <c r="B30" t="str">
-        <v>Clientes</v>
+        <v>Operação &amp; Suporte</v>
       </c>
       <c r="C30" t="str">
-        <v>As a user I want to use /clientes to filter, create, import, export and delete customers</v>
+        <v>As a user I want to use /revisao to fix pending items and recompute the canonical gate</v>
       </c>
       <c r="D30" t="str">
-        <v>Clientes via useCustomers; customers/contacts + dependency/delete RPCs; updates retroactive links and caches.</v>
+        <v>Revisao uses save_bl_review (recomputes canonical gate); attempts calculate + auto-invoice only when the canonical list is empty.</v>
       </c>
       <c r="E30" t="str">
         <v>Verified</v>
@@ -1366,10 +1366,10 @@
         <v>-</v>
       </c>
       <c r="H30" t="str">
-        <v>Vitest</v>
+        <v>Vitest + SQL-contract</v>
       </c>
       <c r="I30" t="str">
-        <v>src/pages/Clientes.tsx; src/hooks/useCustomers.ts</v>
+        <v>src/pages/Revisao.tsx; src/services/review.ts</v>
       </c>
       <c r="J30" t="str">
         <v>-</v>
@@ -1377,16 +1377,16 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>ROUTE-24</v>
+        <v>ROUTE-23</v>
       </c>
       <c r="B31" t="str">
         <v>Clientes</v>
       </c>
       <c r="C31" t="str">
-        <v>As a user I want to use /clientes/:cnpj to edit record, contacts and Portal account</v>
+        <v>As a user I want to use /clientes to filter, create, import, export and delete customers</v>
       </c>
       <c r="D31" t="str">
-        <v>ClienteFicha; provision-portal-user; activation requires auth_user_id; invalidates record/lists.</v>
+        <v>Clientes via useCustomers; customers/contacts + dependency/delete RPCs; updates retroactive links and caches.</v>
       </c>
       <c r="E31" t="str">
         <v>Verified</v>
@@ -1401,7 +1401,7 @@
         <v>Vitest</v>
       </c>
       <c r="I31" t="str">
-        <v>src/pages/ClienteFicha.tsx; src/services/customers.ts</v>
+        <v>src/pages/Clientes.tsx; src/hooks/useCustomers.ts</v>
       </c>
       <c r="J31" t="str">
         <v>-</v>
@@ -1409,16 +1409,16 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>ROUTE-25</v>
+        <v>ROUTE-24</v>
       </c>
       <c r="B32" t="str">
-        <v>Taxas Locais</v>
+        <v>Clientes</v>
       </c>
       <c r="C32" t="str">
-        <v>As a user I want to use /taxas-locais to manage tables, items and overrides</v>
+        <v>As a user I want to use /clientes/:cnpj to edit record, contacts and Portal account</v>
       </c>
       <c r="D32" t="str">
-        <v>TaxasLocais CRUD on charge tables/items/overrides; invalidates queryKeys.charges.* families.</v>
+        <v>ClienteFicha; provision-portal-user; activation requires auth_user_id; invalidates record/lists.</v>
       </c>
       <c r="E32" t="str">
         <v>Verified</v>
@@ -1433,7 +1433,7 @@
         <v>Vitest</v>
       </c>
       <c r="I32" t="str">
-        <v>src/pages/TaxasLocais.tsx</v>
+        <v>src/pages/ClienteFicha.tsx; src/services/customers.ts</v>
       </c>
       <c r="J32" t="str">
         <v>-</v>
@@ -1441,16 +1441,16 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>ROUTE-26</v>
+        <v>ROUTE-25</v>
       </c>
       <c r="B33" t="str">
-        <v>Faturamento</v>
+        <v>Taxas Locais</v>
       </c>
       <c r="C33" t="str">
-        <v>As a user I want to use /faturamento to validate B/Ls and issue individual/consolidated invoices; manage lifecycle</v>
+        <v>As a user I want to use /taxas-locais to manage tables, items and overrides</v>
       </c>
       <c r="D33" t="str">
-        <v>Faturamento + InvoiceDetailModal: invoice/ledger RPCs; payment, cancel, refund, print; keeps balance/states coherent; invalidates financial caches.</v>
+        <v>TaxasLocais CRUD on charge tables/items/overrides; invalidates queryKeys.charges.* families.</v>
       </c>
       <c r="E33" t="str">
         <v>Verified</v>
@@ -1462,10 +1462,10 @@
         <v>-</v>
       </c>
       <c r="H33" t="str">
-        <v>Vitest + SQL-contract</v>
+        <v>Vitest</v>
       </c>
       <c r="I33" t="str">
-        <v>src/pages/Faturamento.tsx; src/components/.../InvoiceDetailModal.tsx</v>
+        <v>src/pages/TaxasLocais.tsx</v>
       </c>
       <c r="J33" t="str">
         <v>-</v>
@@ -1473,16 +1473,16 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>ROUTE-27</v>
+        <v>ROUTE-26</v>
       </c>
       <c r="B34" t="str">
-        <v>Demurrage</v>
+        <v>Faturamento</v>
       </c>
       <c r="C34" t="str">
-        <v>As a user I want to use /demurrage to track containers and manage demurrage invoices</v>
+        <v>As a user I want to use /faturamento to validate B/Ls and issue individual/consolidated invoices; manage lifecycle</v>
       </c>
       <c r="D34" t="str">
-        <v>Demurrage services + exchange rates; calc by dates/rates, ROE freeze, PIX/reversal RPCs, own caches.</v>
+        <v>Faturamento + InvoiceDetailModal: invoice/ledger RPCs; payment, cancel, refund, print; keeps balance/states coherent; invalidates financial caches.</v>
       </c>
       <c r="E34" t="str">
         <v>Verified</v>
@@ -1494,10 +1494,10 @@
         <v>-</v>
       </c>
       <c r="H34" t="str">
-        <v>Vitest</v>
+        <v>Vitest + SQL-contract</v>
       </c>
       <c r="I34" t="str">
-        <v>src/pages/Demurrage.tsx</v>
+        <v>src/pages/Faturamento.tsx; src/components/.../InvoiceDetailModal.tsx</v>
       </c>
       <c r="J34" t="str">
         <v>-</v>
@@ -1505,16 +1505,16 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>ROUTE-28</v>
+        <v>ROUTE-27</v>
       </c>
       <c r="B35" t="str">
         <v>Demurrage</v>
       </c>
       <c r="C35" t="str">
-        <v>As a user I want to use /demurrage/taxas to manage demurrage rates</v>
+        <v>As a user I want to use /demurrage to track containers and manage demurrage invoices</v>
       </c>
       <c r="D35" t="str">
-        <v>DemurrageRates CRUD/activation on demurrage_rates updates future calculation; delete behind confirm dialog.</v>
+        <v>Demurrage services + exchange rates; calc by dates/rates, ROE freeze, PIX/reversal RPCs, own caches.</v>
       </c>
       <c r="E35" t="str">
         <v>Verified</v>
@@ -1529,24 +1529,24 @@
         <v>Vitest</v>
       </c>
       <c r="I35" t="str">
-        <v>src/pages/DemurrageRates.tsx; DemurrageRates.behavior.test.tsx</v>
+        <v>src/pages/Demurrage.tsx</v>
       </c>
       <c r="J35" t="str">
-        <v>DEF: behavior test was missing the ConfirmDialog provider mock after the page adopted useConfirm (commit 864f818); fixed in this loop.</v>
+        <v>-</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>ROUTE-29</v>
+        <v>ROUTE-28</v>
       </c>
       <c r="B36" t="str">
-        <v>Conciliação PIX</v>
+        <v>Demurrage</v>
       </c>
       <c r="C36" t="str">
-        <v>As a user I want to use /reconciliacao to import statement, classify and confirm PIX; reverse payments</v>
+        <v>As a user I want to use /demurrage/taxas to manage demurrage rates</v>
       </c>
       <c r="D36" t="str">
-        <v>Reconciliacao: confirm_unified_pix_matches; history + reversal RPCs with justification; propagates payment and invalidates local/demurrage domains.</v>
+        <v>DemurrageRates CRUD/activation on demurrage_rates updates future calculation; delete behind confirm dialog.</v>
       </c>
       <c r="E36" t="str">
         <v>Verified</v>
@@ -1558,27 +1558,27 @@
         <v>-</v>
       </c>
       <c r="H36" t="str">
-        <v>Vitest + SQL-contract</v>
+        <v>Vitest</v>
       </c>
       <c r="I36" t="str">
-        <v>src/pages/Reconciliacao.tsx; src/services/reconciliacao.ts</v>
+        <v>src/pages/DemurrageRates.tsx; DemurrageRates.behavior.test.tsx</v>
       </c>
       <c r="J36" t="str">
-        <v>-</v>
+        <v>DEF: behavior test was missing the ConfirmDialog provider mock after the page adopted useConfirm (commit 864f818); fixed in this loop.</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>ROUTE-30</v>
+        <v>ROUTE-29</v>
       </c>
       <c r="B37" t="str">
-        <v>Operação &amp; Suporte</v>
+        <v>Conciliação PIX</v>
       </c>
       <c r="C37" t="str">
-        <v>As a user I want to use /alertas to filter, acknowledge and close alerts</v>
+        <v>As a user I want to use /reconciliacao to import statement, classify and confirm PIX; reverse payments</v>
       </c>
       <c r="D37" t="str">
-        <v>Alertas via useOperationalAlerts; updates alerts; invalidates op-count and dashboard.</v>
+        <v>Reconciliacao: confirm_unified_pix_matches; history + reversal RPCs with justification; propagates payment and invalidates local/demurrage domains.</v>
       </c>
       <c r="E37" t="str">
         <v>Verified</v>
@@ -1590,27 +1590,27 @@
         <v>-</v>
       </c>
       <c r="H37" t="str">
-        <v>Static</v>
+        <v>Vitest + SQL-contract</v>
       </c>
       <c r="I37" t="str">
-        <v>src/pages/Alertas.tsx; src/services/alerts.ts</v>
+        <v>src/pages/Reconciliacao.tsx; src/services/reconciliacao.ts</v>
       </c>
       <c r="J37" t="str">
-        <v>Runtime not executed.</v>
+        <v>-</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>ROUTE-31</v>
+        <v>ROUTE-30</v>
       </c>
       <c r="B38" t="str">
         <v>Operação &amp; Suporte</v>
       </c>
       <c r="C38" t="str">
-        <v>As a user I want to use /relatorios to query and export XLSX reports</v>
+        <v>As a user I want to use /alertas to filter, acknowledge and close alerts</v>
       </c>
       <c r="D38" t="str">
-        <v>Relatorios reads B/Ls/invoices/customers/demurrage; per-tab/filter caches; export generates a local file.</v>
+        <v>Alertas via useOperationalAlerts; updates alerts; invalidates op-count and dashboard.</v>
       </c>
       <c r="E38" t="str">
         <v>Verified</v>
@@ -1622,27 +1622,27 @@
         <v>-</v>
       </c>
       <c r="H38" t="str">
-        <v>Vitest</v>
+        <v>Static</v>
       </c>
       <c r="I38" t="str">
-        <v>src/pages/Relatorios.tsx; src/services/reports.ts</v>
+        <v>src/pages/Alertas.tsx; src/services/alerts.ts</v>
       </c>
       <c r="J38" t="str">
-        <v>-</v>
+        <v>Runtime not executed.</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>ROUTE-32</v>
+        <v>ROUTE-31</v>
       </c>
       <c r="B39" t="str">
         <v>Operação &amp; Suporte</v>
       </c>
       <c r="C39" t="str">
-        <v>As a user I want to use /line-up-tv to reach legacy Line-Up admin</v>
+        <v>As a user I want to use /relatorios to query and export XLSX reports</v>
       </c>
       <c r="D39" t="str">
-        <v>LineUpTV redirects (replace) to /painel.</v>
+        <v>Relatorios reads B/Ls/invoices/customers/demurrage; per-tab/filter caches; export generates a local file.</v>
       </c>
       <c r="E39" t="str">
         <v>Verified</v>
@@ -1654,10 +1654,10 @@
         <v>-</v>
       </c>
       <c r="H39" t="str">
-        <v>Static</v>
+        <v>Vitest</v>
       </c>
       <c r="I39" t="str">
-        <v>src/pages/LineUpTV.tsx</v>
+        <v>src/pages/Relatorios.tsx; src/services/reports.ts</v>
       </c>
       <c r="J39" t="str">
         <v>-</v>
@@ -1665,16 +1665,16 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>ROUTE-33</v>
+        <v>ROUTE-32</v>
       </c>
       <c r="B40" t="str">
         <v>Operação &amp; Suporte</v>
       </c>
       <c r="C40" t="str">
-        <v>As a user I want to use /line-up-tv/display to show and refresh the protected Line-Up TV</v>
+        <v>As a user I want to use /line-up-tv to reach legacy Line-Up admin</v>
       </c>
       <c r="D40" t="str">
-        <v>LineUpTVDisplay via fetchLineUpSnapshot; cache [lineup-tv-display-v2], rotation, fullscreen.</v>
+        <v>LineUpTV redirects (replace) to /painel.</v>
       </c>
       <c r="E40" t="str">
         <v>Verified</v>
@@ -1689,24 +1689,24 @@
         <v>Static</v>
       </c>
       <c r="I40" t="str">
-        <v>src/pages/LineUpTVDisplay.tsx</v>
+        <v>src/pages/LineUpTV.tsx</v>
       </c>
       <c r="J40" t="str">
-        <v>Runtime blocked.</v>
+        <v>-</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>ROUTE-34</v>
+        <v>ROUTE-33</v>
       </c>
       <c r="B41" t="str">
-        <v>Chegadas/Saídas</v>
+        <v>Operação &amp; Suporte</v>
       </c>
       <c r="C41" t="str">
-        <v>As a user I want to use /chegadas-saidas to manage, import, sort and archive the schedule</v>
+        <v>As a user I want to use /line-up-tv/display to show and refresh the protected Line-Up TV</v>
       </c>
       <c r="D41" t="str">
-        <v>ChegadasSaidas via useVesselSchedules; vessel_schedules + ended_vessels; realtime also invalidates the Portal widget.</v>
+        <v>LineUpTVDisplay via fetchLineUpSnapshot; cache [lineup-tv-display-v2], rotation, fullscreen.</v>
       </c>
       <c r="E41" t="str">
         <v>Verified</v>
@@ -1721,24 +1721,24 @@
         <v>Static</v>
       </c>
       <c r="I41" t="str">
-        <v>src/pages/ChegadasSaidas.tsx; src/services/vesselSchedules.ts</v>
+        <v>src/pages/LineUpTVDisplay.tsx</v>
       </c>
       <c r="J41" t="str">
-        <v>Runtime not executed.</v>
+        <v>Runtime blocked.</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>ROUTE-35</v>
+        <v>ROUTE-34</v>
       </c>
       <c r="B42" t="str">
-        <v>Operação &amp; Suporte</v>
+        <v>Chegadas/Saídas</v>
       </c>
       <c r="C42" t="str">
-        <v>As a user I want to use /admin/usuarios to change role/active and consult audit/metrics</v>
+        <v>As a user I want to use /chegadas-saidas to manage, import, sort and archive the schedule</v>
       </c>
       <c r="D42" t="str">
-        <v>AdminUsuarios under ProtectedRoute adminOnly; profiles + audit logs; invalidates users, audit, metrics. Dedicated error states for logs/metrics tabs (DEF-061/062).</v>
+        <v>ChegadasSaidas via useVesselSchedules; vessel_schedules + ended_vessels; realtime also invalidates the Portal widget.</v>
       </c>
       <c r="E42" t="str">
         <v>Verified</v>
@@ -1750,27 +1750,27 @@
         <v>-</v>
       </c>
       <c r="H42" t="str">
-        <v>Vitest</v>
+        <v>Static</v>
       </c>
       <c r="I42" t="str">
-        <v>src/pages/AdminUsuarios.tsx; AdminUsuarios.behavior.test.tsx</v>
+        <v>src/pages/ChegadasSaidas.tsx; src/services/vesselSchedules.ts</v>
       </c>
       <c r="J42" t="str">
-        <v>-</v>
+        <v>Runtime not executed.</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>ROUTE-36</v>
+        <v>ROUTE-35</v>
       </c>
       <c r="B43" t="str">
-        <v>Manifestos &amp; EDI</v>
+        <v>Operação &amp; Suporte</v>
       </c>
       <c r="C43" t="str">
-        <v>As a user I want to use /vazios to be redirected from a compatibility route</v>
+        <v>As a user I want to use /admin/usuarios to change role/active and consult audit/metrics</v>
       </c>
       <c r="D43" t="str">
-        <v>Navigate (replace) to /embarquevazios.</v>
+        <v>AdminUsuarios under ProtectedRoute adminOnly; profiles + audit logs; invalidates users, audit, metrics. Dedicated error states for logs/metrics tabs (DEF-061/062).</v>
       </c>
       <c r="E43" t="str">
         <v>Verified</v>
@@ -1782,10 +1782,10 @@
         <v>-</v>
       </c>
       <c r="H43" t="str">
-        <v>Static</v>
+        <v>Vitest</v>
       </c>
       <c r="I43" t="str">
-        <v>src/App.tsx</v>
+        <v>src/pages/AdminUsuarios.tsx; AdminUsuarios.behavior.test.tsx</v>
       </c>
       <c r="J43" t="str">
         <v>-</v>
@@ -1793,16 +1793,16 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>ROUTE-37</v>
+        <v>ROUTE-36</v>
       </c>
       <c r="B44" t="str">
-        <v>Demurrage</v>
+        <v>Manifestos &amp; EDI</v>
       </c>
       <c r="C44" t="str">
-        <v>As a user I want to use /demurrage/invoices to be redirected from a legacy route</v>
+        <v>As a user I want to use /vazios to be redirected from a compatibility route</v>
       </c>
       <c r="D44" t="str">
-        <v>Navigate (replace) to /demurrage.</v>
+        <v>Navigate (replace) to /embarquevazios.</v>
       </c>
       <c r="E44" t="str">
         <v>Verified</v>
@@ -1825,16 +1825,16 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>ROUTE-38</v>
+        <v>ROUTE-37</v>
       </c>
       <c r="B45" t="str">
-        <v>Conciliação PIX</v>
+        <v>Demurrage</v>
       </c>
       <c r="C45" t="str">
-        <v>As a user I want to use /demurrage/reconciliacao to be redirected from a legacy route</v>
+        <v>As a user I want to use /demurrage/invoices to be redirected from a legacy route</v>
       </c>
       <c r="D45" t="str">
-        <v>Navigate (replace) to /reconciliacao.</v>
+        <v>Navigate (replace) to /demurrage.</v>
       </c>
       <c r="E45" t="str">
         <v>Verified</v>
@@ -1857,16 +1857,16 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>ROUTE-39</v>
+        <v>ROUTE-38</v>
       </c>
       <c r="B46" t="str">
-        <v>Operação &amp; Suporte</v>
+        <v>Conciliação PIX</v>
       </c>
       <c r="C46" t="str">
-        <v>As a user I want to use * to be redirected from an unknown route</v>
+        <v>As a user I want to use /demurrage/reconciliacao to be redirected from a legacy route</v>
       </c>
       <c r="D46" t="str">
-        <v>Navigate (replace) to /painel.</v>
+        <v>Navigate (replace) to /reconciliacao.</v>
       </c>
       <c r="E46" t="str">
         <v>Verified</v>
@@ -1884,24 +1884,24 @@
         <v>src/App.tsx</v>
       </c>
       <c r="J46" t="str">
-        <v>Depends on config/auth state.</v>
+        <v>-</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>RPC-01</v>
+        <v>ROUTE-39</v>
       </c>
       <c r="B47" t="str">
-        <v>Taxas Locais</v>
+        <v>Operação &amp; Suporte</v>
       </c>
       <c r="C47" t="str">
-        <v>As the platform I call supabase.rpc('add_manual_bl_charge')</v>
+        <v>As a user I want to use * to be redirected from an unknown route</v>
       </c>
       <c r="D47" t="str">
-        <v>Inserts charge_calculations, adjusts bls, audits; blocks already-invoiced B/L. Auth: auth.uid()+is_active_user(); PUBLIC revoked; authenticated.</v>
+        <v>Navigate (replace) to /painel.</v>
       </c>
       <c r="E47" t="str">
-        <v>Tested-Pass</v>
+        <v>Verified</v>
       </c>
       <c r="F47" t="str">
         <v>-</v>
@@ -1910,27 +1910,27 @@
         <v>-</v>
       </c>
       <c r="H47" t="str">
-        <v>SQL-contract</v>
+        <v>Static</v>
       </c>
       <c r="I47" t="str">
-        <v>chargeOperationsService.ts; guardManualChargesMigration.test.ts</v>
+        <v>src/App.tsx</v>
       </c>
       <c r="J47" t="str">
-        <v>-</v>
+        <v>Depends on config/auth state.</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>RPC-02</v>
+        <v>RPC-01</v>
       </c>
       <c r="B48" t="str">
-        <v>Faturamento</v>
+        <v>Taxas Locais</v>
       </c>
       <c r="C48" t="str">
-        <v>As the platform I call supabase.rpc('add_manual_invoice_charge')</v>
+        <v>As the platform I call supabase.rpc('add_manual_bl_charge')</v>
       </c>
       <c r="D48" t="str">
-        <v>Inserts invoice_items, recalculates invoice, clears/regenerates PIX, audits. Auth: auth.uid()+active+admin; INVOKER.</v>
+        <v>Inserts charge_calculations, adjusts bls, audits; blocks already-invoiced B/L. Auth: auth.uid()+is_active_user(); PUBLIC revoked; authenticated.</v>
       </c>
       <c r="E48" t="str">
         <v>Tested-Pass</v>
@@ -1945,7 +1945,7 @@
         <v>SQL-contract</v>
       </c>
       <c r="I48" t="str">
-        <v>billing.ts; guardManualChargesMigration.test.ts</v>
+        <v>chargeOperationsService.ts; guardManualChargesMigration.test.ts</v>
       </c>
       <c r="J48" t="str">
         <v>-</v>
@@ -1953,19 +1953,19 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>RPC-03</v>
+        <v>RPC-02</v>
       </c>
       <c r="B49" t="str">
-        <v>Manifestos / CE Mercante</v>
+        <v>Faturamento</v>
       </c>
       <c r="C49" t="str">
-        <v>As the platform I call supabase.rpc('apply_ce_mercante_manifest')</v>
+        <v>As the platform I call supabase.rpc('add_manual_invoice_charge')</v>
       </c>
       <c r="D49" t="str">
-        <v>Batch update of bls.ce_mercante with audit (INVOKER, caller RLS). Auth: PUBLIC/anon revoked; authenticated.</v>
+        <v>Inserts invoice_items, recalculates invoice, clears/regenerates PIX, audits. Auth: auth.uid()+active+admin; INVOKER.</v>
       </c>
       <c r="E49" t="str">
-        <v>Spec’d</v>
+        <v>Tested-Pass</v>
       </c>
       <c r="F49" t="str">
         <v>-</v>
@@ -1974,10 +1974,10 @@
         <v>-</v>
       </c>
       <c r="H49" t="str">
-        <v>Static</v>
+        <v>SQL-contract</v>
       </c>
       <c r="I49" t="str">
-        <v>ceMercanteImport.ts</v>
+        <v>billing.ts; guardManualChargesMigration.test.ts</v>
       </c>
       <c r="J49" t="str">
         <v>-</v>
@@ -1985,19 +1985,19 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>RPC-04</v>
+        <v>RPC-03</v>
       </c>
       <c r="B50" t="str">
         <v>Manifestos / CE Mercante</v>
       </c>
       <c r="C50" t="str">
-        <v>As the platform I call supabase.rpc('apply_ce_mercante_update')</v>
+        <v>As the platform I call supabase.rpc('apply_ce_mercante_manifest')</v>
       </c>
       <c r="D50" t="str">
-        <v>Updates CE of one B/L and audits; returns unchanged when no change. Auth: caller RLS; PUBLIC revoked; authenticated.</v>
+        <v>Batch update of bls.ce_mercante with audit (INVOKER, caller RLS). Auth: PUBLIC/anon revoked; authenticated.</v>
       </c>
       <c r="E50" t="str">
-        <v>Tested-Pass</v>
+        <v>Spec’d</v>
       </c>
       <c r="F50" t="str">
         <v>-</v>
@@ -2006,10 +2006,10 @@
         <v>-</v>
       </c>
       <c r="H50" t="str">
-        <v>Integration (not run)</v>
+        <v>Static</v>
       </c>
       <c r="I50" t="str">
-        <v>ceMercanteImport.ts; supabase.integration.test.ts</v>
+        <v>ceMercanteImport.ts</v>
       </c>
       <c r="J50" t="str">
         <v>-</v>
@@ -2017,19 +2017,19 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>RPC-05</v>
+        <v>RPC-04</v>
       </c>
       <c r="B51" t="str">
-        <v>Revisão / Clientes</v>
+        <v>Manifestos / CE Mercante</v>
       </c>
       <c r="C51" t="str">
-        <v>As the platform I call supabase.rpc('approve_customer_reconciliation')</v>
+        <v>As the platform I call supabase.rpc('apply_ce_mercante_update')</v>
       </c>
       <c r="D51" t="str">
-        <v>Approves queue, links/updates B/L and contact, audits. Auth: active+authenticated; DEFINER.</v>
+        <v>Updates CE of one B/L and audits; returns unchanged when no change. Auth: caller RLS; PUBLIC revoked; authenticated.</v>
       </c>
       <c r="E51" t="str">
-        <v>Spec’d</v>
+        <v>Tested-Pass</v>
       </c>
       <c r="F51" t="str">
         <v>-</v>
@@ -2038,10 +2038,10 @@
         <v>-</v>
       </c>
       <c r="H51" t="str">
-        <v>Static</v>
+        <v>Integration (not run)</v>
       </c>
       <c r="I51" t="str">
-        <v>chargeReconciliationService.ts</v>
+        <v>ceMercanteImport.ts; supabase.integration.test.ts</v>
       </c>
       <c r="J51" t="str">
         <v>-</v>
@@ -2049,19 +2049,19 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>RPC-06</v>
+        <v>RPC-05</v>
       </c>
       <c r="B52" t="str">
-        <v>Chegadas/Saídas</v>
+        <v>Revisão / Clientes</v>
       </c>
       <c r="C52" t="str">
-        <v>As the platform I call supabase.rpc('archive_vessel_schedule')</v>
+        <v>As the platform I call supabase.rpc('approve_customer_reconciliation')</v>
       </c>
       <c r="D52" t="str">
-        <v>Snapshots an ended vessel into ended_vessels and removes the schedule. Auth: active.</v>
+        <v>Approves queue, links/updates B/L and contact, audits. Auth: active+authenticated; DEFINER.</v>
       </c>
       <c r="E52" t="str">
-        <v>Verified</v>
+        <v>Spec’d</v>
       </c>
       <c r="F52" t="str">
         <v>-</v>
@@ -2070,10 +2070,10 @@
         <v>-</v>
       </c>
       <c r="H52" t="str">
-        <v>Vitest</v>
+        <v>Static</v>
       </c>
       <c r="I52" t="str">
-        <v>src/services/vesselSchedules.ts</v>
+        <v>chargeReconciliationService.ts</v>
       </c>
       <c r="J52" t="str">
         <v>-</v>
@@ -2081,19 +2081,19 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>RPC-07</v>
+        <v>RPC-06</v>
       </c>
       <c r="B53" t="str">
-        <v>Faturamento / Ledger</v>
+        <v>Chegadas/Saídas</v>
       </c>
       <c r="C53" t="str">
-        <v>As the platform I call supabase.rpc('backfill_invoice_receivable_links')</v>
+        <v>As the platform I call supabase.rpc('archive_vessel_schedule')</v>
       </c>
       <c r="D53" t="str">
-        <v>Reconstructs invoice_receivable_links for legacy invoices. Auth: admin (ledger maintenance).</v>
+        <v>Snapshots an ended vessel into ended_vessels and removes the schedule. Auth: active.</v>
       </c>
       <c r="E53" t="str">
-        <v>Tested-Pass</v>
+        <v>Verified</v>
       </c>
       <c r="F53" t="str">
         <v>-</v>
@@ -2102,10 +2102,10 @@
         <v>-</v>
       </c>
       <c r="H53" t="str">
-        <v>Integration (not run)</v>
+        <v>Vitest</v>
       </c>
       <c r="I53" t="str">
-        <v>billingLedger.ts; supabase.integration.test.ts</v>
+        <v>src/services/vesselSchedules.ts</v>
       </c>
       <c r="J53" t="str">
         <v>-</v>
@@ -2113,19 +2113,19 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>RPC-08</v>
+        <v>RPC-07</v>
       </c>
       <c r="B54" t="str">
-        <v>Manifestos / B/L</v>
+        <v>Faturamento / Ledger</v>
       </c>
       <c r="C54" t="str">
-        <v>As the platform I call supabase.rpc('bl_timeline')</v>
+        <v>As the platform I call supabase.rpc('backfill_invoice_receivable_links')</v>
       </c>
       <c r="D54" t="str">
-        <v>Read-only humanized B/L timeline (50/page); Auditoria is the justified subset. Auth: is_active_user(); PUBLIC/anon revoked; authenticated.</v>
+        <v>Reconstructs invoice_receivable_links for legacy invoices. Auth: admin (ledger maintenance).</v>
       </c>
       <c r="E54" t="str">
-        <v>Verified</v>
+        <v>Tested-Pass</v>
       </c>
       <c r="F54" t="str">
         <v>-</v>
@@ -2134,10 +2134,10 @@
         <v>-</v>
       </c>
       <c r="H54" t="str">
-        <v>Vitest + SQL-contract</v>
+        <v>Integration (not run)</v>
       </c>
       <c r="I54" t="str">
-        <v>blTimeline.ts; 20260619190144_bl_timeline_rpc.sql</v>
+        <v>billingLedger.ts; supabase.integration.test.ts</v>
       </c>
       <c r="J54" t="str">
         <v>-</v>
@@ -2145,16 +2145,16 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>RPC-09</v>
+        <v>RPC-08</v>
       </c>
       <c r="B55" t="str">
-        <v>Taxas Locais</v>
+        <v>Manifestos / B/L</v>
       </c>
       <c r="C55" t="str">
-        <v>As the platform I call supabase.rpc('calculate_bl_local_charges')</v>
+        <v>As the platform I call supabase.rpc('bl_timeline')</v>
       </c>
       <c r="D55" t="str">
-        <v>Recreates automatic lines, applies table/override, updates status/hold. Auth: requires auth.uid() but NOT is_active_user().</v>
+        <v>Read-only humanized B/L timeline (50/page); Auditoria is the justified subset. Auth: is_active_user(); PUBLIC/anon revoked; authenticated.</v>
       </c>
       <c r="E55" t="str">
         <v>Verified</v>
@@ -2166,30 +2166,30 @@
         <v>-</v>
       </c>
       <c r="H55" t="str">
-        <v>SQL-contract</v>
+        <v>Vitest + SQL-contract</v>
       </c>
       <c r="I55" t="str">
-        <v>chargeOperationsService.ts; 20260612144751_*.sql</v>
+        <v>blTimeline.ts; 20260619190144_bl_timeline_rpc.sql</v>
       </c>
       <c r="J55" t="str">
-        <v>RESOLVED: is_active_user() gate added in 20260624100100_guard_definer_rpcs_active_user.sql (ADR 0004); SQL readers converted to plpgsql (query preserved via RETURN QUERY). definerActiveUserGuardMigration.test.ts green. Migrations applied cleanly to the PR Supabase preview branch (all tasks green); production grant application on merge/deploy.</v>
+        <v>-</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>RPC-10</v>
+        <v>RPC-09</v>
       </c>
       <c r="B56" t="str">
-        <v>Faturamento / Veículos</v>
+        <v>Taxas Locais</v>
       </c>
       <c r="C56" t="str">
-        <v>As the platform I call supabase.rpc('cancel_invoice')</v>
+        <v>As the platform I call supabase.rpc('calculate_bl_local_charges')</v>
       </c>
       <c r="D56" t="str">
-        <v>Cancels unpaid invoice, updates batch + B/L/Granito financial state, audits. Auth: authenticated+active+admin; DEFINER.</v>
+        <v>Recreates automatic lines, applies table/override, updates status/hold. Auth: requires auth.uid() but NOT is_active_user().</v>
       </c>
       <c r="E56" t="str">
-        <v>Tested-Pass</v>
+        <v>Verified</v>
       </c>
       <c r="F56" t="str">
         <v>-</v>
@@ -2198,30 +2198,30 @@
         <v>-</v>
       </c>
       <c r="H56" t="str">
-        <v>Integration (not run)</v>
+        <v>SQL-contract + Runtime (prod)</v>
       </c>
       <c r="I56" t="str">
-        <v>billing.ts; vehicleImport.ts</v>
+        <v>chargeOperationsService.ts; 20260612144751_*.sql</v>
       </c>
       <c r="J56" t="str">
-        <v>-</v>
+        <v>RESOLVED &amp; RUNTIME-VERIFIED in production (fgmkhbzhaeebrsizwccx, 2026-06-24): language=plpgsql, is_active_user() guard present, anon EXECUTE=false. Migration 20260624100100 (ADR 0004); readers converted to plpgsql with query preserved via RETURN QUERY.</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>RPC-11</v>
+        <v>RPC-10</v>
       </c>
       <c r="B57" t="str">
-        <v>Conciliação PIX</v>
+        <v>Faturamento / Veículos</v>
       </c>
       <c r="C57" t="str">
-        <v>As the platform I call supabase.rpc('confirm_unified_pix_matches')</v>
+        <v>As the platform I call supabase.rpc('cancel_invoice')</v>
       </c>
       <c r="D57" t="str">
-        <v>Reconciles local (TXID/value) and demurrage in one transaction; any error aborts the batch. Auth: authenticated; delegates to guarded RPCs.</v>
+        <v>Cancels unpaid invoice, updates batch + B/L/Granito financial state, audits. Auth: authenticated+active+admin; DEFINER.</v>
       </c>
       <c r="E57" t="str">
-        <v>Verified</v>
+        <v>Tested-Pass</v>
       </c>
       <c r="F57" t="str">
         <v>-</v>
@@ -2230,10 +2230,10 @@
         <v>-</v>
       </c>
       <c r="H57" t="str">
-        <v>Vitest + SQL-contract</v>
+        <v>Integration (not run)</v>
       </c>
       <c r="I57" t="str">
-        <v>reconciliacao.ts</v>
+        <v>billing.ts; vehicleImport.ts</v>
       </c>
       <c r="J57" t="str">
         <v>-</v>
@@ -2241,16 +2241,16 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>RPC-12</v>
+        <v>RPC-11</v>
       </c>
       <c r="B58" t="str">
-        <v>Painel</v>
+        <v>Conciliação PIX</v>
       </c>
       <c r="C58" t="str">
-        <v>As the platform I call supabase.rpc('count_distinct_containers')</v>
+        <v>As the platform I call supabase.rpc('confirm_unified_pix_matches')</v>
       </c>
       <c r="D58" t="str">
-        <v>Read-only aggregate for dashboard (INVOKER). Auth: caller RLS; PUBLIC revoked; authenticated.</v>
+        <v>Reconciles local (TXID/value) and demurrage in one transaction; any error aborts the batch. Auth: authenticated; delegates to guarded RPCs.</v>
       </c>
       <c r="E58" t="str">
         <v>Verified</v>
@@ -2262,10 +2262,10 @@
         <v>-</v>
       </c>
       <c r="H58" t="str">
-        <v>Static</v>
+        <v>Vitest + SQL-contract</v>
       </c>
       <c r="I58" t="str">
-        <v>src/pages/Painel.tsx</v>
+        <v>reconciliacao.ts</v>
       </c>
       <c r="J58" t="str">
         <v>-</v>
@@ -2273,16 +2273,16 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>RPC-13</v>
+        <v>RPC-12</v>
       </c>
       <c r="B59" t="str">
-        <v>Clientes</v>
+        <v>Painel</v>
       </c>
       <c r="C59" t="str">
-        <v>As the platform I call supabase.rpc('create_customer_with_contacts')</v>
+        <v>As the platform I call supabase.rpc('count_distinct_containers')</v>
       </c>
       <c r="D59" t="str">
-        <v>Atomically creates a customer and its contacts. Auth: active.</v>
+        <v>Read-only aggregate for dashboard (INVOKER). Auth: caller RLS; PUBLIC revoked; authenticated.</v>
       </c>
       <c r="E59" t="str">
         <v>Verified</v>
@@ -2294,10 +2294,10 @@
         <v>-</v>
       </c>
       <c r="H59" t="str">
-        <v>Vitest</v>
+        <v>Static</v>
       </c>
       <c r="I59" t="str">
-        <v>src/services/customers.ts</v>
+        <v>src/pages/Painel.tsx</v>
       </c>
       <c r="J59" t="str">
         <v>-</v>
@@ -2305,16 +2305,16 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>RPC-14</v>
+        <v>RPC-13</v>
       </c>
       <c r="B60" t="str">
-        <v>Demurrage</v>
+        <v>Clientes</v>
       </c>
       <c r="C60" t="str">
-        <v>As the platform I call supabase.rpc('create_demurrage_invoice_with_items')</v>
+        <v>As the platform I call supabase.rpc('create_customer_with_contacts')</v>
       </c>
       <c r="D60" t="str">
-        <v>Creates a demurrage invoice with frozen line items in one transaction. Auth: active+admin.</v>
+        <v>Atomically creates a customer and its contacts. Auth: active.</v>
       </c>
       <c r="E60" t="str">
         <v>Verified</v>
@@ -2329,7 +2329,7 @@
         <v>Vitest</v>
       </c>
       <c r="I60" t="str">
-        <v>src/services/demurrage/demurrageInvoices.ts</v>
+        <v>src/services/customers.ts</v>
       </c>
       <c r="J60" t="str">
         <v>-</v>
@@ -2337,19 +2337,19 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>RPC-15</v>
+        <v>RPC-14</v>
       </c>
       <c r="B61" t="str">
-        <v>Faturamento</v>
+        <v>Demurrage</v>
       </c>
       <c r="C61" t="str">
-        <v>As the platform I call supabase.rpc('create_invoice_from_bls')</v>
+        <v>As the platform I call supabase.rpc('create_demurrage_invoice_with_items')</v>
       </c>
       <c r="D61" t="str">
-        <v>Legacy invoice creation from B/Ls (superseded by *_with_ledger). Auth: authenticated+active+admin.</v>
+        <v>Creates a demurrage invoice with frozen line items in one transaction. Auth: active+admin.</v>
       </c>
       <c r="E61" t="str">
-        <v>Tested-Pass</v>
+        <v>Verified</v>
       </c>
       <c r="F61" t="str">
         <v>-</v>
@@ -2358,10 +2358,10 @@
         <v>-</v>
       </c>
       <c r="H61" t="str">
-        <v>Integration (not run)</v>
+        <v>Vitest</v>
       </c>
       <c r="I61" t="str">
-        <v>billing.ts; supabase.integration.test.ts</v>
+        <v>src/services/demurrage/demurrageInvoices.ts</v>
       </c>
       <c r="J61" t="str">
         <v>-</v>
@@ -2369,16 +2369,16 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>RPC-16</v>
+        <v>RPC-15</v>
       </c>
       <c r="B62" t="str">
-        <v>Faturamento / Ledger</v>
+        <v>Faturamento</v>
       </c>
       <c r="C62" t="str">
-        <v>As the platform I call supabase.rpc('create_invoice_from_bls_with_ledger')</v>
+        <v>As the platform I call supabase.rpc('create_invoice_from_bls')</v>
       </c>
       <c r="D62" t="str">
-        <v>Validates caller, runs revoked core + link_invoice_to_ledger; frontend persists PIX fallback. Auth: authenticated+active+admin.</v>
+        <v>Legacy invoice creation from B/Ls (superseded by *_with_ledger). Auth: authenticated+active+admin.</v>
       </c>
       <c r="E62" t="str">
         <v>Tested-Pass</v>
@@ -2393,7 +2393,7 @@
         <v>Integration (not run)</v>
       </c>
       <c r="I62" t="str">
-        <v>billing.ts</v>
+        <v>billing.ts; supabase.integration.test.ts</v>
       </c>
       <c r="J62" t="str">
         <v>-</v>
@@ -2401,19 +2401,19 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>RPC-17</v>
+        <v>RPC-16</v>
       </c>
       <c r="B63" t="str">
-        <v>Granito / Faturamento</v>
+        <v>Faturamento / Ledger</v>
       </c>
       <c r="C63" t="str">
-        <v>As the platform I call supabase.rpc('create_invoice_from_granite_bls')</v>
+        <v>As the platform I call supabase.rpc('create_invoice_from_bls_with_ledger')</v>
       </c>
       <c r="D63" t="str">
-        <v>Creates Granito invoice/items/links, updates granite_bls, avoids duplicate active invoice. Auth: authenticated+active+admin.</v>
+        <v>Validates caller, runs revoked core + link_invoice_to_ledger; frontend persists PIX fallback. Auth: authenticated+active+admin.</v>
       </c>
       <c r="E63" t="str">
-        <v>Spec’d</v>
+        <v>Tested-Pass</v>
       </c>
       <c r="F63" t="str">
         <v>-</v>
@@ -2422,7 +2422,7 @@
         <v>-</v>
       </c>
       <c r="H63" t="str">
-        <v>Static</v>
+        <v>Integration (not run)</v>
       </c>
       <c r="I63" t="str">
         <v>billing.ts</v>
@@ -2433,16 +2433,16 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>RPC-18</v>
+        <v>RPC-17</v>
       </c>
       <c r="B64" t="str">
-        <v>Faturamento / Ledger</v>
+        <v>Granito / Faturamento</v>
       </c>
       <c r="C64" t="str">
-        <v>As the platform I call supabase.rpc('create_local_consolidated_invoice')</v>
+        <v>As the platform I call supabase.rpc('create_invoice_from_granite_bls')</v>
       </c>
       <c r="D64" t="str">
-        <v>Creates consolidated invoice, links and lifecycle event. Auth: authenticated+active+admin; wrapper -&gt; private core.</v>
+        <v>Creates Granito invoice/items/links, updates granite_bls, avoids duplicate active invoice. Auth: authenticated+active+admin.</v>
       </c>
       <c r="E64" t="str">
         <v>Spec’d</v>
@@ -2457,7 +2457,7 @@
         <v>Static</v>
       </c>
       <c r="I64" t="str">
-        <v>billingLedger.ts</v>
+        <v>billing.ts</v>
       </c>
       <c r="J64" t="str">
         <v>-</v>
@@ -2465,19 +2465,19 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>RPC-19</v>
+        <v>RPC-18</v>
       </c>
       <c r="B65" t="str">
-        <v>Taxas Locais</v>
+        <v>Faturamento / Ledger</v>
       </c>
       <c r="C65" t="str">
-        <v>As the platform I call supabase.rpc('delete_manual_bl_charge')</v>
+        <v>As the platform I call supabase.rpc('create_local_consolidated_invoice')</v>
       </c>
       <c r="D65" t="str">
-        <v>Deletes only an eligible manual line and audits; blocks invoice-protected B/L. Auth: authenticated+active.</v>
+        <v>Creates consolidated invoice, links and lifecycle event. Auth: authenticated+active+admin; wrapper -&gt; private core.</v>
       </c>
       <c r="E65" t="str">
-        <v>Tested-Pass</v>
+        <v>Spec’d</v>
       </c>
       <c r="F65" t="str">
         <v>-</v>
@@ -2486,10 +2486,10 @@
         <v>-</v>
       </c>
       <c r="H65" t="str">
-        <v>SQL-contract</v>
+        <v>Static</v>
       </c>
       <c r="I65" t="str">
-        <v>chargeOperationsService.ts; guardManualChargesMigration.test.ts</v>
+        <v>billingLedger.ts</v>
       </c>
       <c r="J65" t="str">
         <v>-</v>
@@ -2497,16 +2497,16 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>RPC-20</v>
+        <v>RPC-19</v>
       </c>
       <c r="B66" t="str">
-        <v>Faturamento</v>
+        <v>Taxas Locais</v>
       </c>
       <c r="C66" t="str">
-        <v>As the platform I call supabase.rpc('delete_manual_invoice_charge')</v>
+        <v>As the platform I call supabase.rpc('delete_manual_bl_charge')</v>
       </c>
       <c r="D66" t="str">
-        <v>Deletes a manual item from an open invoice, recalculates total, audits. Auth: authenticated+active+admin; INVOKER.</v>
+        <v>Deletes only an eligible manual line and audits; blocks invoice-protected B/L. Auth: authenticated+active.</v>
       </c>
       <c r="E66" t="str">
         <v>Tested-Pass</v>
@@ -2521,7 +2521,7 @@
         <v>SQL-contract</v>
       </c>
       <c r="I66" t="str">
-        <v>billing.ts; guardManualChargesMigration.test.ts</v>
+        <v>chargeOperationsService.ts; guardManualChargesMigration.test.ts</v>
       </c>
       <c r="J66" t="str">
         <v>-</v>
@@ -2529,19 +2529,19 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>RPC-21</v>
+        <v>RPC-20</v>
       </c>
       <c r="B67" t="str">
-        <v>Alertas / Faturamento</v>
+        <v>Faturamento</v>
       </c>
       <c r="C67" t="str">
-        <v>As the platform I call supabase.rpc('detect_overdue_invoices')</v>
+        <v>As the platform I call supabase.rpc('delete_manual_invoice_charge')</v>
       </c>
       <c r="D67" t="str">
-        <v>Marks overdue local invoices and creates non-duplicate alerts. Auth: anon/PUBLIC revoked; NO internal active/admin check.</v>
+        <v>Deletes a manual item from an open invoice, recalculates total, audits. Auth: authenticated+active+admin; INVOKER.</v>
       </c>
       <c r="E67" t="str">
-        <v>Verified</v>
+        <v>Tested-Pass</v>
       </c>
       <c r="F67" t="str">
         <v>-</v>
@@ -2553,27 +2553,27 @@
         <v>SQL-contract</v>
       </c>
       <c r="I67" t="str">
-        <v>alerts.ts; 024_detect_overdue_invoices.sql</v>
+        <v>billing.ts; guardManualChargesMigration.test.ts</v>
       </c>
       <c r="J67" t="str">
-        <v>RESOLVED: is_active_user() gate added in 20260624100100_guard_definer_rpcs_active_user.sql (ADR 0004); SQL readers converted to plpgsql (query preserved via RETURN QUERY). definerActiveUserGuardMigration.test.ts green. Migrations applied cleanly to the PR Supabase preview branch (all tasks green); production grant application on merge/deploy.</v>
+        <v>-</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>RPC-22</v>
+        <v>RPC-21</v>
       </c>
       <c r="B68" t="str">
-        <v>Clientes / Portal</v>
+        <v>Alertas / Faturamento</v>
       </c>
       <c r="C68" t="str">
-        <v>As the platform I call supabase.rpc('get_customer_portal_account')</v>
+        <v>As the platform I call supabase.rpc('detect_overdue_invoices')</v>
       </c>
       <c r="D68" t="str">
-        <v>Reads Portal account and Auth state for admin/review. Auth: authenticated+active+admin; DEFINER.</v>
+        <v>Marks overdue local invoices and creates non-duplicate alerts. Auth: anon/PUBLIC revoked; NO internal active/admin check.</v>
       </c>
       <c r="E68" t="str">
-        <v>Spec’d</v>
+        <v>Verified</v>
       </c>
       <c r="F68" t="str">
         <v>-</v>
@@ -2582,30 +2582,30 @@
         <v>-</v>
       </c>
       <c r="H68" t="str">
-        <v>Static</v>
+        <v>SQL-contract + Runtime (prod)</v>
       </c>
       <c r="I68" t="str">
-        <v>customers.ts</v>
+        <v>alerts.ts; 024_detect_overdue_invoices.sql</v>
       </c>
       <c r="J68" t="str">
-        <v>-</v>
+        <v>RESOLVED &amp; RUNTIME-VERIFIED in production (fgmkhbzhaeebrsizwccx, 2026-06-24): language=plpgsql, is_active_user() guard present, anon EXECUTE=false. Migration 20260624100100 (ADR 0004); readers converted to plpgsql with query preserved via RETURN QUERY.</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>RPC-23</v>
+        <v>RPC-22</v>
       </c>
       <c r="B69" t="str">
-        <v>Baplie</v>
+        <v>Clientes / Portal</v>
       </c>
       <c r="C69" t="str">
-        <v>As the platform I call supabase.rpc('import_baplie_staging_transactional')</v>
+        <v>As the platform I call supabase.rpc('get_customer_portal_account')</v>
       </c>
       <c r="D69" t="str">
-        <v>Atomically replaces Baplie staging for a voyage. Auth: authenticated+active+admin; anon revoked.</v>
+        <v>Reads Portal account and Auth state for admin/review. Auth: authenticated+active+admin; DEFINER.</v>
       </c>
       <c r="E69" t="str">
-        <v>Verified</v>
+        <v>Spec’d</v>
       </c>
       <c r="F69" t="str">
         <v>-</v>
@@ -2614,10 +2614,10 @@
         <v>-</v>
       </c>
       <c r="H69" t="str">
-        <v>Vitest</v>
+        <v>Static</v>
       </c>
       <c r="I69" t="str">
-        <v>baplieImport.ts</v>
+        <v>customers.ts</v>
       </c>
       <c r="J69" t="str">
         <v>-</v>
@@ -2625,16 +2625,16 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>RPC-24</v>
+        <v>RPC-23</v>
       </c>
       <c r="B70" t="str">
-        <v>Manifestos &amp; EDI</v>
+        <v>Baplie</v>
       </c>
       <c r="C70" t="str">
-        <v>As the platform I call supabase.rpc('import_breakbulk_manifest_transactional')</v>
+        <v>As the platform I call supabase.rpc('import_baplie_staging_transactional')</v>
       </c>
       <c r="D70" t="str">
-        <v>Atomic breakbulk import (converted from non-atomic path in QA loop). Auth: active.</v>
+        <v>Atomically replaces Baplie staging for a voyage. Auth: authenticated+active+admin; anon revoked.</v>
       </c>
       <c r="E70" t="str">
         <v>Verified</v>
@@ -2646,10 +2646,10 @@
         <v>-</v>
       </c>
       <c r="H70" t="str">
-        <v>Vitest + SQL-contract</v>
+        <v>Vitest</v>
       </c>
       <c r="I70" t="str">
-        <v>breakbulkImport.ts; 20260623095500_*.sql</v>
+        <v>baplieImport.ts</v>
       </c>
       <c r="J70" t="str">
         <v>-</v>
@@ -2657,16 +2657,16 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>RPC-25</v>
+        <v>RPC-24</v>
       </c>
       <c r="B71" t="str">
-        <v>Granito</v>
+        <v>Manifestos &amp; EDI</v>
       </c>
       <c r="C71" t="str">
-        <v>As the platform I call supabase.rpc('import_granite_manifest_transactional')</v>
+        <v>As the platform I call supabase.rpc('import_breakbulk_manifest_transactional')</v>
       </c>
       <c r="D71" t="str">
-        <v>Atomic Granito manifest import. Auth: active.</v>
+        <v>Atomic breakbulk import (converted from non-atomic path in QA loop). Auth: active.</v>
       </c>
       <c r="E71" t="str">
         <v>Verified</v>
@@ -2678,10 +2678,10 @@
         <v>-</v>
       </c>
       <c r="H71" t="str">
-        <v>Vitest</v>
+        <v>Vitest + SQL-contract</v>
       </c>
       <c r="I71" t="str">
-        <v>graniteImport.ts</v>
+        <v>breakbulkImport.ts; 20260623095500_*.sql</v>
       </c>
       <c r="J71" t="str">
         <v>-</v>
@@ -2689,19 +2689,19 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>RPC-26</v>
+        <v>RPC-25</v>
       </c>
       <c r="B72" t="str">
-        <v>Manifestos</v>
+        <v>Granito</v>
       </c>
       <c r="C72" t="str">
-        <v>As the platform I call supabase.rpc('import_manifest_transactional')</v>
+        <v>As the platform I call supabase.rpc('import_granite_manifest_transactional')</v>
       </c>
       <c r="D72" t="str">
-        <v>Atomic CNTR import core (duplicate hash 23505, rate limit P0429). Auth: authenticated; internal identity/RLS.</v>
+        <v>Atomic Granito manifest import. Auth: active.</v>
       </c>
       <c r="E72" t="str">
-        <v>Tested-Pass</v>
+        <v>Verified</v>
       </c>
       <c r="F72" t="str">
         <v>-</v>
@@ -2710,10 +2710,10 @@
         <v>-</v>
       </c>
       <c r="H72" t="str">
-        <v>Integration (not run)</v>
+        <v>Vitest</v>
       </c>
       <c r="I72" t="str">
-        <v>manifestImport.ts; supabase.integration.test.ts</v>
+        <v>graniteImport.ts</v>
       </c>
       <c r="J72" t="str">
         <v>-</v>
@@ -2721,19 +2721,19 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>RPC-27</v>
+        <v>RPC-26</v>
       </c>
       <c r="B73" t="str">
         <v>Manifestos</v>
       </c>
       <c r="C73" t="str">
-        <v>As the platform I call supabase.rpc('import_manifest_with_postprocess_transactional')</v>
+        <v>As the platform I call supabase.rpc('import_manifest_transactional')</v>
       </c>
       <c r="D73" t="str">
-        <v>Imports manifest, POL/POD schedules, contacts, canonical gate and post-processed billing in one transaction. Auth: PUBLIC/anon revoked; authenticated.</v>
+        <v>Atomic CNTR import core (duplicate hash 23505, rate limit P0429). Auth: authenticated; internal identity/RLS.</v>
       </c>
       <c r="E73" t="str">
-        <v>Verified</v>
+        <v>Tested-Pass</v>
       </c>
       <c r="F73" t="str">
         <v>-</v>
@@ -2742,10 +2742,10 @@
         <v>-</v>
       </c>
       <c r="H73" t="str">
-        <v>Vitest</v>
+        <v>Integration (not run)</v>
       </c>
       <c r="I73" t="str">
-        <v>manifestImport.ts</v>
+        <v>manifestImport.ts; supabase.integration.test.ts</v>
       </c>
       <c r="J73" t="str">
         <v>-</v>
@@ -2753,16 +2753,16 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>RPC-28</v>
+        <v>RPC-27</v>
       </c>
       <c r="B74" t="str">
-        <v>Manifestos &amp; EDI</v>
+        <v>Manifestos</v>
       </c>
       <c r="C74" t="str">
-        <v>As the platform I call supabase.rpc('import_vazios_bookings_transactional')</v>
+        <v>As the platform I call supabase.rpc('import_manifest_with_postprocess_transactional')</v>
       </c>
       <c r="D74" t="str">
-        <v>Atomic empties-booking import per voyage. Auth: active.</v>
+        <v>Imports manifest, POL/POD schedules, contacts, canonical gate and post-processed billing in one transaction. Auth: PUBLIC/anon revoked; authenticated.</v>
       </c>
       <c r="E74" t="str">
         <v>Verified</v>
@@ -2777,7 +2777,7 @@
         <v>Vitest</v>
       </c>
       <c r="I74" t="str">
-        <v>vaziosImport.ts</v>
+        <v>manifestImport.ts</v>
       </c>
       <c r="J74" t="str">
         <v>-</v>
@@ -2785,16 +2785,16 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>RPC-29</v>
+        <v>RPC-28</v>
       </c>
       <c r="B75" t="str">
         <v>Manifestos &amp; EDI</v>
       </c>
       <c r="C75" t="str">
-        <v>As the platform I call supabase.rpc('import_vazios_importacao_transactional')</v>
+        <v>As the platform I call supabase.rpc('import_vazios_bookings_transactional')</v>
       </c>
       <c r="D75" t="str">
-        <v>Atomic import-empties import (converted in QA loop). Auth: active.</v>
+        <v>Atomic empties-booking import per voyage. Auth: active.</v>
       </c>
       <c r="E75" t="str">
         <v>Verified</v>
@@ -2806,10 +2806,10 @@
         <v>-</v>
       </c>
       <c r="H75" t="str">
-        <v>Vitest + SQL-contract</v>
+        <v>Vitest</v>
       </c>
       <c r="I75" t="str">
-        <v>vaziosImportacaoImport.ts; 20260623111000_*.sql</v>
+        <v>vaziosImport.ts</v>
       </c>
       <c r="J75" t="str">
         <v>-</v>
@@ -2817,16 +2817,16 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>RPC-30</v>
+        <v>RPC-29</v>
       </c>
       <c r="B76" t="str">
-        <v>Veículos</v>
+        <v>Manifestos &amp; EDI</v>
       </c>
       <c r="C76" t="str">
-        <v>As the platform I call supabase.rpc('import_vehicle_rows_transactional')</v>
+        <v>As the platform I call supabase.rpc('import_vazios_importacao_transactional')</v>
       </c>
       <c r="D76" t="str">
-        <v>Atomically inserts vehicles; relationships validated by trigger. Auth: authenticated+active; anon revoked.</v>
+        <v>Atomic import-empties import (converted in QA loop). Auth: active.</v>
       </c>
       <c r="E76" t="str">
         <v>Verified</v>
@@ -2838,10 +2838,10 @@
         <v>-</v>
       </c>
       <c r="H76" t="str">
-        <v>Vitest</v>
+        <v>Vitest + SQL-contract</v>
       </c>
       <c r="I76" t="str">
-        <v>vehicleImport.ts</v>
+        <v>vaziosImportacaoImport.ts; 20260623111000_*.sql</v>
       </c>
       <c r="J76" t="str">
         <v>-</v>
@@ -2849,19 +2849,19 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>RPC-31</v>
+        <v>RPC-30</v>
       </c>
       <c r="B77" t="str">
-        <v>Faturamento / Ledger</v>
+        <v>Veículos</v>
       </c>
       <c r="C77" t="str">
-        <v>As the platform I call supabase.rpc('link_invoice_to_ledger')</v>
+        <v>As the platform I call supabase.rpc('import_vehicle_rows_transactional')</v>
       </c>
       <c r="D77" t="str">
-        <v>Links a created invoice to receivables/ledger. Auth: invoked by ledger wrappers.</v>
+        <v>Atomically inserts vehicles; relationships validated by trigger. Auth: authenticated+active; anon revoked.</v>
       </c>
       <c r="E77" t="str">
-        <v>Tested-Pass</v>
+        <v>Verified</v>
       </c>
       <c r="F77" t="str">
         <v>-</v>
@@ -2870,10 +2870,10 @@
         <v>-</v>
       </c>
       <c r="H77" t="str">
-        <v>Integration (not run)</v>
+        <v>Vitest</v>
       </c>
       <c r="I77" t="str">
-        <v>billing.ts; supabase.integration.test.ts</v>
+        <v>vehicleImport.ts</v>
       </c>
       <c r="J77" t="str">
         <v>-</v>
@@ -2881,19 +2881,19 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>RPC-32</v>
+        <v>RPC-31</v>
       </c>
       <c r="B78" t="str">
-        <v>Taxas Locais</v>
+        <v>Faturamento / Ledger</v>
       </c>
       <c r="C78" t="str">
-        <v>As the platform I call supabase.rpc('list_bl_local_charge_lines')</v>
+        <v>As the platform I call supabase.rpc('link_invoice_to_ledger')</v>
       </c>
       <c r="D78" t="str">
-        <v>Reads charge lines/items per B/L. Auth: PUBLIC revoked; authenticated; NO internal check.</v>
+        <v>Links a created invoice to receivables/ledger. Auth: invoked by ledger wrappers.</v>
       </c>
       <c r="E78" t="str">
-        <v>Verified</v>
+        <v>Tested-Pass</v>
       </c>
       <c r="F78" t="str">
         <v>-</v>
@@ -2902,30 +2902,30 @@
         <v>-</v>
       </c>
       <c r="H78" t="str">
-        <v>SQL-contract</v>
+        <v>Integration (not run)</v>
       </c>
       <c r="I78" t="str">
-        <v>chargeOperationsService.ts; 016_local_charges_stage_a.sql</v>
+        <v>billing.ts; supabase.integration.test.ts</v>
       </c>
       <c r="J78" t="str">
-        <v>RESOLVED: is_active_user() gate added in 20260624100100_guard_definer_rpcs_active_user.sql (ADR 0004); SQL readers converted to plpgsql (query preserved via RETURN QUERY). definerActiveUserGuardMigration.test.ts green. Migrations applied cleanly to the PR Supabase preview branch (all tasks green); production grant application on merge/deploy.</v>
+        <v>-</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>RPC-33</v>
+        <v>RPC-32</v>
       </c>
       <c r="B79" t="str">
-        <v>Faturamento / Ledger</v>
+        <v>Taxas Locais</v>
       </c>
       <c r="C79" t="str">
-        <v>As the platform I call supabase.rpc('list_consolidatable_receivables')</v>
+        <v>As the platform I call supabase.rpc('list_bl_local_charge_lines')</v>
       </c>
       <c r="D79" t="str">
-        <v>Reads balances/eligibility and open links for consolidation. Auth: authenticated+active.</v>
+        <v>Reads charge lines/items per B/L. Auth: PUBLIC revoked; authenticated; NO internal check.</v>
       </c>
       <c r="E79" t="str">
-        <v>Tested-Pass</v>
+        <v>Verified</v>
       </c>
       <c r="F79" t="str">
         <v>-</v>
@@ -2934,30 +2934,30 @@
         <v>-</v>
       </c>
       <c r="H79" t="str">
-        <v>Integration (not run)</v>
+        <v>SQL-contract + Runtime (prod)</v>
       </c>
       <c r="I79" t="str">
-        <v>billingLedger.ts; supabase.integration.test.ts</v>
+        <v>chargeOperationsService.ts; 016_local_charges_stage_a.sql</v>
       </c>
       <c r="J79" t="str">
-        <v>-</v>
+        <v>RESOLVED &amp; RUNTIME-VERIFIED in production (fgmkhbzhaeebrsizwccx, 2026-06-24): language=plpgsql, is_active_user() guard present, anon EXECUTE=false. Migration 20260624100100 (ADR 0004); readers converted to plpgsql with query preserved via RETURN QUERY.</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>RPC-34</v>
+        <v>RPC-33</v>
       </c>
       <c r="B80" t="str">
-        <v>Revisão / Clientes</v>
+        <v>Faturamento / Ledger</v>
       </c>
       <c r="C80" t="str">
-        <v>As the platform I call supabase.rpc('list_customer_reconciliation_queue')</v>
+        <v>As the platform I call supabase.rpc('list_consolidatable_receivables')</v>
       </c>
       <c r="D80" t="str">
-        <v>Reads the reconciliation queue. Auth: PUBLIC revoked; authenticated; NO internal check.</v>
+        <v>Reads balances/eligibility and open links for consolidation. Auth: authenticated+active.</v>
       </c>
       <c r="E80" t="str">
-        <v>Verified</v>
+        <v>Tested-Pass</v>
       </c>
       <c r="F80" t="str">
         <v>-</v>
@@ -2966,27 +2966,27 @@
         <v>-</v>
       </c>
       <c r="H80" t="str">
-        <v>SQL-contract</v>
+        <v>Integration (not run)</v>
       </c>
       <c r="I80" t="str">
-        <v>chargeReconciliationService.ts; 025_*.sql</v>
+        <v>billingLedger.ts; supabase.integration.test.ts</v>
       </c>
       <c r="J80" t="str">
-        <v>RESOLVED: is_active_user() gate added in 20260624100100_guard_definer_rpcs_active_user.sql (ADR 0004); SQL readers converted to plpgsql (query preserved via RETURN QUERY). definerActiveUserGuardMigration.test.ts green. Migrations applied cleanly to the PR Supabase preview branch (all tasks green); production grant application on merge/deploy.</v>
+        <v>-</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>RPC-35</v>
+        <v>RPC-34</v>
       </c>
       <c r="B81" t="str">
-        <v>Faturamento</v>
+        <v>Revisão / Clientes</v>
       </c>
       <c r="C81" t="str">
-        <v>As the platform I call supabase.rpc('list_invoice_details')</v>
+        <v>As the platform I call supabase.rpc('list_customer_reconciliation_queue')</v>
       </c>
       <c r="D81" t="str">
-        <v>Reads invoice, B/Ls, items and payments; client backfills consolidated/PIX best-effort. Auth: authenticated+active+admin; INVOKER.</v>
+        <v>Reads the reconciliation queue. Auth: PUBLIC revoked; authenticated; NO internal check.</v>
       </c>
       <c r="E81" t="str">
         <v>Verified</v>
@@ -2998,30 +2998,30 @@
         <v>-</v>
       </c>
       <c r="H81" t="str">
-        <v>Vitest</v>
+        <v>SQL-contract + Runtime (prod)</v>
       </c>
       <c r="I81" t="str">
-        <v>billing.ts</v>
+        <v>chargeReconciliationService.ts; 025_*.sql</v>
       </c>
       <c r="J81" t="str">
-        <v>-</v>
+        <v>RESOLVED &amp; RUNTIME-VERIFIED in production (fgmkhbzhaeebrsizwccx, 2026-06-24): language=plpgsql, is_active_user() guard present, anon EXECUTE=false. Migration 20260624100100 (ADR 0004); readers converted to plpgsql with query preserved via RETURN QUERY.</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>RPC-36</v>
+        <v>RPC-35</v>
       </c>
       <c r="B82" t="str">
-        <v>Faturamento / Ledger</v>
+        <v>Faturamento</v>
       </c>
       <c r="C82" t="str">
-        <v>As the platform I call supabase.rpc('list_invoice_refunds')</v>
+        <v>As the platform I call supabase.rpc('list_invoice_details')</v>
       </c>
       <c r="D82" t="str">
-        <v>Read-only pending/settled refunds (INVOKER). Auth: admin RLS on invoice_refunds; authenticated.</v>
+        <v>Reads invoice, B/Ls, items and payments; client backfills consolidated/PIX best-effort. Auth: authenticated+active+admin; INVOKER.</v>
       </c>
       <c r="E82" t="str">
-        <v>Tested-Pass</v>
+        <v>Verified</v>
       </c>
       <c r="F82" t="str">
         <v>-</v>
@@ -3030,10 +3030,10 @@
         <v>-</v>
       </c>
       <c r="H82" t="str">
-        <v>SQL-contract</v>
+        <v>Vitest</v>
       </c>
       <c r="I82" t="str">
-        <v>billingLedger.ts; settleInvoiceRefundsMigration.test.ts</v>
+        <v>billing.ts</v>
       </c>
       <c r="J82" t="str">
         <v>-</v>
@@ -3041,19 +3041,19 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>RPC-37</v>
+        <v>RPC-36</v>
       </c>
       <c r="B83" t="str">
-        <v>Taxas Locais</v>
+        <v>Faturamento / Ledger</v>
       </c>
       <c r="C83" t="str">
-        <v>As the platform I call supabase.rpc('list_manual_charge_items_for_bl')</v>
+        <v>As the platform I call supabase.rpc('list_invoice_refunds')</v>
       </c>
       <c r="D83" t="str">
-        <v>Reads eligible manual items and overrides. Auth: PUBLIC revoked; authenticated; NO internal check.</v>
+        <v>Read-only pending/settled refunds (INVOKER). Auth: admin RLS on invoice_refunds; authenticated.</v>
       </c>
       <c r="E83" t="str">
-        <v>Verified</v>
+        <v>Tested-Pass</v>
       </c>
       <c r="F83" t="str">
         <v>-</v>
@@ -3065,27 +3065,27 @@
         <v>SQL-contract</v>
       </c>
       <c r="I83" t="str">
-        <v>chargeOperationsService.ts; 019_*.sql</v>
+        <v>billingLedger.ts; settleInvoiceRefundsMigration.test.ts</v>
       </c>
       <c r="J83" t="str">
-        <v>RESOLVED: is_active_user() gate added in 20260624100100_guard_definer_rpcs_active_user.sql (ADR 0004); SQL readers converted to plpgsql (query preserved via RETURN QUERY). definerActiveUserGuardMigration.test.ts green. Migrations applied cleanly to the PR Supabase preview branch (all tasks green); production grant application on merge/deploy.</v>
+        <v>-</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>RPC-38</v>
+        <v>RPC-37</v>
       </c>
       <c r="B84" t="str">
         <v>Taxas Locais</v>
       </c>
       <c r="C84" t="str">
-        <v>As the platform I call supabase.rpc('mark_bl_charges_reviewed')</v>
+        <v>As the platform I call supabase.rpc('list_manual_charge_items_for_bl')</v>
       </c>
       <c r="D84" t="str">
-        <v>Moves calculations/B/L to reviewed and audits. Auth: authenticated+active.</v>
+        <v>Reads eligible manual items and overrides. Auth: PUBLIC revoked; authenticated; NO internal check.</v>
       </c>
       <c r="E84" t="str">
-        <v>Spec’d</v>
+        <v>Verified</v>
       </c>
       <c r="F84" t="str">
         <v>-</v>
@@ -3094,27 +3094,27 @@
         <v>-</v>
       </c>
       <c r="H84" t="str">
-        <v>Static</v>
+        <v>SQL-contract + Runtime (prod)</v>
       </c>
       <c r="I84" t="str">
-        <v>chargeOperationsService.ts</v>
+        <v>chargeOperationsService.ts; 019_*.sql</v>
       </c>
       <c r="J84" t="str">
-        <v>-</v>
+        <v>RESOLVED &amp; RUNTIME-VERIFIED in production (fgmkhbzhaeebrsizwccx, 2026-06-24): language=plpgsql, is_active_user() guard present, anon EXECUTE=false. Migration 20260624100100 (ADR 0004); readers converted to plpgsql with query preserved via RETURN QUERY.</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>RPC-39</v>
+        <v>RPC-38</v>
       </c>
       <c r="B85" t="str">
-        <v>Taxas Locais / Faturamento</v>
+        <v>Taxas Locais</v>
       </c>
       <c r="C85" t="str">
-        <v>As the platform I call supabase.rpc('mark_bl_ready_and_create_invoice')</v>
+        <v>As the platform I call supabase.rpc('mark_bl_charges_reviewed')</v>
       </c>
       <c r="D85" t="str">
-        <v>Marks ready and creates invoice+ledger atomically; any failure rolls back both. Auth: authenticated+active+admin; INVOKER.</v>
+        <v>Moves calculations/B/L to reviewed and audits. Auth: authenticated+active.</v>
       </c>
       <c r="E85" t="str">
         <v>Spec’d</v>
@@ -3129,7 +3129,7 @@
         <v>Static</v>
       </c>
       <c r="I85" t="str">
-        <v>billing.ts</v>
+        <v>chargeOperationsService.ts</v>
       </c>
       <c r="J85" t="str">
         <v>-</v>
@@ -3137,19 +3137,19 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>RPC-40</v>
+        <v>RPC-39</v>
       </c>
       <c r="B86" t="str">
         <v>Taxas Locais / Faturamento</v>
       </c>
       <c r="C86" t="str">
-        <v>As the platform I call supabase.rpc('mark_bl_ready_for_billing')</v>
+        <v>As the platform I call supabase.rpc('mark_bl_ready_and_create_invoice')</v>
       </c>
       <c r="D86" t="str">
-        <v>Revalidates canonical gate/client/lines/BRL/active table; updates calc/B/L, audits, may auto-issue. Auth: authenticated+active; anon revoked.</v>
+        <v>Marks ready and creates invoice+ledger atomically; any failure rolls back both. Auth: authenticated+active+admin; INVOKER.</v>
       </c>
       <c r="E86" t="str">
-        <v>Tested-Pass</v>
+        <v>Spec’d</v>
       </c>
       <c r="F86" t="str">
         <v>-</v>
@@ -3158,10 +3158,10 @@
         <v>-</v>
       </c>
       <c r="H86" t="str">
-        <v>SQL-contract</v>
+        <v>Static</v>
       </c>
       <c r="I86" t="str">
-        <v>chargeOperationsService.ts; guardInvoiceableReadyStateMigration.test.ts</v>
+        <v>billing.ts</v>
       </c>
       <c r="J86" t="str">
         <v>-</v>
@@ -3169,19 +3169,19 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>RPC-41</v>
+        <v>RPC-40</v>
       </c>
       <c r="B87" t="str">
-        <v>Faturamento</v>
+        <v>Taxas Locais / Faturamento</v>
       </c>
       <c r="C87" t="str">
-        <v>As the platform I call supabase.rpc('mark_bls_ready_and_create_invoice')</v>
+        <v>As the platform I call supabase.rpc('mark_bl_ready_for_billing')</v>
       </c>
       <c r="D87" t="str">
-        <v>Batch variant of mark-ready + atomic invoice creation. Auth: authenticated+active+admin.</v>
+        <v>Revalidates canonical gate/client/lines/BRL/active table; updates calc/B/L, audits, may auto-issue. Auth: authenticated+active; anon revoked.</v>
       </c>
       <c r="E87" t="str">
-        <v>Verified</v>
+        <v>Tested-Pass</v>
       </c>
       <c r="F87" t="str">
         <v>-</v>
@@ -3190,10 +3190,10 @@
         <v>-</v>
       </c>
       <c r="H87" t="str">
-        <v>Vitest</v>
+        <v>SQL-contract</v>
       </c>
       <c r="I87" t="str">
-        <v>billing.ts</v>
+        <v>chargeOperationsService.ts; guardInvoiceableReadyStateMigration.test.ts</v>
       </c>
       <c r="J87" t="str">
         <v>-</v>
@@ -3201,16 +3201,16 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>RPC-42</v>
+        <v>RPC-41</v>
       </c>
       <c r="B88" t="str">
-        <v>Portal / Auth</v>
+        <v>Faturamento</v>
       </c>
       <c r="C88" t="str">
-        <v>As the platform I call supabase.rpc('portal_get_session_overview_v2')</v>
+        <v>As the platform I call supabase.rpc('mark_bls_ready_and_create_invoice')</v>
       </c>
       <c r="D88" t="str">
-        <v>Reads overview and updates last_login_at; requires auth.uid()+active linked account. Auth: PUBLIC revoked; authenticated.</v>
+        <v>Batch variant of mark-ready + atomic invoice creation. Auth: authenticated+active+admin.</v>
       </c>
       <c r="E88" t="str">
         <v>Verified</v>
@@ -3225,7 +3225,7 @@
         <v>Vitest</v>
       </c>
       <c r="I88" t="str">
-        <v>usePortalAuth.tsx</v>
+        <v>billing.ts</v>
       </c>
       <c r="J88" t="str">
         <v>-</v>
@@ -3233,16 +3233,16 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>RPC-43</v>
+        <v>RPC-42</v>
       </c>
       <c r="B89" t="str">
-        <v>Portal / Operação</v>
+        <v>Portal / Auth</v>
       </c>
       <c r="C89" t="str">
-        <v>As the platform I call supabase.rpc('portal_list_operation_bls')</v>
+        <v>As the platform I call supabase.rpc('portal_get_session_overview_v2')</v>
       </c>
       <c r="D89" t="str">
-        <v>Reads own B/Ls/containers and derives free time/demurrage; CE-gated. Auth: current_portal_customer_id() + CE; grant authenticated,anon.</v>
+        <v>Reads overview and updates last_login_at; requires auth.uid()+active linked account. Auth: PUBLIC revoked; authenticated.</v>
       </c>
       <c r="E89" t="str">
         <v>Verified</v>
@@ -3254,30 +3254,30 @@
         <v>-</v>
       </c>
       <c r="H89" t="str">
-        <v>SQL-contract</v>
+        <v>Vitest</v>
       </c>
       <c r="I89" t="str">
-        <v>portalOperation.ts; portalCeMercanteGateMigration.test.ts</v>
+        <v>usePortalAuth.tsx</v>
       </c>
       <c r="J89" t="str">
-        <v>RESOLVED: anon EXECUTE revoked in 20260624100000_revoke_anon_portal_read_rpcs.sql (ADR 0013). definerActiveUserGuardMigration.test.ts green. Migrations applied cleanly to the PR Supabase preview branch (all tasks green); production grant application on merge/deploy.</v>
+        <v>-</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>RPC-44</v>
+        <v>RPC-43</v>
       </c>
       <c r="B90" t="str">
-        <v>Conciliação PIX / Ledger</v>
+        <v>Portal / Operação</v>
       </c>
       <c r="C90" t="str">
-        <v>As the platform I call supabase.rpc('reconcile_invoice_payment_by_txid')</v>
+        <v>As the platform I call supabase.rpc('portal_list_operation_bls')</v>
       </c>
       <c r="D90" t="str">
-        <v>Strict TXID match; records payment/settlement; updates invoice/receivables. Auth: authenticated+active+admin.</v>
+        <v>Reads own B/Ls/containers and derives free time/demurrage; CE-gated. Auth: current_portal_customer_id() + CE; grant authenticated,anon.</v>
       </c>
       <c r="E90" t="str">
-        <v>Tested-Pass</v>
+        <v>Verified</v>
       </c>
       <c r="F90" t="str">
         <v>-</v>
@@ -3286,27 +3286,27 @@
         <v>-</v>
       </c>
       <c r="H90" t="str">
-        <v>Integration (not run)</v>
+        <v>SQL-contract + Runtime (prod)</v>
       </c>
       <c r="I90" t="str">
-        <v>billingLedger.ts; supabase.integration.test.ts</v>
+        <v>portalOperation.ts; portalCeMercanteGateMigration.test.ts</v>
       </c>
       <c r="J90" t="str">
-        <v>-</v>
+        <v>RESOLVED &amp; RUNTIME-VERIFIED: anon EXECUTE=false confirmed in production (fgmkhbzhaeebrsizwccx, 2026-06-24); authenticated EXECUTE=true. Migration 20260624100000 (ADR 0013), asserted by definerActiveUserGuardMigration.test.ts.</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>RPC-45</v>
+        <v>RPC-44</v>
       </c>
       <c r="B91" t="str">
-        <v>Faturamento</v>
+        <v>Conciliação PIX / Ledger</v>
       </c>
       <c r="C91" t="str">
-        <v>As the platform I call supabase.rpc('register_invoice_payment')</v>
+        <v>As the platform I call supabase.rpc('reconcile_invoice_payment_by_txid')</v>
       </c>
       <c r="D91" t="str">
-        <v>Inserts payment, updates invoice/B/L balance/status, audits. Auth: authenticated+active+admin; INVOKER.</v>
+        <v>Strict TXID match; records payment/settlement; updates invoice/receivables. Auth: authenticated+active+admin.</v>
       </c>
       <c r="E91" t="str">
         <v>Tested-Pass</v>
@@ -3321,7 +3321,7 @@
         <v>Integration (not run)</v>
       </c>
       <c r="I91" t="str">
-        <v>billing.ts; supabase.integration.test.ts</v>
+        <v>billingLedger.ts; supabase.integration.test.ts</v>
       </c>
       <c r="J91" t="str">
         <v>-</v>
@@ -3329,16 +3329,16 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>RPC-46</v>
+        <v>RPC-45</v>
       </c>
       <c r="B92" t="str">
-        <v>Faturamento / Ledger</v>
+        <v>Faturamento</v>
       </c>
       <c r="C92" t="str">
-        <v>As the platform I call supabase.rpc('register_ledger_invoice_payment')</v>
+        <v>As the platform I call supabase.rpc('register_invoice_payment')</v>
       </c>
       <c r="D92" t="str">
-        <v>Allocates in ledger, updates receivables/links/invoice/B/Ls, lifecycle + refund for manual overpayment. Auth: authenticated+active+admin.</v>
+        <v>Inserts payment, updates invoice/B/L balance/status, audits. Auth: authenticated+active+admin; INVOKER.</v>
       </c>
       <c r="E92" t="str">
         <v>Tested-Pass</v>
@@ -3350,10 +3350,10 @@
         <v>-</v>
       </c>
       <c r="H92" t="str">
-        <v>SQL-contract</v>
+        <v>Integration (not run)</v>
       </c>
       <c r="I92" t="str">
-        <v>billingLedger.ts; ledgerPartialPaymentsMigration.test.ts</v>
+        <v>billing.ts; supabase.integration.test.ts</v>
       </c>
       <c r="J92" t="str">
         <v>-</v>
@@ -3361,19 +3361,19 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>RPC-47</v>
+        <v>RPC-46</v>
       </c>
       <c r="B93" t="str">
-        <v>Revisão / Clientes</v>
+        <v>Faturamento / Ledger</v>
       </c>
       <c r="C93" t="str">
-        <v>As the platform I call supabase.rpc('reject_customer_reconciliation')</v>
+        <v>As the platform I call supabase.rpc('register_ledger_invoice_payment')</v>
       </c>
       <c r="D93" t="str">
-        <v>Rejects queue, updates B/L and audits. Auth: authenticated+active.</v>
+        <v>Allocates in ledger, updates receivables/links/invoice/B/Ls, lifecycle + refund for manual overpayment. Auth: authenticated+active+admin.</v>
       </c>
       <c r="E93" t="str">
-        <v>Spec’d</v>
+        <v>Tested-Pass</v>
       </c>
       <c r="F93" t="str">
         <v>-</v>
@@ -3382,10 +3382,10 @@
         <v>-</v>
       </c>
       <c r="H93" t="str">
-        <v>Static</v>
+        <v>SQL-contract</v>
       </c>
       <c r="I93" t="str">
-        <v>chargeReconciliationService.ts</v>
+        <v>billingLedger.ts; ledgerPartialPaymentsMigration.test.ts</v>
       </c>
       <c r="J93" t="str">
         <v>-</v>
@@ -3393,19 +3393,19 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>RPC-48</v>
+        <v>RPC-47</v>
       </c>
       <c r="B94" t="str">
-        <v>Chegadas/Saídas</v>
+        <v>Revisão / Clientes</v>
       </c>
       <c r="C94" t="str">
-        <v>As the platform I call supabase.rpc('reorder_vessel_schedules')</v>
+        <v>As the platform I call supabase.rpc('reject_customer_reconciliation')</v>
       </c>
       <c r="D94" t="str">
-        <v>Persists a new display order for vessel_schedules. Auth: active.</v>
+        <v>Rejects queue, updates B/L and audits. Auth: authenticated+active.</v>
       </c>
       <c r="E94" t="str">
-        <v>Verified</v>
+        <v>Spec’d</v>
       </c>
       <c r="F94" t="str">
         <v>-</v>
@@ -3414,10 +3414,10 @@
         <v>-</v>
       </c>
       <c r="H94" t="str">
-        <v>Vitest</v>
+        <v>Static</v>
       </c>
       <c r="I94" t="str">
-        <v>vesselSchedules.ts</v>
+        <v>chargeReconciliationService.ts</v>
       </c>
       <c r="J94" t="str">
         <v>-</v>
@@ -3425,16 +3425,16 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>RPC-49</v>
+        <v>RPC-48</v>
       </c>
       <c r="B95" t="str">
-        <v>Vazios de Importação</v>
+        <v>Chegadas/Saídas</v>
       </c>
       <c r="C95" t="str">
-        <v>As the platform I call supabase.rpc('replace_vazios_from_baplie_transactional')</v>
+        <v>As the platform I call supabase.rpc('reorder_vessel_schedules')</v>
       </c>
       <c r="D95" t="str">
-        <v>Atomically replaces import empties from Baplie source. Auth: active.</v>
+        <v>Persists a new display order for vessel_schedules. Auth: active.</v>
       </c>
       <c r="E95" t="str">
         <v>Verified</v>
@@ -3449,7 +3449,7 @@
         <v>Vitest</v>
       </c>
       <c r="I95" t="str">
-        <v>vaziosImportacaoImport.ts</v>
+        <v>vesselSchedules.ts</v>
       </c>
       <c r="J95" t="str">
         <v>-</v>
@@ -3457,19 +3457,19 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>RPC-50</v>
+        <v>RPC-49</v>
       </c>
       <c r="B96" t="str">
-        <v>Conciliação PIX / Demurrage</v>
+        <v>Vazios de Importação</v>
       </c>
       <c r="C96" t="str">
-        <v>As the platform I call supabase.rpc('reverse_demurrage_payment')</v>
+        <v>As the platform I call supabase.rpc('replace_vazios_from_baplie_transactional')</v>
       </c>
       <c r="D96" t="str">
-        <v>Removes demurrage settlement, reverts status, audits mandatory justification. Auth: authenticated+active+admin; justification required.</v>
+        <v>Atomically replaces import empties from Baplie source. Auth: active.</v>
       </c>
       <c r="E96" t="str">
-        <v>Tested-Pass</v>
+        <v>Verified</v>
       </c>
       <c r="F96" t="str">
         <v>-</v>
@@ -3478,10 +3478,10 @@
         <v>-</v>
       </c>
       <c r="H96" t="str">
-        <v>SQL-contract</v>
+        <v>Vitest</v>
       </c>
       <c r="I96" t="str">
-        <v>reconciliacao.ts; reversalJustificationMigration.test.ts</v>
+        <v>vaziosImportacaoImport.ts</v>
       </c>
       <c r="J96" t="str">
         <v>-</v>
@@ -3489,16 +3489,16 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>RPC-51</v>
+        <v>RPC-50</v>
       </c>
       <c r="B97" t="str">
-        <v>Conciliação PIX / Ledger</v>
+        <v>Conciliação PIX / Demurrage</v>
       </c>
       <c r="C97" t="str">
-        <v>As the platform I call supabase.rpc('reverse_invoice_payment')</v>
+        <v>As the platform I call supabase.rpc('reverse_demurrage_payment')</v>
       </c>
       <c r="D97" t="str">
-        <v>Reverses settlement/payment, reopens receivables/links, fixes invoice and bls.financial_status, audits. Auth: authenticated+active+admin; justification required.</v>
+        <v>Removes demurrage settlement, reverts status, audits mandatory justification. Auth: authenticated+active+admin; justification required.</v>
       </c>
       <c r="E97" t="str">
         <v>Tested-Pass</v>
@@ -3513,7 +3513,7 @@
         <v>SQL-contract</v>
       </c>
       <c r="I97" t="str">
-        <v>reconciliacao.ts; reversalBlsFinancialStatusMigration.test.ts</v>
+        <v>reconciliacao.ts; reversalJustificationMigration.test.ts</v>
       </c>
       <c r="J97" t="str">
         <v>-</v>
@@ -3521,19 +3521,19 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>RPC-52</v>
+        <v>RPC-51</v>
       </c>
       <c r="B98" t="str">
-        <v>Faturamento</v>
+        <v>Conciliação PIX / Ledger</v>
       </c>
       <c r="C98" t="str">
-        <v>As the platform I call supabase.rpc('run_billing_for_import_batch')</v>
+        <v>As the platform I call supabase.rpc('reverse_invoice_payment')</v>
       </c>
       <c r="D98" t="str">
-        <v>Runs billing post-processing for an import batch (now decoupled from import fn). Auth: active+admin.</v>
+        <v>Reverses settlement/payment, reopens receivables/links, fixes invoice and bls.financial_status, audits. Auth: authenticated+active+admin; justification required.</v>
       </c>
       <c r="E98" t="str">
-        <v>Verified</v>
+        <v>Tested-Pass</v>
       </c>
       <c r="F98" t="str">
         <v>-</v>
@@ -3542,10 +3542,10 @@
         <v>-</v>
       </c>
       <c r="H98" t="str">
-        <v>Vitest</v>
+        <v>SQL-contract</v>
       </c>
       <c r="I98" t="str">
-        <v>billing.ts; 20260623130000_*.sql</v>
+        <v>reconciliacao.ts; reversalBlsFinancialStatusMigration.test.ts</v>
       </c>
       <c r="J98" t="str">
         <v>-</v>
@@ -3553,16 +3553,16 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>RPC-53</v>
+        <v>RPC-52</v>
       </c>
       <c r="B99" t="str">
-        <v>Demurrage</v>
+        <v>Faturamento</v>
       </c>
       <c r="C99" t="str">
-        <v>As the platform I call supabase.rpc('save_bl_demurrage_config')</v>
+        <v>As the platform I call supabase.rpc('run_billing_for_import_batch')</v>
       </c>
       <c r="D99" t="str">
-        <v>Atomically saves per-B/L demurrage config (converted in QA loop). Auth: active.</v>
+        <v>Runs billing post-processing for an import batch (now decoupled from import fn). Auth: active+admin.</v>
       </c>
       <c r="E99" t="str">
         <v>Verified</v>
@@ -3574,10 +3574,10 @@
         <v>-</v>
       </c>
       <c r="H99" t="str">
-        <v>Vitest + SQL-contract</v>
+        <v>Vitest</v>
       </c>
       <c r="I99" t="str">
-        <v>BlDemurrageSection.tsx; 20260623112000_*.sql</v>
+        <v>billing.ts; 20260623130000_*.sql</v>
       </c>
       <c r="J99" t="str">
         <v>-</v>
@@ -3585,19 +3585,19 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>RPC-54</v>
+        <v>RPC-53</v>
       </c>
       <c r="B100" t="str">
-        <v>B/L / Revisão / Demurrage</v>
+        <v>Demurrage</v>
       </c>
       <c r="C100" t="str">
-        <v>As the platform I call supabase.rpc('save_bl_review')</v>
+        <v>As the platform I call supabase.rpc('save_bl_demurrage_config')</v>
       </c>
       <c r="D100" t="str">
-        <v>Optimistic lock PT409, updates fields, recomputes gate/notes, audits real state, syncs queue. Auth: authenticated+active; p_changed_by=auth.uid().</v>
+        <v>Atomically saves per-B/L demurrage config (converted in QA loop). Auth: active.</v>
       </c>
       <c r="E100" t="str">
-        <v>Tested-Pass</v>
+        <v>Verified</v>
       </c>
       <c r="F100" t="str">
         <v>-</v>
@@ -3606,10 +3606,10 @@
         <v>-</v>
       </c>
       <c r="H100" t="str">
-        <v>SQL-contract + Integration (not run)</v>
+        <v>Vitest + SQL-contract</v>
       </c>
       <c r="I100" t="str">
-        <v>review.ts; reviewGateHardeningMigration.test.ts</v>
+        <v>BlDemurrageSection.tsx; 20260623112000_*.sql</v>
       </c>
       <c r="J100" t="str">
         <v>-</v>
@@ -3617,19 +3617,19 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>RPC-55</v>
+        <v>RPC-54</v>
       </c>
       <c r="B101" t="str">
-        <v>Granito / Revisão</v>
+        <v>B/L / Revisão / Demurrage</v>
       </c>
       <c r="C101" t="str">
-        <v>As the platform I call supabase.rpc('save_granite_bl_review')</v>
+        <v>As the platform I call supabase.rpc('save_bl_review')</v>
       </c>
       <c r="D101" t="str">
-        <v>Atomic Granito B/L review (converted in QA loop). Auth: active.</v>
+        <v>Optimistic lock PT409, updates fields, recomputes gate/notes, audits real state, syncs queue. Auth: authenticated+active; p_changed_by=auth.uid().</v>
       </c>
       <c r="E101" t="str">
-        <v>Verified</v>
+        <v>Tested-Pass</v>
       </c>
       <c r="F101" t="str">
         <v>-</v>
@@ -3638,10 +3638,10 @@
         <v>-</v>
       </c>
       <c r="H101" t="str">
-        <v>Vitest + SQL-contract</v>
+        <v>SQL-contract + Integration (not run)</v>
       </c>
       <c r="I101" t="str">
-        <v>review.ts; 20260623120000_*.sql</v>
+        <v>review.ts; reviewGateHardeningMigration.test.ts</v>
       </c>
       <c r="J101" t="str">
         <v>-</v>
@@ -3649,19 +3649,19 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>RPC-56</v>
+        <v>RPC-55</v>
       </c>
       <c r="B102" t="str">
-        <v>Clientes / Portal</v>
+        <v>Granito / Revisão</v>
       </c>
       <c r="C102" t="str">
-        <v>As the platform I call supabase.rpc('set_customer_portal_account_active')</v>
+        <v>As the platform I call supabase.rpc('save_granite_bl_review')</v>
       </c>
       <c r="D102" t="str">
-        <v>Toggles Portal account; blocks false active without auth_user_id/email. Auth: authenticated+active+admin.</v>
+        <v>Atomic Granito B/L review (converted in QA loop). Auth: active.</v>
       </c>
       <c r="E102" t="str">
-        <v>Spec’d</v>
+        <v>Verified</v>
       </c>
       <c r="F102" t="str">
         <v>-</v>
@@ -3670,10 +3670,10 @@
         <v>-</v>
       </c>
       <c r="H102" t="str">
-        <v>Static</v>
+        <v>Vitest + SQL-contract</v>
       </c>
       <c r="I102" t="str">
-        <v>customers.ts</v>
+        <v>review.ts; 20260623120000_*.sql</v>
       </c>
       <c r="J102" t="str">
         <v>-</v>
@@ -3681,19 +3681,19 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>RPC-57</v>
+        <v>RPC-56</v>
       </c>
       <c r="B103" t="str">
-        <v>Viagens / Manifestos</v>
+        <v>Clientes / Portal</v>
       </c>
       <c r="C103" t="str">
-        <v>As the platform I call supabase.rpc('set_import_batch_ce_master')</v>
+        <v>As the platform I call supabase.rpc('set_customer_portal_account_active')</v>
       </c>
       <c r="D103" t="str">
-        <v>Atomically sets CE Master on an import batch (converted in QA loop). Auth: active.</v>
+        <v>Toggles Portal account; blocks false active without auth_user_id/email. Auth: authenticated+active+admin.</v>
       </c>
       <c r="E103" t="str">
-        <v>Verified</v>
+        <v>Spec’d</v>
       </c>
       <c r="F103" t="str">
         <v>-</v>
@@ -3702,10 +3702,10 @@
         <v>-</v>
       </c>
       <c r="H103" t="str">
-        <v>Vitest + SQL-contract</v>
+        <v>Static</v>
       </c>
       <c r="I103" t="str">
-        <v>voyages.ts; 20260623110000_*.sql</v>
+        <v>customers.ts</v>
       </c>
       <c r="J103" t="str">
         <v>-</v>
@@ -3713,19 +3713,19 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>RPC-58</v>
+        <v>RPC-57</v>
       </c>
       <c r="B104" t="str">
-        <v>Faturamento / Ledger</v>
+        <v>Viagens / Manifestos</v>
       </c>
       <c r="C104" t="str">
-        <v>As the platform I call supabase.rpc('settle_invoice_refund')</v>
+        <v>As the platform I call supabase.rpc('set_import_batch_ce_master')</v>
       </c>
       <c r="D104" t="str">
-        <v>Moves refund pending -&gt; settled and audits. Auth: authenticated+active+admin.</v>
+        <v>Atomically sets CE Master on an import batch (converted in QA loop). Auth: active.</v>
       </c>
       <c r="E104" t="str">
-        <v>Tested-Pass</v>
+        <v>Verified</v>
       </c>
       <c r="F104" t="str">
         <v>-</v>
@@ -3734,10 +3734,10 @@
         <v>-</v>
       </c>
       <c r="H104" t="str">
-        <v>SQL-contract</v>
+        <v>Vitest + SQL-contract</v>
       </c>
       <c r="I104" t="str">
-        <v>billingLedger.ts; settleInvoiceRefundsMigration.test.ts</v>
+        <v>voyages.ts; 20260623110000_*.sql</v>
       </c>
       <c r="J104" t="str">
         <v>-</v>
@@ -3745,16 +3745,16 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>RPC-59</v>
+        <v>RPC-58</v>
       </c>
       <c r="B105" t="str">
         <v>Faturamento / Ledger</v>
       </c>
       <c r="C105" t="str">
-        <v>As the platform I call supabase.rpc('sync_local_charge_receivable')</v>
+        <v>As the platform I call supabase.rpc('settle_invoice_refund')</v>
       </c>
       <c r="D105" t="str">
-        <v>Synchronizes a B/L receivable from local charges. Auth: invoked by ledger flows.</v>
+        <v>Moves refund pending -&gt; settled and audits. Auth: authenticated+active+admin.</v>
       </c>
       <c r="E105" t="str">
         <v>Tested-Pass</v>
@@ -3766,10 +3766,10 @@
         <v>-</v>
       </c>
       <c r="H105" t="str">
-        <v>Integration (not run)</v>
+        <v>SQL-contract</v>
       </c>
       <c r="I105" t="str">
-        <v>billing.ts; supabase.integration.test.ts</v>
+        <v>billingLedger.ts; settleInvoiceRefundsMigration.test.ts</v>
       </c>
       <c r="J105" t="str">
         <v>-</v>
@@ -3777,19 +3777,19 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>RPC-60</v>
+        <v>RPC-59</v>
       </c>
       <c r="B106" t="str">
-        <v>Clientes</v>
+        <v>Faturamento / Ledger</v>
       </c>
       <c r="C106" t="str">
-        <v>As the platform I call supabase.rpc('update_customer_with_audit')</v>
+        <v>As the platform I call supabase.rpc('sync_local_charge_receivable')</v>
       </c>
       <c r="D106" t="str">
-        <v>Updates a customer with audited change set. Auth: active.</v>
+        <v>Synchronizes a B/L receivable from local charges. Auth: invoked by ledger flows.</v>
       </c>
       <c r="E106" t="str">
-        <v>Verified</v>
+        <v>Tested-Pass</v>
       </c>
       <c r="F106" t="str">
         <v>-</v>
@@ -3798,10 +3798,10 @@
         <v>-</v>
       </c>
       <c r="H106" t="str">
-        <v>Vitest</v>
+        <v>Integration (not run)</v>
       </c>
       <c r="I106" t="str">
-        <v>customers.ts</v>
+        <v>billing.ts; supabase.integration.test.ts</v>
       </c>
       <c r="J106" t="str">
         <v>-</v>
@@ -3809,19 +3809,19 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>RPC-61</v>
+        <v>RPC-60</v>
       </c>
       <c r="B107" t="str">
-        <v>Taxas Locais</v>
+        <v>Clientes</v>
       </c>
       <c r="C107" t="str">
-        <v>As the platform I call supabase.rpc('update_manual_bl_charge')</v>
+        <v>As the platform I call supabase.rpc('update_customer_with_audit')</v>
       </c>
       <c r="D107" t="str">
-        <v>Updates only an eligible manual line, recalculates, audits; blocks invoiced B/L. Auth: authenticated+active.</v>
+        <v>Updates a customer with audited change set. Auth: active.</v>
       </c>
       <c r="E107" t="str">
-        <v>Tested-Pass</v>
+        <v>Verified</v>
       </c>
       <c r="F107" t="str">
         <v>-</v>
@@ -3830,10 +3830,10 @@
         <v>-</v>
       </c>
       <c r="H107" t="str">
-        <v>SQL-contract</v>
+        <v>Vitest</v>
       </c>
       <c r="I107" t="str">
-        <v>chargeOperationsService.ts; guardManualChargesMigration.test.ts</v>
+        <v>customers.ts</v>
       </c>
       <c r="J107" t="str">
         <v>-</v>
@@ -3841,19 +3841,19 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>RPC-62</v>
+        <v>RPC-61</v>
       </c>
       <c r="B108" t="str">
-        <v>Clientes / Portal</v>
+        <v>Taxas Locais</v>
       </c>
       <c r="C108" t="str">
-        <v>As the platform I call supabase.rpc('upsert_customer_portal_account')</v>
+        <v>As the platform I call supabase.rpc('update_manual_bl_charge')</v>
       </c>
       <c r="D108" t="str">
-        <v>Creates/updates an initially-inactive account; provisioning continues in the Edge Function. Auth: authenticated+active+admin.</v>
+        <v>Updates only an eligible manual line, recalculates, audits; blocks invoiced B/L. Auth: authenticated+active.</v>
       </c>
       <c r="E108" t="str">
-        <v>Spec’d</v>
+        <v>Tested-Pass</v>
       </c>
       <c r="F108" t="str">
         <v>-</v>
@@ -3862,10 +3862,10 @@
         <v>-</v>
       </c>
       <c r="H108" t="str">
-        <v>Static</v>
+        <v>SQL-contract</v>
       </c>
       <c r="I108" t="str">
-        <v>customers.ts</v>
+        <v>chargeOperationsService.ts; guardManualChargesMigration.test.ts</v>
       </c>
       <c r="J108" t="str">
         <v>-</v>
@@ -3873,19 +3873,19 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>RPC-63</v>
+        <v>RPC-62</v>
       </c>
       <c r="B109" t="str">
-        <v>Portal / Faturamento</v>
+        <v>Clientes / Portal</v>
       </c>
       <c r="C109" t="str">
-        <v>As the platform I call supabase.rpc('portal_list_invoices')</v>
+        <v>As the platform I call supabase.rpc('upsert_customer_portal_account')</v>
       </c>
       <c r="D109" t="str">
-        <v>Read-only own invoices + ledger balance; CE-gated. Auth: current_portal_customer_id().</v>
+        <v>Creates/updates an initially-inactive account; provisioning continues in the Edge Function. Auth: authenticated+active+admin.</v>
       </c>
       <c r="E109" t="str">
-        <v>Verified</v>
+        <v>Spec’d</v>
       </c>
       <c r="F109" t="str">
         <v>-</v>
@@ -3894,27 +3894,27 @@
         <v>-</v>
       </c>
       <c r="H109" t="str">
-        <v>SQL-contract</v>
+        <v>Static</v>
       </c>
       <c r="I109" t="str">
-        <v>portalBilling.ts; portalInvoiceHistoryLinksMigration.test.ts</v>
+        <v>customers.ts</v>
       </c>
       <c r="J109" t="str">
-        <v>RESOLVED: anon EXECUTE revoked in 20260624100000_revoke_anon_portal_read_rpcs.sql (ADR 0013). definerActiveUserGuardMigration.test.ts green. Migrations applied cleanly to the PR Supabase preview branch (all tasks green); production grant application on merge/deploy.</v>
+        <v>-</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>RPC-64</v>
+        <v>RPC-63</v>
       </c>
       <c r="B110" t="str">
         <v>Portal / Faturamento</v>
       </c>
       <c r="C110" t="str">
-        <v>As the platform I call supabase.rpc('portal_invoice_details')</v>
+        <v>As the platform I call supabase.rpc('portal_list_invoices')</v>
       </c>
       <c r="D110" t="str">
-        <v>Reads invoice, links, breakdown, containers, payments for an own invoice. Auth: current_portal_customer_id().</v>
+        <v>Read-only own invoices + ledger balance; CE-gated. Auth: current_portal_customer_id().</v>
       </c>
       <c r="E110" t="str">
         <v>Verified</v>
@@ -3926,27 +3926,27 @@
         <v>-</v>
       </c>
       <c r="H110" t="str">
-        <v>SQL-contract</v>
+        <v>SQL-contract + Runtime (prod)</v>
       </c>
       <c r="I110" t="str">
-        <v>portalBilling.ts; portalInvoiceConsolidatedBreakdownMigration.test.ts</v>
+        <v>portalBilling.ts; portalInvoiceHistoryLinksMigration.test.ts</v>
       </c>
       <c r="J110" t="str">
-        <v>RESOLVED: anon EXECUTE revoked in 20260624100000_revoke_anon_portal_read_rpcs.sql (ADR 0013). definerActiveUserGuardMigration.test.ts green. Migrations applied cleanly to the PR Supabase preview branch (all tasks green); production grant application on merge/deploy.</v>
+        <v>RESOLVED &amp; RUNTIME-VERIFIED: anon EXECUTE=false confirmed in production (fgmkhbzhaeebrsizwccx, 2026-06-24); authenticated EXECUTE=true. Migration 20260624100000 (ADR 0013), asserted by definerActiveUserGuardMigration.test.ts.</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>RPC-65</v>
+        <v>RPC-64</v>
       </c>
       <c r="B111" t="str">
         <v>Portal / Faturamento</v>
       </c>
       <c r="C111" t="str">
-        <v>As the platform I call supabase.rpc('portal_list_consolidatable_receivables')</v>
+        <v>As the platform I call supabase.rpc('portal_invoice_details')</v>
       </c>
       <c r="D111" t="str">
-        <v>Read-only own eligible receivables; CE-gated. Auth: current_portal_customer_id().</v>
+        <v>Reads invoice, links, breakdown, containers, payments for an own invoice. Auth: current_portal_customer_id().</v>
       </c>
       <c r="E111" t="str">
         <v>Verified</v>
@@ -3958,27 +3958,27 @@
         <v>-</v>
       </c>
       <c r="H111" t="str">
-        <v>SQL-contract</v>
+        <v>SQL-contract + Runtime (prod)</v>
       </c>
       <c r="I111" t="str">
-        <v>portalBilling.ts; portalCeMercanteGateMigration.test.ts</v>
+        <v>portalBilling.ts; portalInvoiceConsolidatedBreakdownMigration.test.ts</v>
       </c>
       <c r="J111" t="str">
-        <v>RESOLVED: anon EXECUTE revoked in 20260624100000_revoke_anon_portal_read_rpcs.sql (ADR 0013). definerActiveUserGuardMigration.test.ts green. Migrations applied cleanly to the PR Supabase preview branch (all tasks green); production grant application on merge/deploy.</v>
+        <v>RESOLVED &amp; RUNTIME-VERIFIED: anon EXECUTE=false confirmed in production (fgmkhbzhaeebrsizwccx, 2026-06-24); authenticated EXECUTE=true. Migration 20260624100000 (ADR 0013), asserted by definerActiveUserGuardMigration.test.ts.</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>RPC-66</v>
+        <v>RPC-65</v>
       </c>
       <c r="B112" t="str">
-        <v>Portal / Demurrage</v>
+        <v>Portal / Faturamento</v>
       </c>
       <c r="C112" t="str">
-        <v>As the platform I call supabase.rpc('portal_list_demurrage_invoices')</v>
+        <v>As the platform I call supabase.rpc('portal_list_consolidatable_receivables')</v>
       </c>
       <c r="D112" t="str">
-        <v>Read-only own demurrage invoices; status + CE gated. Auth: current_portal_customer_id().</v>
+        <v>Read-only own eligible receivables; CE-gated. Auth: current_portal_customer_id().</v>
       </c>
       <c r="E112" t="str">
         <v>Verified</v>
@@ -3990,27 +3990,27 @@
         <v>-</v>
       </c>
       <c r="H112" t="str">
-        <v>SQL-contract</v>
+        <v>SQL-contract + Runtime (prod)</v>
       </c>
       <c r="I112" t="str">
         <v>portalBilling.ts; portalCeMercanteGateMigration.test.ts</v>
       </c>
       <c r="J112" t="str">
-        <v>RESOLVED: anon EXECUTE revoked in 20260624100000_revoke_anon_portal_read_rpcs.sql (ADR 0013). definerActiveUserGuardMigration.test.ts green. Migrations applied cleanly to the PR Supabase preview branch (all tasks green); production grant application on merge/deploy.</v>
+        <v>RESOLVED &amp; RUNTIME-VERIFIED: anon EXECUTE=false confirmed in production (fgmkhbzhaeebrsizwccx, 2026-06-24); authenticated EXECUTE=true. Migration 20260624100000 (ADR 0013), asserted by definerActiveUserGuardMigration.test.ts.</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>RPC-67</v>
+        <v>RPC-66</v>
       </c>
       <c r="B113" t="str">
         <v>Portal / Demurrage</v>
       </c>
       <c r="C113" t="str">
-        <v>As the platform I call supabase.rpc('portal_get_demurrage_invoice_detail')</v>
+        <v>As the platform I call supabase.rpc('portal_list_demurrage_invoices')</v>
       </c>
       <c r="D113" t="str">
-        <v>Read-only own demurrage invoice/items; CE-gated. Auth: current_portal_customer_id().</v>
+        <v>Read-only own demurrage invoices; status + CE gated. Auth: current_portal_customer_id().</v>
       </c>
       <c r="E113" t="str">
         <v>Verified</v>
@@ -4022,30 +4022,30 @@
         <v>-</v>
       </c>
       <c r="H113" t="str">
-        <v>SQL-contract</v>
+        <v>SQL-contract + Runtime (prod)</v>
       </c>
       <c r="I113" t="str">
         <v>portalBilling.ts; portalCeMercanteGateMigration.test.ts</v>
       </c>
       <c r="J113" t="str">
-        <v>RESOLVED: anon EXECUTE revoked in 20260624100000_revoke_anon_portal_read_rpcs.sql (ADR 0013). definerActiveUserGuardMigration.test.ts green. Migrations applied cleanly to the PR Supabase preview branch (all tasks green); production grant application on merge/deploy.</v>
+        <v>RESOLVED &amp; RUNTIME-VERIFIED: anon EXECUTE=false confirmed in production (fgmkhbzhaeebrsizwccx, 2026-06-24); authenticated EXECUTE=true. Migration 20260624100000 (ADR 0013), asserted by definerActiveUserGuardMigration.test.ts.</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>RPC-68</v>
+        <v>RPC-67</v>
       </c>
       <c r="B114" t="str">
-        <v>Portal / Faturamento</v>
+        <v>Portal / Demurrage</v>
       </c>
       <c r="C114" t="str">
-        <v>As the platform I call supabase.rpc('portal_create_consolidation')</v>
+        <v>As the platform I call supabase.rpc('portal_get_demurrage_invoice_detail')</v>
       </c>
       <c r="D114" t="str">
-        <v>Creates a consolidation via core; ownership/CE/rate-limit 3/10min; inserts alert + notification. Auth: current_portal_customer_id().</v>
+        <v>Read-only own demurrage invoice/items; CE-gated. Auth: current_portal_customer_id().</v>
       </c>
       <c r="E114" t="str">
-        <v>Tested-Pass</v>
+        <v>Verified</v>
       </c>
       <c r="F114" t="str">
         <v>-</v>
@@ -4054,30 +4054,30 @@
         <v>-</v>
       </c>
       <c r="H114" t="str">
-        <v>SQL-contract</v>
+        <v>SQL-contract + Runtime (prod)</v>
       </c>
       <c r="I114" t="str">
-        <v>portalBilling.ts; portalCreateConsolidationJsonbMigration.test.ts</v>
+        <v>portalBilling.ts; portalCeMercanteGateMigration.test.ts</v>
       </c>
       <c r="J114" t="str">
-        <v>-</v>
+        <v>RESOLVED &amp; RUNTIME-VERIFIED: anon EXECUTE=false confirmed in production (fgmkhbzhaeebrsizwccx, 2026-06-24); authenticated EXECUTE=true. Migration 20260624100000 (ADR 0013), asserted by definerActiveUserGuardMigration.test.ts.</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>RPC-69</v>
+        <v>RPC-68</v>
       </c>
       <c r="B115" t="str">
         <v>Portal / Faturamento</v>
       </c>
       <c r="C115" t="str">
-        <v>As the platform I call supabase.rpc('portal_obsolete_consolidation')</v>
+        <v>As the platform I call supabase.rpc('portal_create_consolidation')</v>
       </c>
       <c r="D115" t="str">
-        <v>Obsoletes own consolidation + links; rate-limit 3/15min; alert + notification. Auth: current_portal_customer_id().</v>
+        <v>Creates a consolidation via core; ownership/CE/rate-limit 3/10min; inserts alert + notification. Auth: current_portal_customer_id().</v>
       </c>
       <c r="E115" t="str">
-        <v>Spec’d</v>
+        <v>Tested-Pass</v>
       </c>
       <c r="F115" t="str">
         <v>-</v>
@@ -4086,10 +4086,10 @@
         <v>-</v>
       </c>
       <c r="H115" t="str">
-        <v>Static</v>
+        <v>SQL-contract</v>
       </c>
       <c r="I115" t="str">
-        <v>portalBilling.ts</v>
+        <v>portalBilling.ts; portalCreateConsolidationJsonbMigration.test.ts</v>
       </c>
       <c r="J115" t="str">
         <v>-</v>
@@ -4097,16 +4097,16 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>RPC-70</v>
+        <v>RPC-69</v>
       </c>
       <c r="B116" t="str">
-        <v>Portal / Demurrage</v>
+        <v>Portal / Faturamento</v>
       </c>
       <c r="C116" t="str">
-        <v>As the platform I call supabase.rpc('portal_open_demurrage_dispute')</v>
+        <v>As the platform I call supabase.rpc('portal_obsolete_consolidation')</v>
       </c>
       <c r="D116" t="str">
-        <v>Opens a dispute on an own invoice; rate-limit 3/30min; notification + internal alert. Auth: current_portal_customer_id().</v>
+        <v>Obsoletes own consolidation + links; rate-limit 3/15min; alert + notification. Auth: current_portal_customer_id().</v>
       </c>
       <c r="E116" t="str">
         <v>Spec’d</v>
@@ -4129,16 +4129,16 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>RPC-71</v>
+        <v>RPC-70</v>
       </c>
       <c r="B117" t="str">
-        <v>Portal / Perfil</v>
+        <v>Portal / Demurrage</v>
       </c>
       <c r="C117" t="str">
-        <v>As the platform I call supabase.rpc('portal_get_profile')</v>
+        <v>As the platform I call supabase.rpc('portal_open_demurrage_dispute')</v>
       </c>
       <c r="D117" t="str">
-        <v>Reads account, customer record and billing contact. Auth: current_portal_customer_id().</v>
+        <v>Opens a dispute on an own invoice; rate-limit 3/30min; notification + internal alert. Auth: current_portal_customer_id().</v>
       </c>
       <c r="E117" t="str">
         <v>Spec’d</v>
@@ -4161,16 +4161,16 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>RPC-72</v>
+        <v>RPC-71</v>
       </c>
       <c r="B118" t="str">
         <v>Portal / Perfil</v>
       </c>
       <c r="C118" t="str">
-        <v>As the platform I call supabase.rpc('portal_update_profile')</v>
+        <v>As the platform I call supabase.rpc('portal_get_profile')</v>
       </c>
       <c r="D118" t="str">
-        <v>Updates account email, customer address and contact phone. Auth: current_portal_customer_id().</v>
+        <v>Reads account, customer record and billing contact. Auth: current_portal_customer_id().</v>
       </c>
       <c r="E118" t="str">
         <v>Spec’d</v>
@@ -4193,16 +4193,16 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>RPC-73</v>
+        <v>RPC-72</v>
       </c>
       <c r="B119" t="str">
-        <v>Portal / Notificações</v>
+        <v>Portal / Perfil</v>
       </c>
       <c r="C119" t="str">
-        <v>As the platform I call supabase.rpc('portal_list_notifications')</v>
+        <v>As the platform I call supabase.rpc('portal_update_profile')</v>
       </c>
       <c r="D119" t="str">
-        <v>Read-only notifications; cached + polled. Auth: current_portal_customer_id().</v>
+        <v>Updates account email, customer address and contact phone. Auth: current_portal_customer_id().</v>
       </c>
       <c r="E119" t="str">
         <v>Spec’d</v>
@@ -4225,16 +4225,16 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>RPC-74</v>
+        <v>RPC-73</v>
       </c>
       <c r="B120" t="str">
         <v>Portal / Notificações</v>
       </c>
       <c r="C120" t="str">
-        <v>As the platform I call supabase.rpc('portal_mark_all_notifications_read')</v>
+        <v>As the platform I call supabase.rpc('portal_list_notifications')</v>
       </c>
       <c r="D120" t="str">
-        <v>Marks all own notifications read; invalidates list/counter. Auth: current_portal_customer_id().</v>
+        <v>Read-only notifications; cached + polled. Auth: current_portal_customer_id().</v>
       </c>
       <c r="E120" t="str">
         <v>Spec’d</v>
@@ -4257,16 +4257,16 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>RPC-75</v>
+        <v>RPC-74</v>
       </c>
       <c r="B121" t="str">
         <v>Portal / Notificações</v>
       </c>
       <c r="C121" t="str">
-        <v>As the platform I call supabase.rpc('portal_mark_notification_read')</v>
+        <v>As the platform I call supabase.rpc('portal_mark_all_notifications_read')</v>
       </c>
       <c r="D121" t="str">
-        <v>Marks one own notification read. Auth: current_portal_customer_id().</v>
+        <v>Marks all own notifications read; invalidates list/counter. Auth: current_portal_customer_id().</v>
       </c>
       <c r="E121" t="str">
         <v>Spec’d</v>
@@ -4289,16 +4289,16 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>RPC-76</v>
+        <v>RPC-75</v>
       </c>
       <c r="B122" t="str">
         <v>Portal / Notificações</v>
       </c>
       <c r="C122" t="str">
-        <v>As the platform I call supabase.rpc('portal_notification_unread_count')</v>
+        <v>As the platform I call supabase.rpc('portal_mark_notification_read')</v>
       </c>
       <c r="D122" t="str">
-        <v>Unread count; 30s polling. Auth: current_portal_customer_id().</v>
+        <v>Marks one own notification read. Auth: current_portal_customer_id().</v>
       </c>
       <c r="E122" t="str">
         <v>Spec’d</v>
@@ -4321,19 +4321,19 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>RPC-77</v>
+        <v>RPC-76</v>
       </c>
       <c r="B123" t="str">
-        <v>Portal / Auth</v>
+        <v>Portal / Notificações</v>
       </c>
       <c r="C123" t="str">
-        <v>As the platform I call supabase.rpc('portal_resolve_login')</v>
+        <v>As the platform I call supabase.rpc('portal_notification_unread_count')</v>
       </c>
       <c r="D123" t="str">
-        <v>Logs attempt by hash and resolves document to technical email; no session created (ADR 0013 anon exception). Auth: current_portal_customer_id().</v>
+        <v>Unread count; 30s polling. Auth: current_portal_customer_id().</v>
       </c>
       <c r="E123" t="str">
-        <v>Tested-Pass</v>
+        <v>Spec’d</v>
       </c>
       <c r="F123" t="str">
         <v>-</v>
@@ -4342,10 +4342,10 @@
         <v>-</v>
       </c>
       <c r="H123" t="str">
-        <v>SQL-contract</v>
+        <v>Static</v>
       </c>
       <c r="I123" t="str">
-        <v>portalBilling.ts; portalResolveLoginHardeningMigration.test.ts</v>
+        <v>portalBilling.ts</v>
       </c>
       <c r="J123" t="str">
         <v>-</v>
@@ -4353,19 +4353,19 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>EDGE-01</v>
+        <v>RPC-77</v>
       </c>
       <c r="B124" t="str">
-        <v>Clientes / Portal</v>
+        <v>Portal / Auth</v>
       </c>
       <c r="C124" t="str">
-        <v>As an admin I call functions.invoke('provision-portal-user')</v>
+        <v>As the platform I call supabase.rpc('portal_resolve_login')</v>
       </c>
       <c r="D124" t="str">
-        <v>verify_jwt=true; validates JWT (auth.getUser), active internal profile, role admin/administrativo; CORS allowlist; persistent rate limit 20/h per user; service role uses Auth Admin createUser/updateUserById and links auth_user_id/email. Failures: 401/403/429/400/404/409/500.</v>
+        <v>Logs attempt by hash and resolves document to technical email; no session created (ADR 0013 anon exception). Auth: current_portal_customer_id().</v>
       </c>
       <c r="E124" t="str">
-        <v>Verified</v>
+        <v>Tested-Pass</v>
       </c>
       <c r="F124" t="str">
         <v>-</v>
@@ -4374,30 +4374,30 @@
         <v>-</v>
       </c>
       <c r="H124" t="str">
-        <v>Vitest</v>
+        <v>SQL-contract</v>
       </c>
       <c r="I124" t="str">
-        <v>supabase/functions/provision-portal-user/index.ts; supabase/config.toml; customers.test.ts</v>
+        <v>portalBilling.ts; portalResolveLoginHardeningMigration.test.ts</v>
       </c>
       <c r="J124" t="str">
-        <v>customers.test.ts mocks invoke order/failure; Edge runtime not executed here.</v>
+        <v>-</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>EDGE-02</v>
+        <v>EDGE-01</v>
       </c>
       <c r="B125" t="str">
-        <v>Faturamento / Portal</v>
+        <v>Clientes / Portal</v>
       </c>
       <c r="C125" t="str">
-        <v>As the DB webhook I invoke notify-invoice-issued on invoices.status -&gt; issued</v>
+        <v>As an admin I call functions.invoke('provision-portal-user')</v>
       </c>
       <c r="D125" t="str">
-        <v>Bearer must equal SUPABASE_SERVICE_ROLE_KEY (timing-safe); accepts absent Origin or Origin == SUPABASE_URL; service role re-reads invoice/customer/contacts (no DB writes); sends email via Resend. No recipient/key -&gt; skipped/sent:false; auth fail 401; Resend/parse fail 500.</v>
+        <v>verify_jwt=true; validates JWT (auth.getUser), active internal profile, role admin/administrativo; CORS allowlist; persistent rate limit 20/h per user; service role uses Auth Admin createUser/updateUserById and links auth_user_id/email. Failures: 401/403/429/400/404/409/500.</v>
       </c>
       <c r="E125" t="str">
-        <v>Spec’d</v>
+        <v>Verified</v>
       </c>
       <c r="F125" t="str">
         <v>-</v>
@@ -4406,30 +4406,30 @@
         <v>-</v>
       </c>
       <c r="H125" t="str">
-        <v>Static</v>
+        <v>Vitest</v>
       </c>
       <c r="I125" t="str">
-        <v>supabase/functions/notify-invoice-issued/index.ts</v>
+        <v>supabase/functions/provision-portal-user/index.ts; supabase/config.toml; customers.test.ts</v>
       </c>
       <c r="J125" t="str">
-        <v>Suspeita: webhook/secret/deploy not versioned; no dedicated config.toml block to confirm verify_jwt; no own rate limit. Needs controlled-runtime confirmation.</v>
+        <v>customers.test.ts mocks invoke order/failure; Edge runtime not executed here.</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>RLS-01</v>
+        <v>EDGE-02</v>
       </c>
       <c r="B126" t="str">
-        <v>Alertas / Painel</v>
+        <v>Faturamento / Portal</v>
       </c>
       <c r="C126" t="str">
-        <v>As the platform I enforce RLS on alerts (SELECT/INSERT/UPDATE)</v>
+        <v>As the DB webhook I invoke notify-invoice-issued on invoices.status -&gt; issued</v>
       </c>
       <c r="D126" t="str">
-        <v>010: active reads/inserts/updates; admin deletes.</v>
+        <v>Code path: bearer must equal SUPABASE_SERVICE_ROLE_KEY (timing-safe); accepts absent Origin or Origin == SUPABASE_URL; service role re-reads invoice/customer/contacts (no DB writes); sends email via Resend. No recipient/key -&gt; skipped/sent:false; auth fail 401; Resend/parse fail 500.</v>
       </c>
       <c r="E126" t="str">
-        <v>Verified</v>
+        <v>Spec’d</v>
       </c>
       <c r="F126" t="str">
         <v>-</v>
@@ -4438,27 +4438,27 @@
         <v>-</v>
       </c>
       <c r="H126" t="str">
-        <v>SQL (migration) + Static</v>
+        <v>Static + Runtime (prod)</v>
       </c>
       <c r="I126" t="str">
-        <v>docs/RASTREABILIDADE.md (tabelas); alerts</v>
+        <v>supabase/functions/notify-invoice-issued/index.ts</v>
       </c>
       <c r="J126" t="str">
-        <v>-</v>
+        <v>INACTIVE BY DECISION (not a defect): production check 2026-06-24 confirms no Database Webhook wires this function and RESEND_API_KEY is not provisioned, so it never runs. The project does not send customer email today; client notification is in-app (trg_notify_invoice_issued). Re-activation (webhook + key + optional rate limit) is future work, out of current scope.</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>RLS-02</v>
+        <v>RLS-01</v>
       </c>
       <c r="B127" t="str">
-        <v>Auditoria</v>
+        <v>Alertas / Painel</v>
       </c>
       <c r="C127" t="str">
-        <v>As the platform I enforce RLS on audit_logs (SELECT/INSERT)</v>
+        <v>As the platform I enforce RLS on alerts (SELECT/INSERT/UPDATE)</v>
       </c>
       <c r="D127" t="str">
-        <v>014: active reads; insert requires active + changed_by=auth.uid(); update/delete admin.</v>
+        <v>010: active reads/inserts/updates; admin deletes.</v>
       </c>
       <c r="E127" t="str">
         <v>Verified</v>
@@ -4473,7 +4473,7 @@
         <v>SQL (migration) + Static</v>
       </c>
       <c r="I127" t="str">
-        <v>docs/RASTREABILIDADE.md (tabelas); audit_logs</v>
+        <v>docs/RASTREABILIDADE.md (tabelas); alerts</v>
       </c>
       <c r="J127" t="str">
         <v>-</v>
@@ -4481,19 +4481,19 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>RLS-03</v>
+        <v>RLS-02</v>
       </c>
       <c r="B128" t="str">
-        <v>Baplie</v>
+        <v>Auditoria</v>
       </c>
       <c r="C128" t="str">
-        <v>As the platform I enforce RLS on baplie_containers (SELECT)</v>
+        <v>As the platform I enforce RLS on audit_logs (SELECT/INSERT)</v>
       </c>
       <c r="D128" t="str">
-        <v>20260609134000: active r/i/u; admin deletes.</v>
+        <v>014: active reads; insert requires active + changed_by=auth.uid(); update/delete admin.</v>
       </c>
       <c r="E128" t="str">
-        <v>Tested-Pass</v>
+        <v>Verified</v>
       </c>
       <c r="F128" t="str">
         <v>-</v>
@@ -4505,21 +4505,21 @@
         <v>SQL (migration) + Static</v>
       </c>
       <c r="I128" t="str">
-        <v>docs/RASTREABILIDADE.md (tabelas); baplie_containers</v>
+        <v>docs/RASTREABILIDADE.md (tabelas); audit_logs</v>
       </c>
       <c r="J128" t="str">
-        <v>rlsHardeningMigration.test.ts</v>
+        <v>-</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>RLS-04</v>
+        <v>RLS-03</v>
       </c>
       <c r="B129" t="str">
-        <v>Baplie / Reconciliação</v>
+        <v>Baplie</v>
       </c>
       <c r="C129" t="str">
-        <v>As the platform I enforce RLS on baplie_reconciliation_resolutions (SELECT/UPSERT)</v>
+        <v>As the platform I enforce RLS on baplie_containers (SELECT)</v>
       </c>
       <c r="D129" t="str">
         <v>20260609134000: active r/i/u; admin deletes.</v>
@@ -4537,7 +4537,7 @@
         <v>SQL (migration) + Static</v>
       </c>
       <c r="I129" t="str">
-        <v>docs/RASTREABILIDADE.md (tabelas); baplie_reconciliation_resolutions</v>
+        <v>docs/RASTREABILIDADE.md (tabelas); baplie_containers</v>
       </c>
       <c r="J129" t="str">
         <v>rlsHardeningMigration.test.ts</v>
@@ -4545,19 +4545,19 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>RLS-05</v>
+        <v>RLS-04</v>
       </c>
       <c r="B130" t="str">
-        <v>Faturamento</v>
+        <v>Baplie / Reconciliação</v>
       </c>
       <c r="C130" t="str">
-        <v>As the platform I enforce RLS on billing_batches (SELECT)</v>
+        <v>As the platform I enforce RLS on baplie_reconciliation_resolutions (SELECT/UPSERT)</v>
       </c>
       <c r="D130" t="str">
-        <v>041: active reads; admin i/u/d.</v>
+        <v>20260609134000: active r/i/u; admin deletes.</v>
       </c>
       <c r="E130" t="str">
-        <v>Spec’d</v>
+        <v>Tested-Pass</v>
       </c>
       <c r="F130" t="str">
         <v>-</v>
@@ -4569,27 +4569,27 @@
         <v>SQL (migration) + Static</v>
       </c>
       <c r="I130" t="str">
-        <v>docs/RASTREABILIDADE.md (tabelas); billing_batches</v>
+        <v>docs/RASTREABILIDADE.md (tabelas); baplie_reconciliation_resolutions</v>
       </c>
       <c r="J130" t="str">
-        <v>-</v>
+        <v>rlsHardeningMigration.test.ts</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>RLS-06</v>
+        <v>RLS-05</v>
       </c>
       <c r="B131" t="str">
-        <v>Manifestos BB</v>
+        <v>Faturamento</v>
       </c>
       <c r="C131" t="str">
-        <v>As the platform I enforce RLS on bl_breakbulk_items (INSERT/DELETE)</v>
+        <v>As the platform I enforce RLS on billing_batches (SELECT)</v>
       </c>
       <c r="D131" t="str">
-        <v>010 final: active r/i/u; admin deletes; trigger validates carga_solta parent.</v>
+        <v>041: active reads; admin i/u/d.</v>
       </c>
       <c r="E131" t="str">
-        <v>Verified</v>
+        <v>Spec’d</v>
       </c>
       <c r="F131" t="str">
         <v>-</v>
@@ -4601,7 +4601,7 @@
         <v>SQL (migration) + Static</v>
       </c>
       <c r="I131" t="str">
-        <v>docs/RASTREABILIDADE.md (tabelas); bl_breakbulk_items</v>
+        <v>docs/RASTREABILIDADE.md (tabelas); billing_batches</v>
       </c>
       <c r="J131" t="str">
         <v>-</v>
@@ -4609,16 +4609,16 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>RLS-07</v>
+        <v>RLS-06</v>
       </c>
       <c r="B132" t="str">
-        <v>Containers / Demurrage</v>
+        <v>Manifestos BB</v>
       </c>
       <c r="C132" t="str">
-        <v>As the platform I enforce RLS on bl_containers (SELECT/UPDATE/DELETE)</v>
+        <v>As the platform I enforce RLS on bl_breakbulk_items (INSERT/DELETE)</v>
       </c>
       <c r="D132" t="str">
-        <v>010 final: active r/i/u; admin deletes; trigger sets discharge; service blocks delete with dependencies.</v>
+        <v>010 final: active r/i/u; admin deletes; trigger validates carga_solta parent.</v>
       </c>
       <c r="E132" t="str">
         <v>Verified</v>
@@ -4633,7 +4633,7 @@
         <v>SQL (migration) + Static</v>
       </c>
       <c r="I132" t="str">
-        <v>docs/RASTREABILIDADE.md (tabelas); bl_containers</v>
+        <v>docs/RASTREABILIDADE.md (tabelas); bl_breakbulk_items</v>
       </c>
       <c r="J132" t="str">
         <v>-</v>
@@ -4641,19 +4641,19 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>RLS-08</v>
+        <v>RLS-07</v>
       </c>
       <c r="B133" t="str">
-        <v>Ledger</v>
+        <v>Containers / Demurrage</v>
       </c>
       <c r="C133" t="str">
-        <v>As the platform I enforce RLS on bl_receivables (SELECT)</v>
+        <v>As the platform I enforce RLS on bl_containers (SELECT/UPDATE/DELETE)</v>
       </c>
       <c r="D133" t="str">
-        <v>20260529100000: all operations admin only.</v>
+        <v>010 final: active r/i/u; admin deletes; trigger sets discharge; service blocks delete with dependencies.</v>
       </c>
       <c r="E133" t="str">
-        <v>Spec’d</v>
+        <v>Verified</v>
       </c>
       <c r="F133" t="str">
         <v>-</v>
@@ -4665,7 +4665,7 @@
         <v>SQL (migration) + Static</v>
       </c>
       <c r="I133" t="str">
-        <v>docs/RASTREABILIDADE.md (tabelas); bl_receivables</v>
+        <v>docs/RASTREABILIDADE.md (tabelas); bl_containers</v>
       </c>
       <c r="J133" t="str">
         <v>-</v>
@@ -4673,19 +4673,19 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>RLS-09</v>
+        <v>RLS-08</v>
       </c>
       <c r="B134" t="str">
-        <v>B/L (transversal)</v>
+        <v>Ledger</v>
       </c>
       <c r="C134" t="str">
-        <v>As the platform I enforce RLS on bls (SELECT/UPDATE/UPSERT/DELETE)</v>
+        <v>As the platform I enforce RLS on bl_receivables (SELECT)</v>
       </c>
       <c r="D134" t="str">
-        <v>010 final: active r/i/u; admin deletes; review gate, promotion, auto-issue, billing/container guards.</v>
+        <v>20260529100000: all operations admin only.</v>
       </c>
       <c r="E134" t="str">
-        <v>Verified</v>
+        <v>Spec’d</v>
       </c>
       <c r="F134" t="str">
         <v>-</v>
@@ -4697,7 +4697,7 @@
         <v>SQL (migration) + Static</v>
       </c>
       <c r="I134" t="str">
-        <v>docs/RASTREABILIDADE.md (tabelas); bls</v>
+        <v>docs/RASTREABILIDADE.md (tabelas); bl_receivables</v>
       </c>
       <c r="J134" t="str">
         <v>-</v>
@@ -4705,19 +4705,19 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>RLS-10</v>
+        <v>RLS-09</v>
       </c>
       <c r="B135" t="str">
-        <v>Viagens</v>
+        <v>B/L (transversal)</v>
       </c>
       <c r="C135" t="str">
-        <v>As the platform I enforce RLS on carriers (SELECT/INSERT)</v>
+        <v>As the platform I enforce RLS on bls (SELECT/UPDATE/UPSERT/DELETE)</v>
       </c>
       <c r="D135" t="str">
-        <v>010 final: active r/i/u; admin deletes.</v>
+        <v>010 final: active r/i/u; admin deletes; review gate, promotion, auto-issue, billing/container guards.</v>
       </c>
       <c r="E135" t="str">
-        <v>Spec’d</v>
+        <v>Verified</v>
       </c>
       <c r="F135" t="str">
         <v>-</v>
@@ -4729,7 +4729,7 @@
         <v>SQL (migration) + Static</v>
       </c>
       <c r="I135" t="str">
-        <v>docs/RASTREABILIDADE.md (tabelas); carriers</v>
+        <v>docs/RASTREABILIDADE.md (tabelas); bls</v>
       </c>
       <c r="J135" t="str">
         <v>-</v>
@@ -4737,19 +4737,19 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>RLS-11</v>
+        <v>RLS-10</v>
       </c>
       <c r="B136" t="str">
-        <v>Taxas Locais</v>
+        <v>Viagens</v>
       </c>
       <c r="C136" t="str">
-        <v>As the platform I enforce RLS on charge_calculations (SELECT)</v>
+        <v>As the platform I enforce RLS on carriers (SELECT/INSERT)</v>
       </c>
       <c r="D136" t="str">
-        <v>014: SELECT admin; INSERT/UPDATE active; DELETE admin.</v>
+        <v>010 final: active r/i/u; admin deletes.</v>
       </c>
       <c r="E136" t="str">
-        <v>Verified</v>
+        <v>Spec’d</v>
       </c>
       <c r="F136" t="str">
         <v>-</v>
@@ -4761,7 +4761,7 @@
         <v>SQL (migration) + Static</v>
       </c>
       <c r="I136" t="str">
-        <v>docs/RASTREABILIDADE.md (tabelas); charge_calculations</v>
+        <v>docs/RASTREABILIDADE.md (tabelas); carriers</v>
       </c>
       <c r="J136" t="str">
         <v>-</v>
@@ -4769,16 +4769,16 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>RLS-12</v>
+        <v>RLS-11</v>
       </c>
       <c r="B137" t="str">
         <v>Taxas Locais</v>
       </c>
       <c r="C137" t="str">
-        <v>As the platform I enforce RLS on charge_table_items (CRUD)</v>
+        <v>As the platform I enforce RLS on charge_calculations (SELECT)</v>
       </c>
       <c r="D137" t="str">
-        <v>010+014: all operations admin.</v>
+        <v>014: SELECT admin; INSERT/UPDATE active; DELETE admin.</v>
       </c>
       <c r="E137" t="str">
         <v>Verified</v>
@@ -4793,7 +4793,7 @@
         <v>SQL (migration) + Static</v>
       </c>
       <c r="I137" t="str">
-        <v>docs/RASTREABILIDADE.md (tabelas); charge_table_items</v>
+        <v>docs/RASTREABILIDADE.md (tabelas); charge_calculations</v>
       </c>
       <c r="J137" t="str">
         <v>-</v>
@@ -4801,16 +4801,16 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>RLS-13</v>
+        <v>RLS-12</v>
       </c>
       <c r="B138" t="str">
         <v>Taxas Locais</v>
       </c>
       <c r="C138" t="str">
-        <v>As the platform I enforce RLS on charge_tables (SELECT/INSERT/UPDATE)</v>
+        <v>As the platform I enforce RLS on charge_table_items (CRUD)</v>
       </c>
       <c r="D138" t="str">
-        <v>010+014: all operations admin; validity gates ready_for_billing.</v>
+        <v>010+014: all operations admin.</v>
       </c>
       <c r="E138" t="str">
         <v>Verified</v>
@@ -4825,7 +4825,7 @@
         <v>SQL (migration) + Static</v>
       </c>
       <c r="I138" t="str">
-        <v>docs/RASTREABILIDADE.md (tabelas); charge_tables</v>
+        <v>docs/RASTREABILIDADE.md (tabelas); charge_table_items</v>
       </c>
       <c r="J138" t="str">
         <v>-</v>
@@ -4833,16 +4833,16 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>RLS-14</v>
+        <v>RLS-13</v>
       </c>
       <c r="B139" t="str">
-        <v>Clientes</v>
+        <v>Taxas Locais</v>
       </c>
       <c r="C139" t="str">
-        <v>As the platform I enforce RLS on customer_contacts (CRUD)</v>
+        <v>As the platform I enforce RLS on charge_tables (SELECT/INSERT/UPDATE)</v>
       </c>
       <c r="D139" t="str">
-        <v>010 final: active r/i/u; admin deletes; email in gate; Edge reads via service role.</v>
+        <v>010+014: all operations admin; validity gates ready_for_billing.</v>
       </c>
       <c r="E139" t="str">
         <v>Verified</v>
@@ -4857,7 +4857,7 @@
         <v>SQL (migration) + Static</v>
       </c>
       <c r="I139" t="str">
-        <v>docs/RASTREABILIDADE.md (tabelas); customer_contacts</v>
+        <v>docs/RASTREABILIDADE.md (tabelas); charge_tables</v>
       </c>
       <c r="J139" t="str">
         <v>-</v>
@@ -4865,16 +4865,16 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>RLS-15</v>
+        <v>RLS-14</v>
       </c>
       <c r="B140" t="str">
-        <v>Taxas Locais / Clientes</v>
+        <v>Clientes</v>
       </c>
       <c r="C140" t="str">
-        <v>As the platform I enforce RLS on customer_rate_overrides (CRUD)</v>
+        <v>As the platform I enforce RLS on customer_contacts (CRUD)</v>
       </c>
       <c r="D140" t="str">
-        <v>010+014: all operations admin.</v>
+        <v>010 final: active r/i/u; admin deletes; email in gate; Edge reads via service role.</v>
       </c>
       <c r="E140" t="str">
         <v>Verified</v>
@@ -4889,7 +4889,7 @@
         <v>SQL (migration) + Static</v>
       </c>
       <c r="I140" t="str">
-        <v>docs/RASTREABILIDADE.md (tabelas); customer_rate_overrides</v>
+        <v>docs/RASTREABILIDADE.md (tabelas); customer_contacts</v>
       </c>
       <c r="J140" t="str">
         <v>-</v>
@@ -4897,16 +4897,16 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>RLS-16</v>
+        <v>RLS-15</v>
       </c>
       <c r="B141" t="str">
-        <v>Clientes</v>
+        <v>Taxas Locais / Clientes</v>
       </c>
       <c r="C141" t="str">
-        <v>As the platform I enforce RLS on customers (CRUD/UPSERT)</v>
+        <v>As the platform I enforce RLS on customer_rate_overrides (CRUD)</v>
       </c>
       <c r="D141" t="str">
-        <v>010 final: active r/i/u; admin deletes; Portal profile writes via RPC.</v>
+        <v>010+014: all operations admin.</v>
       </c>
       <c r="E141" t="str">
         <v>Verified</v>
@@ -4921,7 +4921,7 @@
         <v>SQL (migration) + Static</v>
       </c>
       <c r="I141" t="str">
-        <v>docs/RASTREABILIDADE.md (tabelas); customers</v>
+        <v>docs/RASTREABILIDADE.md (tabelas); customer_rate_overrides</v>
       </c>
       <c r="J141" t="str">
         <v>-</v>
@@ -4929,16 +4929,16 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>RLS-17</v>
+        <v>RLS-16</v>
       </c>
       <c r="B142" t="str">
-        <v>Demurrage</v>
+        <v>Clientes</v>
       </c>
       <c r="C142" t="str">
-        <v>As the platform I enforce RLS on demurrage_invoice_items (SELECT/INSERT)</v>
+        <v>As the platform I enforce RLS on customers (CRUD/UPSERT)</v>
       </c>
       <c r="D142" t="str">
-        <v>050 final: active r/i/u; admin deletes; frozen lines; cascade on invoice delete.</v>
+        <v>010 final: active r/i/u; admin deletes; Portal profile writes via RPC.</v>
       </c>
       <c r="E142" t="str">
         <v>Verified</v>
@@ -4953,7 +4953,7 @@
         <v>SQL (migration) + Static</v>
       </c>
       <c r="I142" t="str">
-        <v>docs/RASTREABILIDADE.md (tabelas); demurrage_invoice_items</v>
+        <v>docs/RASTREABILIDADE.md (tabelas); customers</v>
       </c>
       <c r="J142" t="str">
         <v>-</v>
@@ -4961,16 +4961,16 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>RLS-18</v>
+        <v>RLS-17</v>
       </c>
       <c r="B143" t="str">
         <v>Demurrage</v>
       </c>
       <c r="C143" t="str">
-        <v>As the platform I enforce RLS on demurrage_invoices (SELECT/INSERT/UPDATE)</v>
+        <v>As the platform I enforce RLS on demurrage_invoice_items (SELECT/INSERT)</v>
       </c>
       <c r="D143" t="str">
-        <v>050 final: active r/i/u; admin deletes; notifications, dispute, overdue cron.</v>
+        <v>050 final: active r/i/u; admin deletes; frozen lines; cascade on invoice delete.</v>
       </c>
       <c r="E143" t="str">
         <v>Verified</v>
@@ -4985,7 +4985,7 @@
         <v>SQL (migration) + Static</v>
       </c>
       <c r="I143" t="str">
-        <v>docs/RASTREABILIDADE.md (tabelas); demurrage_invoices</v>
+        <v>docs/RASTREABILIDADE.md (tabelas); demurrage_invoice_items</v>
       </c>
       <c r="J143" t="str">
         <v>-</v>
@@ -4993,16 +4993,16 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>RLS-19</v>
+        <v>RLS-18</v>
       </c>
       <c r="B144" t="str">
         <v>Demurrage</v>
       </c>
       <c r="C144" t="str">
-        <v>As the platform I enforce RLS on demurrage_rates (CRUD/UPSERT)</v>
+        <v>As the platform I enforce RLS on demurrage_invoices (SELECT/INSERT/UPDATE)</v>
       </c>
       <c r="D144" t="str">
-        <v>SELECT active; INSERT/UPDATE/DELETE active+admin.</v>
+        <v>050 final: active r/i/u; admin deletes; notifications, dispute, overdue cron.</v>
       </c>
       <c r="E144" t="str">
         <v>Verified</v>
@@ -5017,7 +5017,7 @@
         <v>SQL (migration) + Static</v>
       </c>
       <c r="I144" t="str">
-        <v>docs/RASTREABILIDADE.md (tabelas); demurrage_rates</v>
+        <v>docs/RASTREABILIDADE.md (tabelas); demurrage_invoices</v>
       </c>
       <c r="J144" t="str">
         <v>-</v>
@@ -5025,19 +5025,19 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>RLS-20</v>
+        <v>RLS-19</v>
       </c>
       <c r="B145" t="str">
-        <v>Chegadas/Saídas</v>
+        <v>Demurrage</v>
       </c>
       <c r="C145" t="str">
-        <v>As the platform I enforce RLS on ended_vessels (SELECT/INSERT)</v>
+        <v>As the platform I enforce RLS on demurrage_rates (CRUD/UPSERT)</v>
       </c>
       <c r="D145" t="str">
-        <v>SELECT any authenticated; INSERT active; DELETE admin; no UPDATE policy.</v>
+        <v>SELECT active; INSERT/UPDATE/DELETE active+admin.</v>
       </c>
       <c r="E145" t="str">
-        <v>Spec’d</v>
+        <v>Verified</v>
       </c>
       <c r="F145" t="str">
         <v>-</v>
@@ -5049,27 +5049,27 @@
         <v>SQL (migration) + Static</v>
       </c>
       <c r="I145" t="str">
-        <v>docs/RASTREABILIDADE.md (tabelas); ended_vessels</v>
+        <v>docs/RASTREABILIDADE.md (tabelas); demurrage_rates</v>
       </c>
       <c r="J145" t="str">
-        <v>Suspeita: read does not require active internal profile — intentionally Portal-compatible.</v>
+        <v>-</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>RLS-21</v>
+        <v>RLS-20</v>
       </c>
       <c r="B146" t="str">
-        <v>Granito</v>
+        <v>Chegadas/Saídas</v>
       </c>
       <c r="C146" t="str">
-        <v>As the platform I enforce RLS on granite_bl_charges (SELECT/INSERT/DELETE)</v>
+        <v>As the platform I enforce RLS on ended_vessels (SELECT/INSERT)</v>
       </c>
       <c r="D146" t="str">
-        <v>042 final: active r/i/u; admin deletes.</v>
+        <v>SELECT any authenticated; INSERT active; DELETE admin; no UPDATE policy.</v>
       </c>
       <c r="E146" t="str">
-        <v>Verified</v>
+        <v>Spec’d</v>
       </c>
       <c r="F146" t="str">
         <v>-</v>
@@ -5081,24 +5081,24 @@
         <v>SQL (migration) + Static</v>
       </c>
       <c r="I146" t="str">
-        <v>docs/RASTREABILIDADE.md (tabelas); granite_bl_charges</v>
+        <v>docs/RASTREABILIDADE.md (tabelas); ended_vessels</v>
       </c>
       <c r="J146" t="str">
-        <v>-</v>
+        <v>Suspeita: read does not require active internal profile — intentionally Portal-compatible.</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>RLS-22</v>
+        <v>RLS-21</v>
       </c>
       <c r="B147" t="str">
         <v>Granito</v>
       </c>
       <c r="C147" t="str">
-        <v>As the platform I enforce RLS on granite_bls (SELECT/UPDATE/UPSERT)</v>
+        <v>As the platform I enforce RLS on granite_bl_charges (SELECT/INSERT/DELETE)</v>
       </c>
       <c r="D147" t="str">
-        <v>042 final: active r/i/u; admin deletes; status feeds invoice/link guard.</v>
+        <v>042 final: active r/i/u; admin deletes.</v>
       </c>
       <c r="E147" t="str">
         <v>Verified</v>
@@ -5113,7 +5113,7 @@
         <v>SQL (migration) + Static</v>
       </c>
       <c r="I147" t="str">
-        <v>docs/RASTREABILIDADE.md (tabelas); granite_bls</v>
+        <v>docs/RASTREABILIDADE.md (tabelas); granite_bl_charges</v>
       </c>
       <c r="J147" t="str">
         <v>-</v>
@@ -5121,16 +5121,16 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>RLS-23</v>
+        <v>RLS-22</v>
       </c>
       <c r="B148" t="str">
         <v>Granito</v>
       </c>
       <c r="C148" t="str">
-        <v>As the platform I enforce RLS on granite_manifests (SELECT/INSERT)</v>
+        <v>As the platform I enforce RLS on granite_bls (SELECT/UPDATE/UPSERT)</v>
       </c>
       <c r="D148" t="str">
-        <v>042 final: active r/i/u; admin deletes.</v>
+        <v>042 final: active r/i/u; admin deletes; status feeds invoice/link guard.</v>
       </c>
       <c r="E148" t="str">
         <v>Verified</v>
@@ -5145,7 +5145,7 @@
         <v>SQL (migration) + Static</v>
       </c>
       <c r="I148" t="str">
-        <v>docs/RASTREABILIDADE.md (tabelas); granite_manifests</v>
+        <v>docs/RASTREABILIDADE.md (tabelas); granite_bls</v>
       </c>
       <c r="J148" t="str">
         <v>-</v>
@@ -5153,13 +5153,13 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>RLS-24</v>
+        <v>RLS-23</v>
       </c>
       <c r="B149" t="str">
         <v>Granito</v>
       </c>
       <c r="C149" t="str">
-        <v>As the platform I enforce RLS on granite_rates (SELECT/UPSERT/DELETE)</v>
+        <v>As the platform I enforce RLS on granite_manifests (SELECT/INSERT)</v>
       </c>
       <c r="D149" t="str">
         <v>042 final: active r/i/u; admin deletes.</v>
@@ -5177,7 +5177,7 @@
         <v>SQL (migration) + Static</v>
       </c>
       <c r="I149" t="str">
-        <v>docs/RASTREABILIDADE.md (tabelas); granite_rates</v>
+        <v>docs/RASTREABILIDADE.md (tabelas); granite_manifests</v>
       </c>
       <c r="J149" t="str">
         <v>-</v>
@@ -5185,16 +5185,16 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>RLS-25</v>
+        <v>RLS-24</v>
       </c>
       <c r="B150" t="str">
-        <v>Importações</v>
+        <v>Granito</v>
       </c>
       <c r="C150" t="str">
-        <v>As the platform I enforce RLS on import_batches (SELECT/INSERT/UPDATE)</v>
+        <v>As the platform I enforce RLS on granite_rates (SELECT/UPSERT/DELETE)</v>
       </c>
       <c r="D150" t="str">
-        <v>010 final: active r/i/u; admin deletes; links errors/B/Ls and billing run.</v>
+        <v>042 final: active r/i/u; admin deletes.</v>
       </c>
       <c r="E150" t="str">
         <v>Verified</v>
@@ -5209,7 +5209,7 @@
         <v>SQL (migration) + Static</v>
       </c>
       <c r="I150" t="str">
-        <v>docs/RASTREABILIDADE.md (tabelas); import_batches</v>
+        <v>docs/RASTREABILIDADE.md (tabelas); granite_rates</v>
       </c>
       <c r="J150" t="str">
         <v>-</v>
@@ -5217,16 +5217,16 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>RLS-26</v>
+        <v>RLS-25</v>
       </c>
       <c r="B151" t="str">
         <v>Importações</v>
       </c>
       <c r="C151" t="str">
-        <v>As the platform I enforce RLS on import_errors (INSERT)</v>
+        <v>As the platform I enforce RLS on import_batches (SELECT/INSERT/UPDATE)</v>
       </c>
       <c r="D151" t="str">
-        <v>010 final: active r/i/u; admin deletes.</v>
+        <v>010 final: active r/i/u; admin deletes; links errors/B/Ls and billing run.</v>
       </c>
       <c r="E151" t="str">
         <v>Verified</v>
@@ -5241,7 +5241,7 @@
         <v>SQL (migration) + Static</v>
       </c>
       <c r="I151" t="str">
-        <v>docs/RASTREABILIDADE.md (tabelas); import_errors</v>
+        <v>docs/RASTREABILIDADE.md (tabelas); import_batches</v>
       </c>
       <c r="J151" t="str">
         <v>-</v>
@@ -5249,16 +5249,16 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>RLS-27</v>
+        <v>RLS-26</v>
       </c>
       <c r="B152" t="str">
-        <v>Faturamento</v>
+        <v>Importações</v>
       </c>
       <c r="C152" t="str">
-        <v>As the platform I enforce RLS on invoice_bls (SELECT)</v>
+        <v>As the platform I enforce RLS on import_errors (INSERT)</v>
       </c>
       <c r="D152" t="str">
-        <v>020: all operations admin; trigger blocks duplicate active link.</v>
+        <v>010 final: active r/i/u; admin deletes.</v>
       </c>
       <c r="E152" t="str">
         <v>Verified</v>
@@ -5273,7 +5273,7 @@
         <v>SQL (migration) + Static</v>
       </c>
       <c r="I152" t="str">
-        <v>docs/RASTREABILIDADE.md (tabelas); invoice_bls</v>
+        <v>docs/RASTREABILIDADE.md (tabelas); import_errors</v>
       </c>
       <c r="J152" t="str">
         <v>-</v>
@@ -5281,19 +5281,19 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>RLS-28</v>
+        <v>RLS-27</v>
       </c>
       <c r="B153" t="str">
-        <v>Ledger</v>
+        <v>Faturamento</v>
       </c>
       <c r="C153" t="str">
-        <v>As the platform I enforce RLS on invoice_receivable_links (SELECT)</v>
+        <v>As the platform I enforce RLS on invoice_bls (SELECT)</v>
       </c>
       <c r="D153" t="str">
-        <v>20260529100000: all operations admin; triggers obsolete/re-chain consolidated.</v>
+        <v>020: all operations admin; trigger blocks duplicate active link.</v>
       </c>
       <c r="E153" t="str">
-        <v>Tested-Pass</v>
+        <v>Verified</v>
       </c>
       <c r="F153" t="str">
         <v>-</v>
@@ -5305,7 +5305,7 @@
         <v>SQL (migration) + Static</v>
       </c>
       <c r="I153" t="str">
-        <v>docs/RASTREABILIDADE.md (tabelas); invoice_receivable_links</v>
+        <v>docs/RASTREABILIDADE.md (tabelas); invoice_bls</v>
       </c>
       <c r="J153" t="str">
         <v>-</v>
@@ -5313,19 +5313,19 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>RLS-29</v>
+        <v>RLS-28</v>
       </c>
       <c r="B154" t="str">
-        <v>Faturamento</v>
+        <v>Ledger</v>
       </c>
       <c r="C154" t="str">
-        <v>As the platform I enforce RLS on invoices (SELECT/UPDATE)</v>
+        <v>As the platform I enforce RLS on invoice_receivable_links (SELECT)</v>
       </c>
       <c r="D154" t="str">
-        <v>010+014: all operations admin; number, overdue guard, PIX, lifecycle, notifications, email webhook.</v>
+        <v>20260529100000: all operations admin; triggers obsolete/re-chain consolidated.</v>
       </c>
       <c r="E154" t="str">
-        <v>Verified</v>
+        <v>Tested-Pass</v>
       </c>
       <c r="F154" t="str">
         <v>-</v>
@@ -5337,7 +5337,7 @@
         <v>SQL (migration) + Static</v>
       </c>
       <c r="I154" t="str">
-        <v>docs/RASTREABILIDADE.md (tabelas); invoices</v>
+        <v>docs/RASTREABILIDADE.md (tabelas); invoice_receivable_links</v>
       </c>
       <c r="J154" t="str">
         <v>-</v>
@@ -5345,16 +5345,16 @@
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>RLS-30</v>
+        <v>RLS-29</v>
       </c>
       <c r="B155" t="str">
-        <v>Faturamento / Conciliação</v>
+        <v>Faturamento</v>
       </c>
       <c r="C155" t="str">
-        <v>As the platform I enforce RLS on payments (SELECT)</v>
+        <v>As the platform I enforce RLS on invoices (SELECT/UPDATE)</v>
       </c>
       <c r="D155" t="str">
-        <v>010+014: all operations admin.</v>
+        <v>010+014: all operations admin; number, overdue guard, PIX, lifecycle, notifications, email webhook.</v>
       </c>
       <c r="E155" t="str">
         <v>Verified</v>
@@ -5369,7 +5369,7 @@
         <v>SQL (migration) + Static</v>
       </c>
       <c r="I155" t="str">
-        <v>docs/RASTREABILIDADE.md (tabelas); payments</v>
+        <v>docs/RASTREABILIDADE.md (tabelas); invoices</v>
       </c>
       <c r="J155" t="str">
         <v>-</v>
@@ -5377,16 +5377,16 @@
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>RLS-31</v>
+        <v>RLS-30</v>
       </c>
       <c r="B156" t="str">
-        <v>Administração / Auth</v>
+        <v>Faturamento / Conciliação</v>
       </c>
       <c r="C156" t="str">
-        <v>As the platform I enforce RLS on user_profiles (SELECT/UPDATE)</v>
+        <v>As the platform I enforce RLS on payments (SELECT)</v>
       </c>
       <c r="D156" t="str">
-        <v>self/admin SELECT; own update only if active; admin any; INSERT/DELETE admin; trigger blocks self-elevation.</v>
+        <v>010+014: all operations admin.</v>
       </c>
       <c r="E156" t="str">
         <v>Verified</v>
@@ -5401,24 +5401,24 @@
         <v>SQL (migration) + Static</v>
       </c>
       <c r="I156" t="str">
-        <v>docs/RASTREABILIDADE.md (tabelas); user_profiles</v>
+        <v>docs/RASTREABILIDADE.md (tabelas); payments</v>
       </c>
       <c r="J156" t="str">
-        <v>Sustains is_active_user()/is_admin().</v>
+        <v>-</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>RLS-32</v>
+        <v>RLS-31</v>
       </c>
       <c r="B157" t="str">
-        <v>Embarque de Vazios</v>
+        <v>Administração / Auth</v>
       </c>
       <c r="C157" t="str">
-        <v>As the platform I enforce RLS on vazios_bookings (SELECT/UPSERT)</v>
+        <v>As the platform I enforce RLS on user_profiles (SELECT/UPDATE)</v>
       </c>
       <c r="D157" t="str">
-        <v>042 final: active r/i/u; admin deletes.</v>
+        <v>self/admin SELECT; own update only if active; admin any; INSERT/DELETE admin; trigger blocks self-elevation.</v>
       </c>
       <c r="E157" t="str">
         <v>Verified</v>
@@ -5433,24 +5433,24 @@
         <v>SQL (migration) + Static</v>
       </c>
       <c r="I157" t="str">
-        <v>docs/RASTREABILIDADE.md (tabelas); vazios_bookings</v>
+        <v>docs/RASTREABILIDADE.md (tabelas); user_profiles</v>
       </c>
       <c r="J157" t="str">
-        <v>-</v>
+        <v>Sustains is_active_user()/is_admin().</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>RLS-33</v>
+        <v>RLS-32</v>
       </c>
       <c r="B158" t="str">
-        <v>Vazios de Importação</v>
+        <v>Embarque de Vazios</v>
       </c>
       <c r="C158" t="str">
-        <v>As the platform I enforce RLS on vazios_importacao_containers (SELECT/UPSERT)</v>
+        <v>As the platform I enforce RLS on vazios_bookings (SELECT/UPSERT)</v>
       </c>
       <c r="D158" t="str">
-        <v>042 + 20260610163251: active r/i/u; admin deletes.</v>
+        <v>042 final: active r/i/u; admin deletes.</v>
       </c>
       <c r="E158" t="str">
         <v>Verified</v>
@@ -5465,7 +5465,7 @@
         <v>SQL (migration) + Static</v>
       </c>
       <c r="I158" t="str">
-        <v>docs/RASTREABILIDADE.md (tabelas); vazios_importacao_containers</v>
+        <v>docs/RASTREABILIDADE.md (tabelas); vazios_bookings</v>
       </c>
       <c r="J158" t="str">
         <v>-</v>
@@ -5473,13 +5473,13 @@
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>RLS-34</v>
+        <v>RLS-33</v>
       </c>
       <c r="B159" t="str">
         <v>Vazios de Importação</v>
       </c>
       <c r="C159" t="str">
-        <v>As the platform I enforce RLS on vazios_importacao_manifests (SELECT/INSERT)</v>
+        <v>As the platform I enforce RLS on vazios_importacao_containers (SELECT/UPSERT)</v>
       </c>
       <c r="D159" t="str">
         <v>042 + 20260610163251: active r/i/u; admin deletes.</v>
@@ -5497,7 +5497,7 @@
         <v>SQL (migration) + Static</v>
       </c>
       <c r="I159" t="str">
-        <v>docs/RASTREABILIDADE.md (tabelas); vazios_importacao_manifests</v>
+        <v>docs/RASTREABILIDADE.md (tabelas); vazios_importacao_containers</v>
       </c>
       <c r="J159" t="str">
         <v>-</v>
@@ -5505,16 +5505,16 @@
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>RLS-35</v>
+        <v>RLS-34</v>
       </c>
       <c r="B160" t="str">
-        <v>Embarque de Vazios</v>
+        <v>Vazios de Importação</v>
       </c>
       <c r="C160" t="str">
-        <v>As the platform I enforce RLS on vazios_manifests (SELECT/INSERT)</v>
+        <v>As the platform I enforce RLS on vazios_importacao_manifests (SELECT/INSERT)</v>
       </c>
       <c r="D160" t="str">
-        <v>042 final: active r/i/u; admin deletes.</v>
+        <v>042 + 20260610163251: active r/i/u; admin deletes.</v>
       </c>
       <c r="E160" t="str">
         <v>Verified</v>
@@ -5529,7 +5529,7 @@
         <v>SQL (migration) + Static</v>
       </c>
       <c r="I160" t="str">
-        <v>docs/RASTREABILIDADE.md (tabelas); vazios_manifests</v>
+        <v>docs/RASTREABILIDADE.md (tabelas); vazios_importacao_manifests</v>
       </c>
       <c r="J160" t="str">
         <v>-</v>
@@ -5537,16 +5537,16 @@
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>RLS-36</v>
+        <v>RLS-35</v>
       </c>
       <c r="B161" t="str">
-        <v>Veículos</v>
+        <v>Embarque de Vazios</v>
       </c>
       <c r="C161" t="str">
-        <v>As the platform I enforce RLS on vehicles (SELECT/DELETE)</v>
+        <v>As the platform I enforce RLS on vazios_manifests (SELECT/INSERT)</v>
       </c>
       <c r="D161" t="str">
-        <v>010 final: active r/i/u; admin deletes; trigger validates voyage/B/L/container.</v>
+        <v>042 final: active r/i/u; admin deletes.</v>
       </c>
       <c r="E161" t="str">
         <v>Verified</v>
@@ -5561,7 +5561,7 @@
         <v>SQL (migration) + Static</v>
       </c>
       <c r="I161" t="str">
-        <v>docs/RASTREABILIDADE.md (tabelas); vehicles</v>
+        <v>docs/RASTREABILIDADE.md (tabelas); vazios_manifests</v>
       </c>
       <c r="J161" t="str">
         <v>-</v>
@@ -5569,16 +5569,16 @@
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>RLS-37</v>
+        <v>RLS-36</v>
       </c>
       <c r="B162" t="str">
-        <v>Chegadas/Saídas</v>
+        <v>Veículos</v>
       </c>
       <c r="C162" t="str">
-        <v>As the platform I enforce RLS on vessel_schedules (CRUD)</v>
+        <v>As the platform I enforce RLS on vehicles (SELECT/DELETE)</v>
       </c>
       <c r="D162" t="str">
-        <v>SELECT any authenticated; INSERT/UPDATE active; DELETE admin; realtime for Portal widget.</v>
+        <v>010 final: active r/i/u; admin deletes; trigger validates voyage/B/L/container.</v>
       </c>
       <c r="E162" t="str">
         <v>Verified</v>
@@ -5593,7 +5593,7 @@
         <v>SQL (migration) + Static</v>
       </c>
       <c r="I162" t="str">
-        <v>docs/RASTREABILIDADE.md (tabelas); vessel_schedules</v>
+        <v>docs/RASTREABILIDADE.md (tabelas); vehicles</v>
       </c>
       <c r="J162" t="str">
         <v>-</v>
@@ -5601,19 +5601,19 @@
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>RLS-38</v>
+        <v>RLS-37</v>
       </c>
       <c r="B163" t="str">
-        <v>Viagens</v>
+        <v>Chegadas/Saídas</v>
       </c>
       <c r="C163" t="str">
-        <v>As the platform I enforce RLS on vessels (SELECT/INSERT)</v>
+        <v>As the platform I enforce RLS on vessel_schedules (CRUD)</v>
       </c>
       <c r="D163" t="str">
-        <v>010 final: active r/i/u; admin deletes.</v>
+        <v>SELECT any authenticated; INSERT/UPDATE active; DELETE admin; realtime for Portal widget.</v>
       </c>
       <c r="E163" t="str">
-        <v>Spec’d</v>
+        <v>Verified</v>
       </c>
       <c r="F163" t="str">
         <v>-</v>
@@ -5625,7 +5625,7 @@
         <v>SQL (migration) + Static</v>
       </c>
       <c r="I163" t="str">
-        <v>docs/RASTREABILIDADE.md (tabelas); vessels</v>
+        <v>docs/RASTREABILIDADE.md (tabelas); vessel_schedules</v>
       </c>
       <c r="J163" t="str">
         <v>-</v>
@@ -5633,19 +5633,19 @@
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>RLS-39</v>
+        <v>RLS-38</v>
       </c>
       <c r="B164" t="str">
-        <v>Viagens / Line Up</v>
+        <v>Viagens</v>
       </c>
       <c r="C164" t="str">
-        <v>As the platform I enforce RLS on voyage_export_schedules (SELECT/UPSERT/DELETE)</v>
+        <v>As the platform I enforce RLS on vessels (SELECT/INSERT)</v>
       </c>
       <c r="D164" t="str">
-        <v>20260609134000: active r/i/u; admin deletes.</v>
+        <v>010 final: active r/i/u; admin deletes.</v>
       </c>
       <c r="E164" t="str">
-        <v>Tested-Pass</v>
+        <v>Spec’d</v>
       </c>
       <c r="F164" t="str">
         <v>-</v>
@@ -5657,27 +5657,27 @@
         <v>SQL (migration) + Static</v>
       </c>
       <c r="I164" t="str">
-        <v>docs/RASTREABILIDADE.md (tabelas); voyage_export_schedules</v>
+        <v>docs/RASTREABILIDADE.md (tabelas); vessels</v>
       </c>
       <c r="J164" t="str">
-        <v>rlsHardeningMigration.test.ts</v>
+        <v>-</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>RLS-40</v>
+        <v>RLS-39</v>
       </c>
       <c r="B165" t="str">
-        <v>Viagens</v>
+        <v>Viagens / Line Up</v>
       </c>
       <c r="C165" t="str">
-        <v>As the platform I enforce RLS on voyages (CRUD)</v>
+        <v>As the platform I enforce RLS on voyage_export_schedules (SELECT/UPSERT/DELETE)</v>
       </c>
       <c r="D165" t="str">
-        <v>010 final: active r/i/u; admin deletes; POD/POL snapshots by trigger; delete dependency guard.</v>
+        <v>20260609134000: active r/i/u; admin deletes.</v>
       </c>
       <c r="E165" t="str">
-        <v>Verified</v>
+        <v>Tested-Pass</v>
       </c>
       <c r="F165" t="str">
         <v>-</v>
@@ -5689,24 +5689,24 @@
         <v>SQL (migration) + Static</v>
       </c>
       <c r="I165" t="str">
-        <v>docs/RASTREABILIDADE.md (tabelas); voyages</v>
+        <v>docs/RASTREABILIDADE.md (tabelas); voyage_export_schedules</v>
       </c>
       <c r="J165" t="str">
-        <v>-</v>
+        <v>rlsHardeningMigration.test.ts</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>TRG-01</v>
+        <v>RLS-40</v>
       </c>
       <c r="B166" t="str">
-        <v>Faturamento</v>
+        <v>Viagens</v>
       </c>
       <c r="C166" t="str">
-        <v>As the platform I enforce the assign_invoice_number trigger/job</v>
+        <v>As the platform I enforce RLS on voyages (CRUD)</v>
       </c>
       <c r="D166" t="str">
-        <v>BEFORE INSERT invoices: increments annual counter and fills invoice number.</v>
+        <v>010 final: active r/i/u; admin deletes; POD/POL snapshots by trigger; delete dependency guard.</v>
       </c>
       <c r="E166" t="str">
         <v>Verified</v>
@@ -5718,27 +5718,27 @@
         <v>-</v>
       </c>
       <c r="H166" t="str">
-        <v>SQL (migration)</v>
+        <v>SQL (migration) + Static</v>
       </c>
       <c r="I166" t="str">
-        <v>supabase/migrations/003_functions.sql</v>
+        <v>docs/RASTREABILIDADE.md (tabelas); voyages</v>
       </c>
       <c r="J166" t="str">
-        <v>Indirect effect; runtime not inspected for cron jobs.</v>
+        <v>-</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>TRG-02</v>
+        <v>TRG-01</v>
       </c>
       <c r="B167" t="str">
-        <v>Veículos</v>
+        <v>Faturamento</v>
       </c>
       <c r="C167" t="str">
-        <v>As the platform I enforce the validate_vehicle_relationships trigger/job</v>
+        <v>As the platform I enforce the assign_invoice_number trigger/job</v>
       </c>
       <c r="D167" t="str">
-        <v>BEFORE I/U vehicles: normalizes and rejects incoherent voyage/B/L/container.</v>
+        <v>BEFORE INSERT invoices: increments annual counter and fills invoice number.</v>
       </c>
       <c r="E167" t="str">
         <v>Verified</v>
@@ -5753,7 +5753,7 @@
         <v>SQL (migration)</v>
       </c>
       <c r="I167" t="str">
-        <v>supabase/migrations/004_vehicles.sql</v>
+        <v>supabase/migrations/003_functions.sql</v>
       </c>
       <c r="J167" t="str">
         <v>Indirect effect; runtime not inspected for cron jobs.</v>
@@ -5761,16 +5761,16 @@
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>TRG-03</v>
+        <v>TRG-02</v>
       </c>
       <c r="B168" t="str">
-        <v>Manifestos BB</v>
+        <v>Veículos</v>
       </c>
       <c r="C168" t="str">
-        <v>As the platform I enforce the validate_bl_breakbulk_item_parent trigger/job</v>
+        <v>As the platform I enforce the validate_vehicle_relationships trigger/job</v>
       </c>
       <c r="D168" t="str">
-        <v>BEFORE I/U bl_breakbulk_items: rejects item whose B/L is not carga_solta.</v>
+        <v>BEFORE I/U vehicles: normalizes and rejects incoherent voyage/B/L/container.</v>
       </c>
       <c r="E168" t="str">
         <v>Verified</v>
@@ -5785,7 +5785,7 @@
         <v>SQL (migration)</v>
       </c>
       <c r="I168" t="str">
-        <v>supabase/migrations/006_breakbulk_module.sql</v>
+        <v>supabase/migrations/004_vehicles.sql</v>
       </c>
       <c r="J168" t="str">
         <v>Indirect effect; runtime not inspected for cron jobs.</v>
@@ -5793,16 +5793,16 @@
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>TRG-04</v>
+        <v>TRG-03</v>
       </c>
       <c r="B169" t="str">
-        <v>Demurrage</v>
+        <v>Manifestos BB</v>
       </c>
       <c r="C169" t="str">
-        <v>As the platform I enforce the set_container_discharge_date trigger/job</v>
+        <v>As the platform I enforce the validate_bl_breakbulk_item_parent trigger/job</v>
       </c>
       <c r="D169" t="str">
-        <v>BEFORE INSERT bl_containers without discharge: copies voyages.ata.</v>
+        <v>BEFORE I/U bl_breakbulk_items: rejects item whose B/L is not carga_solta.</v>
       </c>
       <c r="E169" t="str">
         <v>Verified</v>
@@ -5817,7 +5817,7 @@
         <v>SQL (migration)</v>
       </c>
       <c r="I169" t="str">
-        <v>supabase/migrations/028_demurrage_module.sql</v>
+        <v>supabase/migrations/006_breakbulk_module.sql</v>
       </c>
       <c r="J169" t="str">
         <v>Indirect effect; runtime not inspected for cron jobs.</v>
@@ -5825,16 +5825,16 @@
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>TRG-05</v>
+        <v>TRG-04</v>
       </c>
       <c r="B170" t="str">
-        <v>Faturamento / Demurrage</v>
+        <v>Demurrage</v>
       </c>
       <c r="C170" t="str">
-        <v>As the platform I enforce the mark_overdue_invoices trigger/job</v>
+        <v>As the platform I enforce the set_container_discharge_date trigger/job</v>
       </c>
       <c r="D170" t="str">
-        <v>pg_cron daily 06:00 UTC: marks overdue local + demurrage invoices.</v>
+        <v>BEFORE INSERT bl_containers without discharge: copies voyages.ata.</v>
       </c>
       <c r="E170" t="str">
         <v>Verified</v>
@@ -5849,7 +5849,7 @@
         <v>SQL (migration)</v>
       </c>
       <c r="I170" t="str">
-        <v>supabase/migrations/031_overdue_enforcement.sql</v>
+        <v>supabase/migrations/028_demurrage_module.sql</v>
       </c>
       <c r="J170" t="str">
         <v>Indirect effect; runtime not inspected for cron jobs.</v>
@@ -5857,16 +5857,16 @@
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>TRG-06</v>
+        <v>TRG-05</v>
       </c>
       <c r="B171" t="str">
-        <v>Faturamento</v>
+        <v>Faturamento / Demurrage</v>
       </c>
       <c r="C171" t="str">
-        <v>As the platform I enforce the fn_block_invoice_overdue_customer trigger/job</v>
+        <v>As the platform I enforce the mark_overdue_invoices trigger/job</v>
       </c>
       <c r="D171" t="str">
-        <v>BEFORE INSERT invoices: blocks new invoice when customer has overdue local invoice.</v>
+        <v>pg_cron daily 06:00 UTC: marks overdue local + demurrage invoices.</v>
       </c>
       <c r="E171" t="str">
         <v>Verified</v>
@@ -5889,16 +5889,16 @@
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>TRG-07</v>
+        <v>TRG-06</v>
       </c>
       <c r="B172" t="str">
-        <v>Viagens / Line Up</v>
+        <v>Faturamento</v>
       </c>
       <c r="C172" t="str">
-        <v>As the platform I enforce the trg_voyage_schedule_snapshot trigger/job</v>
+        <v>As the platform I enforce the fn_block_invoice_overdue_customer trigger/job</v>
       </c>
       <c r="D172" t="str">
-        <v>AFTER INSERT audit_logs (POD/POL): updates voyages JSONB snapshot, preserving JSON null.</v>
+        <v>BEFORE INSERT invoices: blocks new invoice when customer has overdue local invoice.</v>
       </c>
       <c r="E172" t="str">
         <v>Verified</v>
@@ -5913,7 +5913,7 @@
         <v>SQL (migration)</v>
       </c>
       <c r="I172" t="str">
-        <v>supabase/migrations/052_fix_voyage_snapshot_null_new_value.sql</v>
+        <v>supabase/migrations/031_overdue_enforcement.sql</v>
       </c>
       <c r="J172" t="str">
         <v>Indirect effect; runtime not inspected for cron jobs.</v>
@@ -5921,16 +5921,16 @@
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>TRG-08</v>
+        <v>TRG-07</v>
       </c>
       <c r="B173" t="str">
-        <v>Faturamento</v>
+        <v>Viagens / Line Up</v>
       </c>
       <c r="C173" t="str">
-        <v>As the platform I enforce the prevent_duplicate_active_invoice_bl_link trigger/job</v>
+        <v>As the platform I enforce the trg_voyage_schedule_snapshot trigger/job</v>
       </c>
       <c r="D173" t="str">
-        <v>BEFORE I/U invoice_bls: rejects 2nd active/paid link for same B/L (23505/PT409).</v>
+        <v>AFTER INSERT audit_logs (POD/POL): updates voyages JSONB snapshot, preserving JSON null.</v>
       </c>
       <c r="E173" t="str">
         <v>Verified</v>
@@ -5945,7 +5945,7 @@
         <v>SQL (migration)</v>
       </c>
       <c r="I173" t="str">
-        <v>supabase/migrations/20260528134131_*.sql</v>
+        <v>supabase/migrations/052_fix_voyage_snapshot_null_new_value.sql</v>
       </c>
       <c r="J173" t="str">
         <v>Indirect effect; runtime not inspected for cron jobs.</v>
@@ -5953,16 +5953,16 @@
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>TRG-09</v>
+        <v>TRG-08</v>
       </c>
       <c r="B174" t="str">
-        <v>Taxas / Revisão</v>
+        <v>Faturamento</v>
       </c>
       <c r="C174" t="str">
-        <v>As the platform I enforce the guard_container_bl_without_containers trigger/job</v>
+        <v>As the platform I enforce the prevent_duplicate_active_invoice_bl_link trigger/job</v>
       </c>
       <c r="D174" t="str">
-        <v>AFTER I/U bls: synthetic pending + prevents empty container B/L staying calculated/ready.</v>
+        <v>BEFORE I/U invoice_bls: rejects 2nd active/paid link for same B/L (23505/PT409).</v>
       </c>
       <c r="E174" t="str">
         <v>Verified</v>
@@ -5985,16 +5985,16 @@
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>TRG-10</v>
+        <v>TRG-09</v>
       </c>
       <c r="B175" t="str">
-        <v>Ledger / Faturamento</v>
+        <v>Taxas / Revisão</v>
       </c>
       <c r="C175" t="str">
-        <v>As the platform I enforce the emit_invoice_on_bl_ready trigger/job</v>
+        <v>As the platform I enforce the guard_container_bl_without_containers trigger/job</v>
       </c>
       <c r="D175" t="str">
-        <v>AFTER I/U charge_status bls: syncs receivable + best-effort individual invoice; failure -&gt; audit auto_invoice_failed.</v>
+        <v>AFTER I/U bls: synthetic pending + prevents empty container B/L staying calculated/ready.</v>
       </c>
       <c r="E175" t="str">
         <v>Verified</v>
@@ -6009,7 +6009,7 @@
         <v>SQL (migration)</v>
       </c>
       <c r="I175" t="str">
-        <v>supabase/migrations/20260529140000_*.sql</v>
+        <v>supabase/migrations/20260528134131_*.sql</v>
       </c>
       <c r="J175" t="str">
         <v>Indirect effect; runtime not inspected for cron jobs.</v>
@@ -6017,16 +6017,16 @@
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>TRG-11</v>
+        <v>TRG-10</v>
       </c>
       <c r="B176" t="str">
-        <v>Faturamento / PIX</v>
+        <v>Ledger / Faturamento</v>
       </c>
       <c r="C176" t="str">
-        <v>As the platform I enforce the populate_local_invoice_pix_payload trigger/job</v>
+        <v>As the platform I enforce the emit_invoice_on_bl_ready trigger/job</v>
       </c>
       <c r="D176" t="str">
-        <v>BEFORE I/U invoices: generates PIX payload for local invoice.</v>
+        <v>AFTER I/U charge_status bls: syncs receivable + best-effort individual invoice; failure -&gt; audit auto_invoice_failed.</v>
       </c>
       <c r="E176" t="str">
         <v>Verified</v>
@@ -6041,7 +6041,7 @@
         <v>SQL (migration)</v>
       </c>
       <c r="I176" t="str">
-        <v>supabase/migrations/20260529144000_*.sql</v>
+        <v>supabase/migrations/20260529140000_*.sql</v>
       </c>
       <c r="J176" t="str">
         <v>Indirect effect; runtime not inspected for cron jobs.</v>
@@ -6049,16 +6049,16 @@
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>TRG-12</v>
+        <v>TRG-11</v>
       </c>
       <c r="B177" t="str">
-        <v>Administração / Auth</v>
+        <v>Faturamento / PIX</v>
       </c>
       <c r="C177" t="str">
-        <v>As the platform I enforce the prevent_user_profile_privilege_escalation trigger/job</v>
+        <v>As the platform I enforce the populate_local_invoice_pix_payload trigger/job</v>
       </c>
       <c r="D177" t="str">
-        <v>BEFORE UPDATE user_profiles: blocks self role/active change; service role allowed.</v>
+        <v>BEFORE I/U invoices: generates PIX payload for local invoice.</v>
       </c>
       <c r="E177" t="str">
         <v>Verified</v>
@@ -6073,7 +6073,7 @@
         <v>SQL (migration)</v>
       </c>
       <c r="I177" t="str">
-        <v>supabase/migrations/20260530102906_*.sql</v>
+        <v>supabase/migrations/20260529144000_*.sql</v>
       </c>
       <c r="J177" t="str">
         <v>Indirect effect; runtime not inspected for cron jobs.</v>
@@ -6081,16 +6081,16 @@
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>TRG-13</v>
+        <v>TRG-12</v>
       </c>
       <c r="B178" t="str">
-        <v>Portal / Notificações</v>
+        <v>Administração / Auth</v>
       </c>
       <c r="C178" t="str">
-        <v>As the platform I enforce the notify_invoice_issued trigger/job</v>
+        <v>As the platform I enforce the prevent_user_profile_privilege_escalation trigger/job</v>
       </c>
       <c r="D178" t="str">
-        <v>AFTER I/U status invoices: in-app notification when invoice becomes issued.</v>
+        <v>BEFORE UPDATE user_profiles: blocks self role/active change; service role allowed.</v>
       </c>
       <c r="E178" t="str">
         <v>Verified</v>
@@ -6105,7 +6105,7 @@
         <v>SQL (migration)</v>
       </c>
       <c r="I178" t="str">
-        <v>supabase/migrations/20260615000003_*.sql</v>
+        <v>supabase/migrations/20260530102906_*.sql</v>
       </c>
       <c r="J178" t="str">
         <v>Indirect effect; runtime not inspected for cron jobs.</v>
@@ -6113,16 +6113,16 @@
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>TRG-14</v>
+        <v>TRG-13</v>
       </c>
       <c r="B179" t="str">
-        <v>Revisão / Billing gate</v>
+        <v>Portal / Notificações</v>
       </c>
       <c r="C179" t="str">
-        <v>As the platform I enforce the promote_calculated_bl_ready_for_billing trigger/job</v>
+        <v>As the platform I enforce the notify_invoice_issued trigger/job</v>
       </c>
       <c r="D179" t="str">
-        <v>BEFORE I/U bls: only promotes when canonical gate/client/BRL/currencies allow; execute revoked.</v>
+        <v>AFTER I/U status invoices: in-app notification when invoice becomes issued.</v>
       </c>
       <c r="E179" t="str">
         <v>Verified</v>
@@ -6137,7 +6137,7 @@
         <v>SQL (migration)</v>
       </c>
       <c r="I179" t="str">
-        <v>supabase/migrations/20260619130000_*.sql</v>
+        <v>supabase/migrations/20260615000003_*.sql</v>
       </c>
       <c r="J179" t="str">
         <v>Indirect effect; runtime not inspected for cron jobs.</v>
@@ -6145,16 +6145,16 @@
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>TRG-15</v>
+        <v>TRG-14</v>
       </c>
       <c r="B180" t="str">
         <v>Revisão / Billing gate</v>
       </c>
       <c r="C180" t="str">
-        <v>As the platform I enforce the prevent_pending_review_invoice trigger/job</v>
+        <v>As the platform I enforce the promote_calculated_bl_ready_for_billing trigger/job</v>
       </c>
       <c r="D180" t="str">
-        <v>BEFORE I/U financial_status bls: blocks invoiced while review/canonical pendencies open.</v>
+        <v>BEFORE I/U bls: only promotes when canonical gate/client/BRL/currencies allow; execute revoked.</v>
       </c>
       <c r="E180" t="str">
         <v>Verified</v>
@@ -6175,10 +6175,42 @@
         <v>Indirect effect; runtime not inspected for cron jobs.</v>
       </c>
     </row>
+    <row r="181">
+      <c r="A181" t="str">
+        <v>TRG-15</v>
+      </c>
+      <c r="B181" t="str">
+        <v>Revisão / Billing gate</v>
+      </c>
+      <c r="C181" t="str">
+        <v>As the platform I enforce the prevent_pending_review_invoice trigger/job</v>
+      </c>
+      <c r="D181" t="str">
+        <v>BEFORE I/U financial_status bls: blocks invoiced while review/canonical pendencies open.</v>
+      </c>
+      <c r="E181" t="str">
+        <v>Verified</v>
+      </c>
+      <c r="F181" t="str">
+        <v>-</v>
+      </c>
+      <c r="G181" t="str">
+        <v>-</v>
+      </c>
+      <c r="H181" t="str">
+        <v>SQL (migration)</v>
+      </c>
+      <c r="I181" t="str">
+        <v>supabase/migrations/20260619130000_*.sql</v>
+      </c>
+      <c r="J181" t="str">
+        <v>Indirect effect; runtime not inspected for cron jobs.</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J180"/>
+  <autoFilter ref="A1:J181"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J180"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J181"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -6212,7 +6244,7 @@
         <v>Total stories</v>
       </c>
       <c r="B3">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="4">
@@ -6220,7 +6252,7 @@
         <v>Status: Verified</v>
       </c>
       <c r="B4">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="5">
